--- a/donnees/milieux/Associations_milieux_habitats.xlsx
+++ b/donnees/milieux/Associations_milieux_habitats.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sans association" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Associations'!$A$1:$L$938</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Associations'!$A$1:$L$987</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L938"/>
+  <dimension ref="A1:L987"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -52021,17 +52021,17 @@
     <row r="849">
       <c r="A849" s="2" t="inlineStr">
         <is>
-          <t>Sophora japonica</t>
+          <t>Solidago canadensis</t>
         </is>
       </c>
       <c r="B849" s="2" t="inlineStr">
         <is>
-          <t>Sophora du Japon</t>
+          <t>Verge d'or</t>
         </is>
       </c>
       <c r="C849" s="2" t="inlineStr">
         <is>
-          <t>exotique (cultivée en France)</t>
+          <t>naturalisée</t>
         </is>
       </c>
       <c r="D849" s="2" t="inlineStr">
@@ -52041,22 +52041,22 @@
       </c>
       <c r="E849" s="2" t="inlineStr">
         <is>
-          <t>Jardins, parcs et plantes ornementales</t>
+          <t>Murs, friches et espaces très artificialisés</t>
         </is>
       </c>
       <c r="F849" s="2" t="inlineStr">
         <is>
-          <t>HAB-01</t>
+          <t>HAB-03</t>
         </is>
       </c>
       <c r="G849" s="2" t="inlineStr">
         <is>
-          <t>cultivé ou planté</t>
+          <t>spontané (milieu secondaire)</t>
         </is>
       </c>
       <c r="H849" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>typique</t>
         </is>
       </c>
       <c r="I849" s="2" t="inlineStr">
@@ -52066,34 +52066,34 @@
       </c>
       <c r="J849" s="3" t="inlineStr">
         <is>
-          <t>Espèce exotique (origine : Chine, Corée), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+          <t>C'est généralement l'une des premières plantes à coloniser une zone après perturbations et elle persiste rarement une fois que les arbustes et les arbres s'établissent.</t>
         </is>
       </c>
       <c r="K849" s="2" t="inlineStr">
         <is>
-          <t>https://www.rhs.org.uk/plants/231724/wd/details</t>
+          <t>https://fr.wikipedia.org/wiki/Solidago_canadensis</t>
         </is>
       </c>
       <c r="L849" s="3" t="inlineStr">
         <is>
-          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+          <t>introduite en France comme ornementale et localement envahissante - milieu décrit pour l'aire générale</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" s="2" t="inlineStr">
         <is>
-          <t>Sorbaria sorbifolia</t>
+          <t>Solidago canadensis</t>
         </is>
       </c>
       <c r="B850" s="2" t="inlineStr">
         <is>
-          <t>Sorbaria</t>
+          <t>Verge d'or</t>
         </is>
       </c>
       <c r="C850" s="2" t="inlineStr">
         <is>
-          <t>exotique (cultivée en France)</t>
+          <t>naturalisée</t>
         </is>
       </c>
       <c r="D850" s="2" t="inlineStr">
@@ -52128,59 +52128,59 @@
       </c>
       <c r="J850" s="3" t="inlineStr">
         <is>
-          <t>Espèce exotique (origine : Asie du Nord-Est (Sibérie, Mandchourie, Corée, Japon)), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+          <t>Elle a été introduite dans de nombreuses régions tempérées du monde, dont la France, en tant que plante ornementale et mellifère.</t>
         </is>
       </c>
       <c r="K850" s="2" t="inlineStr">
         <is>
-          <t>https://rhs.org.uk/Plants/17517/wd/Details</t>
+          <t>https://fr.wikipedia.org/wiki/Solidago_canadensis</t>
         </is>
       </c>
       <c r="L850" s="3" t="inlineStr">
         <is>
-          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+          <t>introduite en France comme ornementale et localement envahissante - milieu décrit pour l'aire générale</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" s="2" t="inlineStr">
         <is>
-          <t>Sorbus aria</t>
+          <t>Sophora japonica</t>
         </is>
       </c>
       <c r="B851" s="2" t="inlineStr">
         <is>
-          <t>Alisier blanc</t>
+          <t>Sophora du Japon</t>
         </is>
       </c>
       <c r="C851" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>exotique (cultivée en France)</t>
         </is>
       </c>
       <c r="D851" s="2" t="inlineStr">
         <is>
-          <t>Forêts et sous-bois</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E851" s="2" t="inlineStr">
         <is>
-          <t>Forêts de feuillus caducs</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F851" s="2" t="inlineStr">
         <is>
-          <t>FOR-01</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G851" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H851" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I851" s="2" t="inlineStr">
@@ -52190,54 +52190,54 @@
       </c>
       <c r="J851" s="3" t="inlineStr">
         <is>
-          <t>Bois caducifoliés basophiles et méso-oligotrophes des plaines et collines (Quercetalia pubescentis).</t>
+          <t>Espèce exotique (origine : Chine, Corée), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
         </is>
       </c>
       <c r="K851" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/eflore/?action=fiche&amp;module=fiche&amp;num_nom=65271&amp;onglet=synthese&amp;referentiel=bdtfx</t>
+          <t>https://www.rhs.org.uk/plants/231724/wd/details</t>
         </is>
       </c>
       <c r="L851" s="3" t="inlineStr">
         <is>
-          <t>absent de l'Ouest et de la région méditerranéenne</t>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
         </is>
       </c>
     </row>
     <row r="852">
       <c r="A852" s="2" t="inlineStr">
         <is>
-          <t>Sorbus aria</t>
+          <t>Sorbaria sorbifolia</t>
         </is>
       </c>
       <c r="B852" s="2" t="inlineStr">
         <is>
-          <t>Alisier blanc</t>
+          <t>Sorbaria</t>
         </is>
       </c>
       <c r="C852" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>exotique (cultivée en France)</t>
         </is>
       </c>
       <c r="D852" s="2" t="inlineStr">
         <is>
-          <t>Rochers, éboulis et sols superficiels</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E852" s="2" t="inlineStr">
         <is>
-          <t>Falaises intérieures et dalles rocheuses</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F852" s="2" t="inlineStr">
         <is>
-          <t>ROC-02</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G852" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H852" s="2" t="inlineStr">
@@ -52252,29 +52252,29 @@
       </c>
       <c r="J852" s="3" t="inlineStr">
         <is>
-          <t>Bois et rochers des montagnes dans une grande partie de la France.</t>
+          <t>Espèce exotique (origine : Asie du Nord-Est (Sibérie, Mandchourie, Corée, Japon)), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
         </is>
       </c>
       <c r="K852" s="2" t="inlineStr">
         <is>
-          <t>https://tela-botanica.org/eflore/?action=fiche&amp;action=fiche&amp;module=fiche&amp;module=fiche&amp;niveau=3&amp;num_nom=54275&amp;num_nom=54275&amp;onglet=synthese&amp;referentiel=bdtfx&amp;referentiel=bdtfx</t>
+          <t>https://rhs.org.uk/Plants/17517/wd/Details</t>
         </is>
       </c>
       <c r="L852" s="3" t="inlineStr">
         <is>
-          <t>absent de l'Ouest et de la région méditerranéenne</t>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" s="2" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Sorbus aria</t>
         </is>
       </c>
       <c r="B853" s="2" t="inlineStr">
         <is>
-          <t>Sorbier des oiseleurs</t>
+          <t>Alisier blanc</t>
         </is>
       </c>
       <c r="C853" s="2" t="inlineStr">
@@ -52314,29 +52314,29 @@
       </c>
       <c r="J853" s="3" t="inlineStr">
         <is>
-          <t>Bois des montagnes, surtout siliceuses, dans une grande partie de la France, nul dans la région méditerranéenne.</t>
+          <t>Bois caducifoliés basophiles et méso-oligotrophes des plaines et collines (Quercetalia pubescentis).</t>
         </is>
       </c>
       <c r="K853" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-65277</t>
+          <t>https://www.tela-botanica.org/eflore/?action=fiche&amp;module=fiche&amp;num_nom=65271&amp;onglet=synthese&amp;referentiel=bdtfx</t>
         </is>
       </c>
       <c r="L853" s="3" t="inlineStr">
         <is>
-          <t>absent de la région méditerranéenne</t>
+          <t>absent de l'Ouest et de la région méditerranéenne</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" s="2" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Sorbus aria</t>
         </is>
       </c>
       <c r="B854" s="2" t="inlineStr">
         <is>
-          <t>Sorbier des oiseleurs</t>
+          <t>Alisier blanc</t>
         </is>
       </c>
       <c r="C854" s="2" t="inlineStr">
@@ -52346,17 +52346,17 @@
       </c>
       <c r="D854" s="2" t="inlineStr">
         <is>
-          <t>Haies, lisières et fourrés</t>
+          <t>Rochers, éboulis et sols superficiels</t>
         </is>
       </c>
       <c r="E854" s="2" t="inlineStr">
         <is>
-          <t>Lisières et clairières herbacées</t>
+          <t>Falaises intérieures et dalles rocheuses</t>
         </is>
       </c>
       <c r="F854" s="2" t="inlineStr">
         <is>
-          <t>LIS-02</t>
+          <t>ROC-02</t>
         </is>
       </c>
       <c r="G854" s="2" t="inlineStr">
@@ -52376,17 +52376,17 @@
       </c>
       <c r="J854" s="3" t="inlineStr">
         <is>
-          <t>Il vit principalement en lisière de forêts d'épicéas.</t>
+          <t>Bois et rochers des montagnes dans une grande partie de la France.</t>
         </is>
       </c>
       <c r="K854" s="2" t="inlineStr">
         <is>
-          <t>https://fr.wikipedia.org/wiki/Sorbier_des_oiseleurs</t>
+          <t>https://tela-botanica.org/eflore/?action=fiche&amp;action=fiche&amp;module=fiche&amp;module=fiche&amp;niveau=3&amp;num_nom=54275&amp;num_nom=54275&amp;onglet=synthese&amp;referentiel=bdtfx&amp;referentiel=bdtfx</t>
         </is>
       </c>
       <c r="L854" s="3" t="inlineStr">
         <is>
-          <t>absent de la région méditerranéenne</t>
+          <t>absent de l'Ouest et de la région méditerranéenne</t>
         </is>
       </c>
     </row>
@@ -52408,17 +52408,17 @@
       </c>
       <c r="D855" s="2" t="inlineStr">
         <is>
-          <t>Landes, bruyères et fourrés méditerranéens</t>
+          <t>Forêts et sous-bois</t>
         </is>
       </c>
       <c r="E855" s="2" t="inlineStr">
         <is>
-          <t>Landes tempérées à bruyères</t>
+          <t>Forêts de feuillus caducs</t>
         </is>
       </c>
       <c r="F855" s="2" t="inlineStr">
         <is>
-          <t>LAN-01</t>
+          <t>FOR-01</t>
         </is>
       </c>
       <c r="G855" s="2" t="inlineStr">
@@ -52428,7 +52428,7 @@
       </c>
       <c r="H855" s="2" t="inlineStr">
         <is>
-          <t>possible</t>
+          <t>typique</t>
         </is>
       </c>
       <c r="I855" s="2" t="inlineStr">
@@ -52438,12 +52438,12 @@
       </c>
       <c r="J855" s="3" t="inlineStr">
         <is>
-          <t>Il pousse dans les bois, les forêts et les haies, dans les landes et les lieux rocheux, souvent en moyenne montagne, sur sol léger.</t>
+          <t>Bois des montagnes, surtout siliceuses, dans une grande partie de la France, nul dans la région méditerranéenne.</t>
         </is>
       </c>
       <c r="K855" s="2" t="inlineStr">
         <is>
-          <t>https://fr.wikipedia.org/wiki/Sorbier_des_oiseleurs</t>
+          <t>https://www.tela-botanica.org/bdtfx-nn-65277</t>
         </is>
       </c>
       <c r="L855" s="3" t="inlineStr">
@@ -52455,12 +52455,12 @@
     <row r="856">
       <c r="A856" s="2" t="inlineStr">
         <is>
-          <t>Sorbus domestica</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="B856" s="2" t="inlineStr">
         <is>
-          <t>Cormier</t>
+          <t>Sorbier des oiseleurs</t>
         </is>
       </c>
       <c r="C856" s="2" t="inlineStr">
@@ -52475,12 +52475,12 @@
       </c>
       <c r="E856" s="2" t="inlineStr">
         <is>
-          <t>Haies et lignes d'arbres</t>
+          <t>Lisières et clairières herbacées</t>
         </is>
       </c>
       <c r="F856" s="2" t="inlineStr">
         <is>
-          <t>LIS-01</t>
+          <t>LIS-02</t>
         </is>
       </c>
       <c r="G856" s="2" t="inlineStr">
@@ -52490,7 +52490,7 @@
       </c>
       <c r="H856" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I856" s="2" t="inlineStr">
@@ -52500,29 +52500,29 @@
       </c>
       <c r="J856" s="3" t="inlineStr">
         <is>
-          <t>Haies et bois, surtout calcaires, principalement dans le Midi, le Centre et l'Ouest, et en Corse.</t>
+          <t>Il vit principalement en lisière de forêts d'épicéas.</t>
         </is>
       </c>
       <c r="K856" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/eflore/?action=fiche&amp;module=fiche&amp;niveau=2&amp;num_nom=65300&amp;onglet=description&amp;referentiel=bdtfx</t>
+          <t>https://fr.wikipedia.org/wiki/Sorbier_des_oiseleurs</t>
         </is>
       </c>
       <c r="L856" s="3" t="inlineStr">
         <is>
-          <t>rare à l'état spontané - souvent planté près des habitations</t>
+          <t>absent de la région méditerranéenne</t>
         </is>
       </c>
     </row>
     <row r="857">
       <c r="A857" s="2" t="inlineStr">
         <is>
-          <t>Sorbus domestica</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="B857" s="2" t="inlineStr">
         <is>
-          <t>Cormier</t>
+          <t>Sorbier des oiseleurs</t>
         </is>
       </c>
       <c r="C857" s="2" t="inlineStr">
@@ -52532,17 +52532,17 @@
       </c>
       <c r="D857" s="2" t="inlineStr">
         <is>
-          <t>Forêts et sous-bois</t>
+          <t>Landes, bruyères et fourrés méditerranéens</t>
         </is>
       </c>
       <c r="E857" s="2" t="inlineStr">
         <is>
-          <t>Forêts de feuillus caducs</t>
+          <t>Landes tempérées à bruyères</t>
         </is>
       </c>
       <c r="F857" s="2" t="inlineStr">
         <is>
-          <t>FOR-01</t>
+          <t>LAN-01</t>
         </is>
       </c>
       <c r="G857" s="2" t="inlineStr">
@@ -52552,7 +52552,7 @@
       </c>
       <c r="H857" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>possible</t>
         </is>
       </c>
       <c r="I857" s="2" t="inlineStr">
@@ -52562,17 +52562,17 @@
       </c>
       <c r="J857" s="3" t="inlineStr">
         <is>
-          <t>Rare à l'état spontané dans les chênaies pubescentes en Lozère.</t>
+          <t>Il pousse dans les bois, les forêts et les haies, dans les landes et les lieux rocheux, souvent en moyenne montagne, sur sol léger.</t>
         </is>
       </c>
       <c r="K857" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/eflore/?action=fiche&amp;module=fiche&amp;niveau=2&amp;num_nom=65300&amp;onglet=description&amp;referentiel=bdtfx</t>
+          <t>https://fr.wikipedia.org/wiki/Sorbier_des_oiseleurs</t>
         </is>
       </c>
       <c r="L857" s="3" t="inlineStr">
         <is>
-          <t>rare à l'état spontané - souvent planté près des habitations</t>
+          <t>absent de la région méditerranéenne</t>
         </is>
       </c>
     </row>
@@ -52594,27 +52594,27 @@
       </c>
       <c r="D858" s="2" t="inlineStr">
         <is>
-          <t>Jardins et paysages façonnés</t>
+          <t>Haies, lisières et fourrés</t>
         </is>
       </c>
       <c r="E858" s="2" t="inlineStr">
         <is>
-          <t>Jardins, parcs et plantes ornementales</t>
+          <t>Haies et lignes d'arbres</t>
         </is>
       </c>
       <c r="F858" s="2" t="inlineStr">
         <is>
-          <t>HAB-01</t>
+          <t>LIS-01</t>
         </is>
       </c>
       <c r="G858" s="2" t="inlineStr">
         <is>
-          <t>cultivé ou planté</t>
+          <t>naturel</t>
         </is>
       </c>
       <c r="H858" s="2" t="inlineStr">
         <is>
-          <t>possible</t>
+          <t>typique</t>
         </is>
       </c>
       <c r="I858" s="2" t="inlineStr">
@@ -52624,7 +52624,7 @@
       </c>
       <c r="J858" s="3" t="inlineStr">
         <is>
-          <t>Se rencontre plus souvent planté près des habitations.</t>
+          <t>Haies et bois, surtout calcaires, principalement dans le Midi, le Centre et l'Ouest, et en Corse.</t>
         </is>
       </c>
       <c r="K858" s="2" t="inlineStr">
@@ -52641,12 +52641,12 @@
     <row r="859">
       <c r="A859" s="2" t="inlineStr">
         <is>
-          <t>Sorbus torminalis</t>
+          <t>Sorbus domestica</t>
         </is>
       </c>
       <c r="B859" s="2" t="inlineStr">
         <is>
-          <t>Alisier torminal</t>
+          <t>Cormier</t>
         </is>
       </c>
       <c r="C859" s="2" t="inlineStr">
@@ -52676,7 +52676,7 @@
       </c>
       <c r="H859" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I859" s="2" t="inlineStr">
@@ -52686,29 +52686,29 @@
       </c>
       <c r="J859" s="3" t="inlineStr">
         <is>
-          <t>Bois des plaines et des basses montagnes, dans presque toute la France, rare dans la région méditerranéenne.</t>
+          <t>Rare à l'état spontané dans les chênaies pubescentes en Lozère.</t>
         </is>
       </c>
       <c r="K859" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-65340-synthese</t>
+          <t>https://www.tela-botanica.org/eflore/?action=fiche&amp;module=fiche&amp;niveau=2&amp;num_nom=65300&amp;onglet=description&amp;referentiel=bdtfx</t>
         </is>
       </c>
       <c r="L859" s="3" t="inlineStr">
         <is>
-          <t>rare dans la région méditerranéenne</t>
+          <t>rare à l'état spontané - souvent planté près des habitations</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" s="2" t="inlineStr">
         <is>
-          <t>Sorbus torminalis</t>
+          <t>Sorbus domestica</t>
         </is>
       </c>
       <c r="B860" s="2" t="inlineStr">
         <is>
-          <t>Alisier torminal</t>
+          <t>Cormier</t>
         </is>
       </c>
       <c r="C860" s="2" t="inlineStr">
@@ -52718,27 +52718,27 @@
       </c>
       <c r="D860" s="2" t="inlineStr">
         <is>
-          <t>Haies, lisières et fourrés</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E860" s="2" t="inlineStr">
         <is>
-          <t>Lisières et clairières herbacées</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F860" s="2" t="inlineStr">
         <is>
-          <t>LIS-02</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G860" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H860" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>possible</t>
         </is>
       </c>
       <c r="I860" s="2" t="inlineStr">
@@ -52748,34 +52748,34 @@
       </c>
       <c r="J860" s="3" t="inlineStr">
         <is>
-          <t>Certaines lisières thermophiles à Alisier torminal et hybride de Chêne pubescent.</t>
+          <t>Se rencontre plus souvent planté près des habitations.</t>
         </is>
       </c>
       <c r="K860" s="2" t="inlineStr">
         <is>
-          <t>https://inpn.mnhn.fr/zone/znieff/220013965/tab/commentaires</t>
+          <t>https://www.tela-botanica.org/eflore/?action=fiche&amp;module=fiche&amp;niveau=2&amp;num_nom=65300&amp;onglet=description&amp;referentiel=bdtfx</t>
         </is>
       </c>
       <c r="L860" s="3" t="inlineStr">
         <is>
-          <t>rare dans la région méditerranéenne</t>
+          <t>rare à l'état spontané - souvent planté près des habitations</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" s="2" t="inlineStr">
         <is>
-          <t>Sorghastrum nutans</t>
+          <t>Sorbus intermedia</t>
         </is>
       </c>
       <c r="B861" s="2" t="inlineStr">
         <is>
-          <t>Sorghastre penché</t>
+          <t>Alisier de Suède</t>
         </is>
       </c>
       <c r="C861" s="2" t="inlineStr">
         <is>
-          <t>exotique (cultivée en France)</t>
+          <t>à vérifier</t>
         </is>
       </c>
       <c r="D861" s="2" t="inlineStr">
@@ -52810,29 +52810,29 @@
       </c>
       <c r="J861" s="3" t="inlineStr">
         <is>
-          <t>Espèce exotique (origine : Amérique du Nord (centre et est)), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+          <t>Il est planté comme arbre d'ornement dans les parcs et les jardins dans une grande partie de l'Europe et souvent utilisé comme arbre d'alignement dans les rues.</t>
         </is>
       </c>
       <c r="K861" s="2" t="inlineStr">
         <is>
-          <t>https://plants.ces.ncsu.edu/plants/sorghastrum-nutans</t>
+          <t>https://fr.wikipedia.org/wiki/Scandosorbus_intermedia</t>
         </is>
       </c>
       <c r="L861" s="3" t="inlineStr">
         <is>
-          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+          <t>statut en France non précisé par le texte - milieu d'origine non renseigné (règle R10)</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" s="2" t="inlineStr">
         <is>
-          <t>Spartium junceum</t>
+          <t>Sorbus torminalis</t>
         </is>
       </c>
       <c r="B862" s="2" t="inlineStr">
         <is>
-          <t>Spartier à tiges de jonc</t>
+          <t>Alisier torminal</t>
         </is>
       </c>
       <c r="C862" s="2" t="inlineStr">
@@ -52842,17 +52842,17 @@
       </c>
       <c r="D862" s="2" t="inlineStr">
         <is>
-          <t>Landes, bruyères et fourrés méditerranéens</t>
+          <t>Forêts et sous-bois</t>
         </is>
       </c>
       <c r="E862" s="2" t="inlineStr">
         <is>
-          <t>Maquis et fourrés méditerranéens</t>
+          <t>Forêts de feuillus caducs</t>
         </is>
       </c>
       <c r="F862" s="2" t="inlineStr">
         <is>
-          <t>LAN-02</t>
+          <t>FOR-01</t>
         </is>
       </c>
       <c r="G862" s="2" t="inlineStr">
@@ -52872,25 +52872,29 @@
       </c>
       <c r="J862" s="3" t="inlineStr">
         <is>
-          <t>Espèce dominante des fourrés à Spartium junceum (EUNIS S5-3).</t>
+          <t>Bois des plaines et des basses montagnes, dans presque toute la France, rare dans la région méditerranéenne.</t>
         </is>
       </c>
       <c r="K862" s="2" t="inlineStr">
         <is>
-          <t>https://inpn.mnhn.fr/espece/cd_nom/124453/tab/habitats</t>
-        </is>
-      </c>
-      <c r="L862" s="3" t="inlineStr"/>
+          <t>https://www.tela-botanica.org/bdtfx-nn-65340-synthese</t>
+        </is>
+      </c>
+      <c r="L862" s="3" t="inlineStr">
+        <is>
+          <t>rare dans la région méditerranéenne</t>
+        </is>
+      </c>
     </row>
     <row r="863">
       <c r="A863" s="2" t="inlineStr">
         <is>
-          <t>Spartium junceum</t>
+          <t>Sorbus torminalis</t>
         </is>
       </c>
       <c r="B863" s="2" t="inlineStr">
         <is>
-          <t>Spartier à tiges de jonc</t>
+          <t>Alisier torminal</t>
         </is>
       </c>
       <c r="C863" s="2" t="inlineStr">
@@ -52900,17 +52904,17 @@
       </c>
       <c r="D863" s="2" t="inlineStr">
         <is>
-          <t>Prairies et pelouses</t>
+          <t>Haies, lisières et fourrés</t>
         </is>
       </c>
       <c r="E863" s="2" t="inlineStr">
         <is>
-          <t>Pelouses et prairies sèches</t>
+          <t>Lisières et clairières herbacées</t>
         </is>
       </c>
       <c r="F863" s="2" t="inlineStr">
         <is>
-          <t>PRA-01</t>
+          <t>LIS-02</t>
         </is>
       </c>
       <c r="G863" s="2" t="inlineStr">
@@ -52930,30 +52934,34 @@
       </c>
       <c r="J863" s="3" t="inlineStr">
         <is>
-          <t>Écologie : coteaux arides de tout le Midi, jusque dans le Rhône, le Lot et la Dordogne ; Corse.</t>
+          <t>Certaines lisières thermophiles à Alisier torminal et hybride de Chêne pubescent.</t>
         </is>
       </c>
       <c r="K863" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-65481</t>
-        </is>
-      </c>
-      <c r="L863" s="3" t="inlineStr"/>
+          <t>https://inpn.mnhn.fr/zone/znieff/220013965/tab/commentaires</t>
+        </is>
+      </c>
+      <c r="L863" s="3" t="inlineStr">
+        <is>
+          <t>rare dans la région méditerranéenne</t>
+        </is>
+      </c>
     </row>
     <row r="864">
       <c r="A864" s="2" t="inlineStr">
         <is>
-          <t>Spartium junceum</t>
+          <t>Sorghastrum nutans</t>
         </is>
       </c>
       <c r="B864" s="2" t="inlineStr">
         <is>
-          <t>Spartier à tiges de jonc</t>
+          <t>Sorghastre penché</t>
         </is>
       </c>
       <c r="C864" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>exotique (cultivée en France)</t>
         </is>
       </c>
       <c r="D864" s="2" t="inlineStr">
@@ -52963,22 +52971,22 @@
       </c>
       <c r="E864" s="2" t="inlineStr">
         <is>
-          <t>Murs, friches et espaces très artificialisés</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F864" s="2" t="inlineStr">
         <is>
-          <t>HAB-03</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G864" s="2" t="inlineStr">
         <is>
-          <t>spontané (milieu secondaire)</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H864" s="2" t="inlineStr">
         <is>
-          <t>possible</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I864" s="2" t="inlineStr">
@@ -52988,55 +52996,59 @@
       </c>
       <c r="J864" s="3" t="inlineStr">
         <is>
-          <t>Colonise les friches et espaces ouverts, en particulier le long des routes et autoroutes.</t>
+          <t>Espèce exotique (origine : Amérique du Nord (centre et est)), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
         </is>
       </c>
       <c r="K864" s="2" t="inlineStr">
         <is>
-          <t>https://inpn.mnhn.fr/espece/cd_nom/124453/tab/habitats</t>
-        </is>
-      </c>
-      <c r="L864" s="3" t="inlineStr"/>
+          <t>https://plants.ces.ncsu.edu/plants/sorghastrum-nutans</t>
+        </is>
+      </c>
+      <c r="L864" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+        </is>
+      </c>
     </row>
     <row r="865">
       <c r="A865" s="2" t="inlineStr">
         <is>
-          <t>Sporobolus heterolepis</t>
+          <t>Spartium junceum</t>
         </is>
       </c>
       <c r="B865" s="2" t="inlineStr">
         <is>
-          <t>Sporobole</t>
+          <t>Spartier à tiges de jonc</t>
         </is>
       </c>
       <c r="C865" s="2" t="inlineStr">
         <is>
-          <t>exotique (cultivée en France)</t>
+          <t>indigène</t>
         </is>
       </c>
       <c r="D865" s="2" t="inlineStr">
         <is>
-          <t>Jardins et paysages façonnés</t>
+          <t>Landes, bruyères et fourrés méditerranéens</t>
         </is>
       </c>
       <c r="E865" s="2" t="inlineStr">
         <is>
-          <t>Jardins, parcs et plantes ornementales</t>
+          <t>Maquis et fourrés méditerranéens</t>
         </is>
       </c>
       <c r="F865" s="2" t="inlineStr">
         <is>
-          <t>HAB-01</t>
+          <t>LAN-02</t>
         </is>
       </c>
       <c r="G865" s="2" t="inlineStr">
         <is>
-          <t>cultivé ou planté</t>
+          <t>naturel</t>
         </is>
       </c>
       <c r="H865" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>typique</t>
         </is>
       </c>
       <c r="I865" s="2" t="inlineStr">
@@ -53046,54 +53058,50 @@
       </c>
       <c r="J865" s="3" t="inlineStr">
         <is>
-          <t>Espèce exotique (origine : Amérique du Nord (centre et est)), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+          <t>Espèce dominante des fourrés à Spartium junceum (EUNIS S5-3).</t>
         </is>
       </c>
       <c r="K865" s="2" t="inlineStr">
         <is>
-          <t>https://mdc.mo.gov/discover-nature/field-guide/prairie-dropseed</t>
-        </is>
-      </c>
-      <c r="L865" s="3" t="inlineStr">
-        <is>
-          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
-        </is>
-      </c>
+          <t>https://inpn.mnhn.fr/espece/cd_nom/124453/tab/habitats</t>
+        </is>
+      </c>
+      <c r="L865" s="3" t="inlineStr"/>
     </row>
     <row r="866">
       <c r="A866" s="2" t="inlineStr">
         <is>
-          <t>Stachys byzantina</t>
+          <t>Spartium junceum</t>
         </is>
       </c>
       <c r="B866" s="2" t="inlineStr">
         <is>
-          <t>Épiaire laineuse</t>
+          <t>Spartier à tiges de jonc</t>
         </is>
       </c>
       <c r="C866" s="2" t="inlineStr">
         <is>
-          <t>exotique (cultivée en France)</t>
+          <t>indigène</t>
         </is>
       </c>
       <c r="D866" s="2" t="inlineStr">
         <is>
-          <t>Jardins et paysages façonnés</t>
+          <t>Prairies et pelouses</t>
         </is>
       </c>
       <c r="E866" s="2" t="inlineStr">
         <is>
-          <t>Jardins, parcs et plantes ornementales</t>
+          <t>Pelouses et prairies sèches</t>
         </is>
       </c>
       <c r="F866" s="2" t="inlineStr">
         <is>
-          <t>HAB-01</t>
+          <t>PRA-01</t>
         </is>
       </c>
       <c r="G866" s="2" t="inlineStr">
         <is>
-          <t>cultivé ou planté</t>
+          <t>naturel</t>
         </is>
       </c>
       <c r="H866" s="2" t="inlineStr">
@@ -53108,29 +53116,25 @@
       </c>
       <c r="J866" s="3" t="inlineStr">
         <is>
-          <t>Espèce exotique (origine : Caucase à l'Iran), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+          <t>Écologie : coteaux arides de tout le Midi, jusque dans le Rhône, le Lot et la Dordogne ; Corse.</t>
         </is>
       </c>
       <c r="K866" s="2" t="inlineStr">
         <is>
-          <t>https://www.rhs.org.uk/plants/17707/Stachys-byzantina/Details</t>
-        </is>
-      </c>
-      <c r="L866" s="3" t="inlineStr">
-        <is>
-          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
-        </is>
-      </c>
+          <t>https://www.tela-botanica.org/bdtfx-nn-65481</t>
+        </is>
+      </c>
+      <c r="L866" s="3" t="inlineStr"/>
     </row>
     <row r="867">
       <c r="A867" s="2" t="inlineStr">
         <is>
-          <t>Staphylea pinnata</t>
+          <t>Spartium junceum</t>
         </is>
       </c>
       <c r="B867" s="2" t="inlineStr">
         <is>
-          <t>Faux-pistachier</t>
+          <t>Spartier à tiges de jonc</t>
         </is>
       </c>
       <c r="C867" s="2" t="inlineStr">
@@ -53140,27 +53144,27 @@
       </c>
       <c r="D867" s="2" t="inlineStr">
         <is>
-          <t>Forêts et sous-bois</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E867" s="2" t="inlineStr">
         <is>
-          <t>Forêts de feuillus caducs</t>
+          <t>Murs, friches et espaces très artificialisés</t>
         </is>
       </c>
       <c r="F867" s="2" t="inlineStr">
         <is>
-          <t>FOR-01</t>
+          <t>HAB-03</t>
         </is>
       </c>
       <c r="G867" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>spontané (milieu secondaire)</t>
         </is>
       </c>
       <c r="H867" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>possible</t>
         </is>
       </c>
       <c r="I867" s="2" t="inlineStr">
@@ -53170,34 +53174,30 @@
       </c>
       <c r="J867" s="3" t="inlineStr">
         <is>
-          <t>Écologie : bois de l'Alsace et du Jura septentrional (environs de Montbéliard).</t>
+          <t>Colonise les friches et espaces ouverts, en particulier le long des routes et autoroutes.</t>
         </is>
       </c>
       <c r="K867" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-65985</t>
-        </is>
-      </c>
-      <c r="L867" s="3" t="inlineStr">
-        <is>
-          <t>indigène seulement en Alsace et dans le Jura septentrional</t>
-        </is>
-      </c>
+          <t>https://inpn.mnhn.fr/espece/cd_nom/124453/tab/habitats</t>
+        </is>
+      </c>
+      <c r="L867" s="3" t="inlineStr"/>
     </row>
     <row r="868">
       <c r="A868" s="2" t="inlineStr">
         <is>
-          <t>Staphylea pinnata</t>
+          <t>Spiraea japonica</t>
         </is>
       </c>
       <c r="B868" s="2" t="inlineStr">
         <is>
-          <t>Faux-pistachier</t>
+          <t>Spirée du Japon</t>
         </is>
       </c>
       <c r="C868" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>à vérifier</t>
         </is>
       </c>
       <c r="D868" s="2" t="inlineStr">
@@ -53232,59 +53232,59 @@
       </c>
       <c r="J868" s="3" t="inlineStr">
         <is>
-          <t>Fréquemment planté dans les jardins et les parcs.</t>
+          <t>Elle a été introduite en Europe et en Amérique du Nord comme plante ornementale et y est maintenant considérée comme envahissante.</t>
         </is>
       </c>
       <c r="K868" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-65985</t>
+          <t>https://fr.wikipedia.org/wiki/Spiraea_japonica</t>
         </is>
       </c>
       <c r="L868" s="3" t="inlineStr">
         <is>
-          <t>indigène seulement en Alsace et dans le Jura septentrional</t>
+          <t>introduite en Europe comme ornementale et envahissante, France non citée - habitats décrits sans localisation</t>
         </is>
       </c>
     </row>
     <row r="869">
       <c r="A869" s="2" t="inlineStr">
         <is>
-          <t>Stephanandra incisa</t>
+          <t>Spiraea japonica</t>
         </is>
       </c>
       <c r="B869" s="2" t="inlineStr">
         <is>
-          <t>Stéphanandra</t>
+          <t>Spirée du Japon</t>
         </is>
       </c>
       <c r="C869" s="2" t="inlineStr">
         <is>
-          <t>exotique (cultivée en France)</t>
+          <t>à vérifier</t>
         </is>
       </c>
       <c r="D869" s="2" t="inlineStr">
         <is>
-          <t>Jardins et paysages façonnés</t>
+          <t>Mares, rivières et berges</t>
         </is>
       </c>
       <c r="E869" s="2" t="inlineStr">
         <is>
-          <t>Jardins, parcs et plantes ornementales</t>
+          <t>Berges et zones littorales d'eau douce</t>
         </is>
       </c>
       <c r="F869" s="2" t="inlineStr">
         <is>
-          <t>HAB-01</t>
+          <t>EAU-03</t>
         </is>
       </c>
       <c r="G869" s="2" t="inlineStr">
         <is>
-          <t>cultivé ou planté</t>
+          <t>spontané (milieu secondaire)</t>
         </is>
       </c>
       <c r="H869" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>possible</t>
         </is>
       </c>
       <c r="I869" s="2" t="inlineStr">
@@ -53294,59 +53294,59 @@
       </c>
       <c r="J869" s="3" t="inlineStr">
         <is>
-          <t>Espèce exotique (origine : Japon, Corée), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+          <t>On la trouve souvent le long des ruisseaux, dans les tourbières, en bordure de forêt ou dans les clairières.</t>
         </is>
       </c>
       <c r="K869" s="2" t="inlineStr">
         <is>
-          <t>https://www.rhs.org.uk/plants/43659/stephanandra-incisa-prostrata/details</t>
+          <t>https://fr.wikipedia.org/wiki/Spiraea_japonica</t>
         </is>
       </c>
       <c r="L869" s="3" t="inlineStr">
         <is>
-          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+          <t>introduite en Europe comme ornementale et envahissante, France non citée - habitats décrits sans localisation</t>
         </is>
       </c>
     </row>
     <row r="870">
       <c r="A870" s="2" t="inlineStr">
         <is>
-          <t>Symphyotrichum novi-belgii</t>
+          <t>Sporobolus heterolepis</t>
         </is>
       </c>
       <c r="B870" s="2" t="inlineStr">
         <is>
-          <t>Aster de Nouvelle-Belgique</t>
+          <t>Sporobole</t>
         </is>
       </c>
       <c r="C870" s="2" t="inlineStr">
         <is>
-          <t>naturalisée</t>
+          <t>exotique (cultivée en France)</t>
         </is>
       </c>
       <c r="D870" s="2" t="inlineStr">
         <is>
-          <t>Mares, rivières et berges</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E870" s="2" t="inlineStr">
         <is>
-          <t>Berges et zones littorales d'eau douce</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F870" s="2" t="inlineStr">
         <is>
-          <t>EAU-03</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G870" s="2" t="inlineStr">
         <is>
-          <t>spontané (milieu secondaire)</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H870" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I870" s="2" t="inlineStr">
@@ -53356,59 +53356,59 @@
       </c>
       <c r="J870" s="3" t="inlineStr">
         <is>
-          <t>Originaire d'Amérique du Nord, naturalisé au bord des rivières : Alsace, Jura, Doubs, vallées de la Saône, du Rhône.</t>
+          <t>Espèce exotique (origine : Amérique du Nord (centre et est)), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
         </is>
       </c>
       <c r="K870" s="2" t="inlineStr">
         <is>
-          <t>https://tela-botanica.org/eflore/?action=fiche&amp;module=fiche&amp;num_nom=7821&amp;onglet=synthese&amp;referentiel=bdtfx</t>
+          <t>https://mdc.mo.gov/discover-nature/field-guide/prairie-dropseed</t>
         </is>
       </c>
       <c r="L870" s="3" t="inlineStr">
         <is>
-          <t>originaire d'Amérique du Nord, écologie donnée par Coste pour la var. laevigatus</t>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
         </is>
       </c>
     </row>
     <row r="871">
       <c r="A871" s="2" t="inlineStr">
         <is>
-          <t>Symphytum officinale</t>
+          <t>Stachys byzantina</t>
         </is>
       </c>
       <c r="B871" s="2" t="inlineStr">
         <is>
-          <t>Consoude officinale</t>
+          <t>Épiaire laineuse</t>
         </is>
       </c>
       <c r="C871" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>exotique (cultivée en France)</t>
         </is>
       </c>
       <c r="D871" s="2" t="inlineStr">
         <is>
-          <t>Prairies et pelouses</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E871" s="2" t="inlineStr">
         <is>
-          <t>Prairies humides</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F871" s="2" t="inlineStr">
         <is>
-          <t>PRA-03</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G871" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H871" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I871" s="2" t="inlineStr">
@@ -53418,25 +53418,29 @@
       </c>
       <c r="J871" s="3" t="inlineStr">
         <is>
-          <t>Écologie : prés humides, fossés, bords des eaux, dans presque toute la France.</t>
+          <t>Espèce exotique (origine : Caucase à l'Iran), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
         </is>
       </c>
       <c r="K871" s="2" t="inlineStr">
         <is>
-          <t>https://tela-botanica.org/eflore/?action=fiche&amp;module=fiche&amp;num_nom=75402&amp;onglet=description&amp;referentiel=bdtfx</t>
-        </is>
-      </c>
-      <c r="L871" s="3" t="inlineStr"/>
+          <t>https://www.rhs.org.uk/plants/17707/Stachys-byzantina/Details</t>
+        </is>
+      </c>
+      <c r="L871" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+        </is>
+      </c>
     </row>
     <row r="872">
       <c r="A872" s="2" t="inlineStr">
         <is>
-          <t>Symphytum officinale</t>
+          <t>Staphylea pinnata</t>
         </is>
       </c>
       <c r="B872" s="2" t="inlineStr">
         <is>
-          <t>Consoude officinale</t>
+          <t>Faux-pistachier</t>
         </is>
       </c>
       <c r="C872" s="2" t="inlineStr">
@@ -53446,17 +53450,17 @@
       </c>
       <c r="D872" s="2" t="inlineStr">
         <is>
-          <t>Mares, rivières et berges</t>
+          <t>Forêts et sous-bois</t>
         </is>
       </c>
       <c r="E872" s="2" t="inlineStr">
         <is>
-          <t>Berges et zones littorales d'eau douce</t>
+          <t>Forêts de feuillus caducs</t>
         </is>
       </c>
       <c r="F872" s="2" t="inlineStr">
         <is>
-          <t>EAU-03</t>
+          <t>FOR-01</t>
         </is>
       </c>
       <c r="G872" s="2" t="inlineStr">
@@ -53466,7 +53470,7 @@
       </c>
       <c r="H872" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>typique</t>
         </is>
       </c>
       <c r="I872" s="2" t="inlineStr">
@@ -53476,25 +53480,29 @@
       </c>
       <c r="J872" s="3" t="inlineStr">
         <is>
-          <t>Prés humides, fossés, bords des eaux.</t>
+          <t>Écologie : bois de l'Alsace et du Jura septentrional (environs de Montbéliard).</t>
         </is>
       </c>
       <c r="K872" s="2" t="inlineStr">
         <is>
-          <t>https://tela-botanica.org/eflore/?action=fiche&amp;module=fiche&amp;num_nom=75402&amp;onglet=description&amp;referentiel=bdtfx</t>
-        </is>
-      </c>
-      <c r="L872" s="3" t="inlineStr"/>
+          <t>https://www.tela-botanica.org/bdtfx-nn-65985</t>
+        </is>
+      </c>
+      <c r="L872" s="3" t="inlineStr">
+        <is>
+          <t>indigène seulement en Alsace et dans le Jura septentrional</t>
+        </is>
+      </c>
     </row>
     <row r="873">
       <c r="A873" s="2" t="inlineStr">
         <is>
-          <t>Symphytum officinale</t>
+          <t>Staphylea pinnata</t>
         </is>
       </c>
       <c r="B873" s="2" t="inlineStr">
         <is>
-          <t>Consoude officinale</t>
+          <t>Faux-pistachier</t>
         </is>
       </c>
       <c r="C873" s="2" t="inlineStr">
@@ -53504,27 +53512,27 @@
       </c>
       <c r="D873" s="2" t="inlineStr">
         <is>
-          <t>Marais, prairies humides et tourbières</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E873" s="2" t="inlineStr">
         <is>
-          <t>Prairies inondables ou longuement humides</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F873" s="2" t="inlineStr">
         <is>
-          <t>HUM-03</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G873" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H873" s="2" t="inlineStr">
         <is>
-          <t>possible</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I873" s="2" t="inlineStr">
@@ -53534,55 +53542,59 @@
       </c>
       <c r="J873" s="3" t="inlineStr">
         <is>
-          <t>Pousse sur des sols humides au moins l'hiver et riches en matières organiques se décomposant mal.</t>
+          <t>Fréquemment planté dans les jardins et les parcs.</t>
         </is>
       </c>
       <c r="K873" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/2017/08/article8229/</t>
-        </is>
-      </c>
-      <c r="L873" s="3" t="inlineStr"/>
+          <t>https://www.tela-botanica.org/bdtfx-nn-65985</t>
+        </is>
+      </c>
+      <c r="L873" s="3" t="inlineStr">
+        <is>
+          <t>indigène seulement en Alsace et dans le Jura septentrional</t>
+        </is>
+      </c>
     </row>
     <row r="874">
       <c r="A874" s="2" t="inlineStr">
         <is>
-          <t>Tamarix gallica</t>
+          <t>Stephanandra incisa</t>
         </is>
       </c>
       <c r="B874" s="2" t="inlineStr">
         <is>
-          <t>Tamaris de France</t>
+          <t>Stéphanandra</t>
         </is>
       </c>
       <c r="C874" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>exotique (cultivée en France)</t>
         </is>
       </c>
       <c r="D874" s="2" t="inlineStr">
         <is>
-          <t>Mares, rivières et berges</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E874" s="2" t="inlineStr">
         <is>
-          <t>Berges et zones littorales d'eau douce</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F874" s="2" t="inlineStr">
         <is>
-          <t>EAU-03</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G874" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H874" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I874" s="2" t="inlineStr">
@@ -53592,50 +53604,54 @@
       </c>
       <c r="J874" s="3" t="inlineStr">
         <is>
-          <t>F9.313 « Fourrés méditerranéo-macaronésiens à Tamaris » : berges, zones humides et localités côtières du bassin méditerranéen.</t>
+          <t>Espèce exotique (origine : Japon, Corée), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
         </is>
       </c>
       <c r="K874" s="2" t="inlineStr">
         <is>
-          <t>https://inpn.mnhn.fr/habitat/cd_hab/11627/tab/description</t>
-        </is>
-      </c>
-      <c r="L874" s="3" t="inlineStr"/>
+          <t>https://www.rhs.org.uk/plants/43659/stephanandra-incisa-prostrata/details</t>
+        </is>
+      </c>
+      <c r="L874" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+        </is>
+      </c>
     </row>
     <row r="875">
       <c r="A875" s="2" t="inlineStr">
         <is>
-          <t>Tamarix gallica</t>
+          <t>Stipa gigantea</t>
         </is>
       </c>
       <c r="B875" s="2" t="inlineStr">
         <is>
-          <t>Tamaris de France</t>
+          <t>Stipe géante</t>
         </is>
       </c>
       <c r="C875" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>exotique (cultivée en France)</t>
         </is>
       </c>
       <c r="D875" s="2" t="inlineStr">
         <is>
-          <t>Littoral, dunes et rivages salés</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E875" s="2" t="inlineStr">
         <is>
-          <t>Prés salés et végétation de transition côtière</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F875" s="2" t="inlineStr">
         <is>
-          <t>LIT-04</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G875" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H875" s="2" t="inlineStr">
@@ -53650,25 +53666,29 @@
       </c>
       <c r="J875" s="3" t="inlineStr">
         <is>
-          <t>Côtes de l'Océan et de la Manche ; fourrés d'arbrisseaux hydrophiles et subhalophiles (Tamaricion africanae).</t>
+          <t>Stipa gigantea est cultivée comme plante ornementale soit en touffe isolée, soit en masse dans les jardins particuliers ou dans les parcs publics.</t>
         </is>
       </c>
       <c r="K875" s="2" t="inlineStr">
         <is>
-          <t>https://tela-botanica.org/eflore/?action=fiche&amp;module=fiche&amp;niveau=3&amp;num_nom=66702&amp;onglet=synthese&amp;referentiel=bdtfx</t>
-        </is>
-      </c>
-      <c r="L875" s="3" t="inlineStr"/>
+          <t>https://fr.wikipedia.org/wiki/Stipa_gigantea</t>
+        </is>
+      </c>
+      <c r="L875" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+        </is>
+      </c>
     </row>
     <row r="876">
       <c r="A876" s="2" t="inlineStr">
         <is>
-          <t>Taxodium distichum</t>
+          <t>Strelitzia reginae</t>
         </is>
       </c>
       <c r="B876" s="2" t="inlineStr">
         <is>
-          <t>Cyprès chauve</t>
+          <t>Oiseau de paradis</t>
         </is>
       </c>
       <c r="C876" s="2" t="inlineStr">
@@ -53708,12 +53728,12 @@
       </c>
       <c r="J876" s="3" t="inlineStr">
         <is>
-          <t>Espèce exotique (origine : Sud-Est des États-Unis), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+          <t>Excepté dans les zones non gélives, l'oiseau de paradis doit être cultivé en bac et hiverner dans une véranda.</t>
         </is>
       </c>
       <c r="K876" s="2" t="inlineStr">
         <is>
-          <t>https://www.rhs.org.uk/plants/17999/taxodium-distichum-swamp-cypress-bald-cypress/details</t>
+          <t>https://fr.wikipedia.org/wiki/Strelitzia_reginae</t>
         </is>
       </c>
       <c r="L876" s="3" t="inlineStr">
@@ -53725,42 +53745,42 @@
     <row r="877">
       <c r="A877" s="2" t="inlineStr">
         <is>
-          <t>Taxus baccata</t>
+          <t>Symphoricarpos albus</t>
         </is>
       </c>
       <c r="B877" s="2" t="inlineStr">
         <is>
-          <t>If commun</t>
+          <t>Symphorine</t>
         </is>
       </c>
       <c r="C877" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>naturalisée</t>
         </is>
       </c>
       <c r="D877" s="2" t="inlineStr">
         <is>
-          <t>Forêts et sous-bois</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E877" s="2" t="inlineStr">
         <is>
-          <t>Forêts de feuillus caducs</t>
+          <t>Murs, friches et espaces très artificialisés</t>
         </is>
       </c>
       <c r="F877" s="2" t="inlineStr">
         <is>
-          <t>FOR-01</t>
+          <t>HAB-03</t>
         </is>
       </c>
       <c r="G877" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>spontané (milieu secondaire)</t>
         </is>
       </c>
       <c r="H877" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>typique</t>
         </is>
       </c>
       <c r="I877" s="2" t="inlineStr">
@@ -53770,55 +53790,59 @@
       </c>
       <c r="J877" s="3" t="inlineStr">
         <is>
-          <t>Écologie : rochers et bois des montagnes (Vosges, Jura, Alpes, Cévennes, Pyrénées, Corse).</t>
+          <t>Elle affectionne les rocailles, le long des chemins et des voies ferrées, souvent à proximité des habitations où elle forme des haies naturelles.</t>
         </is>
       </c>
       <c r="K877" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-67146</t>
-        </is>
-      </c>
-      <c r="L877" s="3" t="inlineStr"/>
+          <t>https://fr.wikipedia.org/wiki/Symphorine_blanche</t>
+        </is>
+      </c>
+      <c r="L877" s="3" t="inlineStr">
+        <is>
+          <t>naturalisation décrite pour l'Europe occidentale</t>
+        </is>
+      </c>
     </row>
     <row r="878">
       <c r="A878" s="2" t="inlineStr">
         <is>
-          <t>Taxus baccata</t>
+          <t>Symphoricarpos albus</t>
         </is>
       </c>
       <c r="B878" s="2" t="inlineStr">
         <is>
-          <t>If commun</t>
+          <t>Symphorine</t>
         </is>
       </c>
       <c r="C878" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>naturalisée</t>
         </is>
       </c>
       <c r="D878" s="2" t="inlineStr">
         <is>
-          <t>Rochers, éboulis et sols superficiels</t>
+          <t>Mares, rivières et berges</t>
         </is>
       </c>
       <c r="E878" s="2" t="inlineStr">
         <is>
-          <t>Falaises intérieures et dalles rocheuses</t>
+          <t>Berges et zones littorales d'eau douce</t>
         </is>
       </c>
       <c r="F878" s="2" t="inlineStr">
         <is>
-          <t>ROC-02</t>
+          <t>EAU-03</t>
         </is>
       </c>
       <c r="G878" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>spontané (milieu secondaire)</t>
         </is>
       </c>
       <c r="H878" s="2" t="inlineStr">
         <is>
-          <t>possible</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I878" s="2" t="inlineStr">
@@ -53828,55 +53852,59 @@
       </c>
       <c r="J878" s="3" t="inlineStr">
         <is>
-          <t>Écologie : rochers et bois des montagnes.</t>
+          <t>Elle affectionne les sols calcaires, les rocailles et les bords des rivières.</t>
         </is>
       </c>
       <c r="K878" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-67146</t>
-        </is>
-      </c>
-      <c r="L878" s="3" t="inlineStr"/>
+          <t>https://fr.wikipedia.org/wiki/Symphorine_blanche</t>
+        </is>
+      </c>
+      <c r="L878" s="3" t="inlineStr">
+        <is>
+          <t>naturalisation décrite pour l'Europe occidentale</t>
+        </is>
+      </c>
     </row>
     <row r="879">
       <c r="A879" s="2" t="inlineStr">
         <is>
-          <t>Taxus baccata</t>
+          <t>Symphoricarpos albus</t>
         </is>
       </c>
       <c r="B879" s="2" t="inlineStr">
         <is>
-          <t>If commun</t>
+          <t>Symphorine</t>
         </is>
       </c>
       <c r="C879" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>naturalisée</t>
         </is>
       </c>
       <c r="D879" s="2" t="inlineStr">
         <is>
-          <t>Forêts et sous-bois</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E879" s="2" t="inlineStr">
         <is>
-          <t>Boisements de feuillus sempervirents</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F879" s="2" t="inlineStr">
         <is>
-          <t>FOR-02</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G879" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H879" s="2" t="inlineStr">
         <is>
-          <t>possible</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I879" s="2" t="inlineStr">
@@ -53886,55 +53914,59 @@
       </c>
       <c r="J879" s="3" t="inlineStr">
         <is>
-          <t>Habitat 9580 « Bois méditerranéens à Taxus baccata » (Cahiers d'habitats).</t>
+          <t>Elle forme des haies naturelles ou plantées à des fins ornementales.</t>
         </is>
       </c>
       <c r="K879" s="2" t="inlineStr">
         <is>
-          <t>https://inpn.mnhn.fr/habitat/cd_hab/1163</t>
-        </is>
-      </c>
-      <c r="L879" s="3" t="inlineStr"/>
+          <t>https://fr.wikipedia.org/wiki/Symphorine_blanche</t>
+        </is>
+      </c>
+      <c r="L879" s="3" t="inlineStr">
+        <is>
+          <t>naturalisation décrite pour l'Europe occidentale</t>
+        </is>
+      </c>
     </row>
     <row r="880">
       <c r="A880" s="2" t="inlineStr">
         <is>
-          <t>Taxus baccata</t>
+          <t>Symphyotrichum novi-belgii</t>
         </is>
       </c>
       <c r="B880" s="2" t="inlineStr">
         <is>
-          <t>If commun</t>
+          <t>Aster de Nouvelle-Belgique</t>
         </is>
       </c>
       <c r="C880" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>naturalisée</t>
         </is>
       </c>
       <c r="D880" s="2" t="inlineStr">
         <is>
-          <t>Jardins et paysages façonnés</t>
+          <t>Mares, rivières et berges</t>
         </is>
       </c>
       <c r="E880" s="2" t="inlineStr">
         <is>
-          <t>Jardins, parcs et plantes ornementales</t>
+          <t>Berges et zones littorales d'eau douce</t>
         </is>
       </c>
       <c r="F880" s="2" t="inlineStr">
         <is>
-          <t>HAB-01</t>
+          <t>EAU-03</t>
         </is>
       </c>
       <c r="G880" s="2" t="inlineStr">
         <is>
-          <t>cultivé ou planté</t>
+          <t>spontané (milieu secondaire)</t>
         </is>
       </c>
       <c r="H880" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>typique</t>
         </is>
       </c>
       <c r="I880" s="2" t="inlineStr">
@@ -53944,55 +53976,59 @@
       </c>
       <c r="J880" s="3" t="inlineStr">
         <is>
-          <t>Hors de son aire spontanée, surtout planté dans les parcs et les cimetières.</t>
+          <t>Originaire d'Amérique du Nord, naturalisé au bord des rivières : Alsace, Jura, Doubs, vallées de la Saône, du Rhône.</t>
         </is>
       </c>
       <c r="K880" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-67146</t>
-        </is>
-      </c>
-      <c r="L880" s="3" t="inlineStr"/>
+          <t>https://tela-botanica.org/eflore/?action=fiche&amp;module=fiche&amp;num_nom=7821&amp;onglet=synthese&amp;referentiel=bdtfx</t>
+        </is>
+      </c>
+      <c r="L880" s="3" t="inlineStr">
+        <is>
+          <t>originaire d'Amérique du Nord, écologie donnée par Coste pour la var. laevigatus</t>
+        </is>
+      </c>
     </row>
     <row r="881">
       <c r="A881" s="2" t="inlineStr">
         <is>
-          <t>Taxus × media</t>
+          <t>Symphytum officinale</t>
         </is>
       </c>
       <c r="B881" s="2" t="inlineStr">
         <is>
-          <t>If hybride</t>
+          <t>Consoude officinale</t>
         </is>
       </c>
       <c r="C881" s="2" t="inlineStr">
         <is>
-          <t>exotique (cultivée en France)</t>
+          <t>indigène</t>
         </is>
       </c>
       <c r="D881" s="2" t="inlineStr">
         <is>
-          <t>Jardins et paysages façonnés</t>
+          <t>Prairies et pelouses</t>
         </is>
       </c>
       <c r="E881" s="2" t="inlineStr">
         <is>
-          <t>Jardins, parcs et plantes ornementales</t>
+          <t>Prairies humides</t>
         </is>
       </c>
       <c r="F881" s="2" t="inlineStr">
         <is>
-          <t>HAB-01</t>
+          <t>PRA-03</t>
         </is>
       </c>
       <c r="G881" s="2" t="inlineStr">
         <is>
-          <t>cultivé ou planté</t>
+          <t>naturel</t>
         </is>
       </c>
       <c r="H881" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>typique</t>
         </is>
       </c>
       <c r="I881" s="2" t="inlineStr">
@@ -54002,29 +54038,25 @@
       </c>
       <c r="J881" s="3" t="inlineStr">
         <is>
-          <t>Espèce exotique (origine : hybride horticole (T. baccata × T. cuspidata)), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+          <t>Écologie : prés humides, fossés, bords des eaux, dans presque toute la France.</t>
         </is>
       </c>
       <c r="K881" s="2" t="inlineStr">
         <is>
-          <t>https://www.rhs.org.uk/plants/518671/taxus-x-media-groenland/details</t>
-        </is>
-      </c>
-      <c r="L881" s="3" t="inlineStr">
-        <is>
-          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
-        </is>
-      </c>
+          <t>https://tela-botanica.org/eflore/?action=fiche&amp;module=fiche&amp;num_nom=75402&amp;onglet=description&amp;referentiel=bdtfx</t>
+        </is>
+      </c>
+      <c r="L881" s="3" t="inlineStr"/>
     </row>
     <row r="882">
       <c r="A882" s="2" t="inlineStr">
         <is>
-          <t>Teucrium fruticans</t>
+          <t>Symphytum officinale</t>
         </is>
       </c>
       <c r="B882" s="2" t="inlineStr">
         <is>
-          <t>Germandrée arbustive</t>
+          <t>Consoude officinale</t>
         </is>
       </c>
       <c r="C882" s="2" t="inlineStr">
@@ -54034,17 +54066,17 @@
       </c>
       <c r="D882" s="2" t="inlineStr">
         <is>
-          <t>Landes, bruyères et fourrés méditerranéens</t>
+          <t>Mares, rivières et berges</t>
         </is>
       </c>
       <c r="E882" s="2" t="inlineStr">
         <is>
-          <t>Maquis et fourrés méditerranéens</t>
+          <t>Berges et zones littorales d'eau douce</t>
         </is>
       </c>
       <c r="F882" s="2" t="inlineStr">
         <is>
-          <t>LAN-02</t>
+          <t>EAU-03</t>
         </is>
       </c>
       <c r="G882" s="2" t="inlineStr">
@@ -54054,7 +54086,7 @@
       </c>
       <c r="H882" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I882" s="2" t="inlineStr">
@@ -54064,29 +54096,25 @@
       </c>
       <c r="J882" s="3" t="inlineStr">
         <is>
-          <t>Espèce des fourrés et fruticées thermoméditerranéens, plutôt sur substrat acide à l'état indigène.</t>
+          <t>Prés humides, fossés, bords des eaux.</t>
         </is>
       </c>
       <c r="K882" s="2" t="inlineStr">
         <is>
-          <t>https://inpn.mnhn.fr/espece/cd_nom/125995</t>
-        </is>
-      </c>
-      <c r="L882" s="3" t="inlineStr">
-        <is>
-          <t>très rare et menacé à l'état indigène (sud de la Corse, Albères), peut-être naturalisé par endroits</t>
-        </is>
-      </c>
+          <t>https://tela-botanica.org/eflore/?action=fiche&amp;module=fiche&amp;num_nom=75402&amp;onglet=description&amp;referentiel=bdtfx</t>
+        </is>
+      </c>
+      <c r="L882" s="3" t="inlineStr"/>
     </row>
     <row r="883">
       <c r="A883" s="2" t="inlineStr">
         <is>
-          <t>Teucrium fruticans</t>
+          <t>Symphytum officinale</t>
         </is>
       </c>
       <c r="B883" s="2" t="inlineStr">
         <is>
-          <t>Germandrée arbustive</t>
+          <t>Consoude officinale</t>
         </is>
       </c>
       <c r="C883" s="2" t="inlineStr">
@@ -54096,17 +54124,17 @@
       </c>
       <c r="D883" s="2" t="inlineStr">
         <is>
-          <t>Littoral, dunes et rivages salés</t>
+          <t>Marais, prairies humides et tourbières</t>
         </is>
       </c>
       <c r="E883" s="2" t="inlineStr">
         <is>
-          <t>Falaises et rivages rocheux côtiers</t>
+          <t>Prairies inondables ou longuement humides</t>
         </is>
       </c>
       <c r="F883" s="2" t="inlineStr">
         <is>
-          <t>LIT-03</t>
+          <t>HUM-03</t>
         </is>
       </c>
       <c r="G883" s="2" t="inlineStr">
@@ -54126,34 +54154,30 @@
       </c>
       <c r="J883" s="3" t="inlineStr">
         <is>
-          <t>Écologie : coteaux du littoral de la Méditerranée (Pyrénées-Orientales, Var, Corse).</t>
+          <t>Pousse sur des sols humides au moins l'hiver et riches en matières organiques se décomposant mal.</t>
         </is>
       </c>
       <c r="K883" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-75407</t>
-        </is>
-      </c>
-      <c r="L883" s="3" t="inlineStr">
-        <is>
-          <t>très rare et menacé à l'état indigène (sud de la Corse, Albères), peut-être naturalisé par endroits</t>
-        </is>
-      </c>
+          <t>https://www.tela-botanica.org/2017/08/article8229/</t>
+        </is>
+      </c>
+      <c r="L883" s="3" t="inlineStr"/>
     </row>
     <row r="884">
       <c r="A884" s="2" t="inlineStr">
         <is>
-          <t>Teucrium fruticans</t>
+          <t>Syringa vulgaris</t>
         </is>
       </c>
       <c r="B884" s="2" t="inlineStr">
         <is>
-          <t>Germandrée arbustive</t>
+          <t>Lilas commun</t>
         </is>
       </c>
       <c r="C884" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>naturalisée</t>
         </is>
       </c>
       <c r="D884" s="2" t="inlineStr">
@@ -54178,7 +54202,7 @@
       </c>
       <c r="H884" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>typique</t>
         </is>
       </c>
       <c r="I884" s="2" t="inlineStr">
@@ -54188,29 +54212,29 @@
       </c>
       <c r="J884" s="3" t="inlineStr">
         <is>
-          <t>Largement utilisée comme plante ornementale et plus ou moins naturalisée en climat thermoméditerranéen.</t>
+          <t>Cet arbrisseau très populaire est fréquemment planté dans les jardins d'Europe et d'Amérique du Nord en raison de ses attrayantes fleurs odorantes.</t>
         </is>
       </c>
       <c r="K884" s="2" t="inlineStr">
         <is>
-          <t>https://inpn.mnhn.fr/espece/cd_nom/125995</t>
+          <t>https://fr.wikipedia.org/wiki/Syringa_vulgaris</t>
         </is>
       </c>
       <c r="L884" s="3" t="inlineStr">
         <is>
-          <t>très rare et menacé à l'état indigène (sud de la Corse, Albères), peut-être naturalisé par endroits</t>
+          <t>naturalisation décrite pour l'Europe occidentale et septentrionale - milieux de naturalisation non décrits</t>
         </is>
       </c>
     </row>
     <row r="885">
       <c r="A885" s="2" t="inlineStr">
         <is>
-          <t>Thalictrum aquilegiifolium</t>
+          <t>Tamarix gallica</t>
         </is>
       </c>
       <c r="B885" s="2" t="inlineStr">
         <is>
-          <t>Pigamon à feuilles d'ancolie</t>
+          <t>Tamaris de France</t>
         </is>
       </c>
       <c r="C885" s="2" t="inlineStr">
@@ -54220,17 +54244,17 @@
       </c>
       <c r="D885" s="2" t="inlineStr">
         <is>
-          <t>Marais, prairies humides et tourbières</t>
+          <t>Mares, rivières et berges</t>
         </is>
       </c>
       <c r="E885" s="2" t="inlineStr">
         <is>
-          <t>Prairies inondables ou longuement humides</t>
+          <t>Berges et zones littorales d'eau douce</t>
         </is>
       </c>
       <c r="F885" s="2" t="inlineStr">
         <is>
-          <t>HUM-03</t>
+          <t>EAU-03</t>
         </is>
       </c>
       <c r="G885" s="2" t="inlineStr">
@@ -54250,29 +54274,25 @@
       </c>
       <c r="J885" s="3" t="inlineStr">
         <is>
-          <t>Mégaphorbiaies hygrophiles subboréales à montagnardes, méso-eutrophiles à eutrophiles (Petasito hybridi - Chaerophylletalia hirsuti).</t>
+          <t>F9.313 « Fourrés méditerranéo-macaronésiens à Tamaris » : berges, zones humides et localités côtières du bassin méditerranéen.</t>
         </is>
       </c>
       <c r="K885" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-67476-description</t>
-        </is>
-      </c>
-      <c r="L885" s="3" t="inlineStr">
-        <is>
-          <t>montagnes (Jura, Alpes, Massif central, Cévennes, Corbières, Pyrénées)</t>
-        </is>
-      </c>
+          <t>https://inpn.mnhn.fr/habitat/cd_hab/11627/tab/description</t>
+        </is>
+      </c>
+      <c r="L885" s="3" t="inlineStr"/>
     </row>
     <row r="886">
       <c r="A886" s="2" t="inlineStr">
         <is>
-          <t>Thalictrum aquilegiifolium</t>
+          <t>Tamarix gallica</t>
         </is>
       </c>
       <c r="B886" s="2" t="inlineStr">
         <is>
-          <t>Pigamon à feuilles d'ancolie</t>
+          <t>Tamaris de France</t>
         </is>
       </c>
       <c r="C886" s="2" t="inlineStr">
@@ -54282,17 +54302,17 @@
       </c>
       <c r="D886" s="2" t="inlineStr">
         <is>
-          <t>Forêts et sous-bois</t>
+          <t>Littoral, dunes et rivages salés</t>
         </is>
       </c>
       <c r="E886" s="2" t="inlineStr">
         <is>
-          <t>Forêts de feuillus caducs</t>
+          <t>Prés salés et végétation de transition côtière</t>
         </is>
       </c>
       <c r="F886" s="2" t="inlineStr">
         <is>
-          <t>FOR-01</t>
+          <t>LIT-04</t>
         </is>
       </c>
       <c r="G886" s="2" t="inlineStr">
@@ -54312,54 +54332,50 @@
       </c>
       <c r="J886" s="3" t="inlineStr">
         <is>
-          <t>Écologie : bois et ravins des montagnes.</t>
+          <t>Côtes de l'Océan et de la Manche ; fourrés d'arbrisseaux hydrophiles et subhalophiles (Tamaricion africanae).</t>
         </is>
       </c>
       <c r="K886" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-67476-description</t>
-        </is>
-      </c>
-      <c r="L886" s="3" t="inlineStr">
-        <is>
-          <t>montagnes (Jura, Alpes, Massif central, Cévennes, Corbières, Pyrénées)</t>
-        </is>
-      </c>
+          <t>https://tela-botanica.org/eflore/?action=fiche&amp;module=fiche&amp;niveau=3&amp;num_nom=66702&amp;onglet=synthese&amp;referentiel=bdtfx</t>
+        </is>
+      </c>
+      <c r="L886" s="3" t="inlineStr"/>
     </row>
     <row r="887">
       <c r="A887" s="2" t="inlineStr">
         <is>
-          <t>Thymus vulgaris</t>
+          <t>Tanacetum parthenium</t>
         </is>
       </c>
       <c r="B887" s="2" t="inlineStr">
         <is>
-          <t>Thym commun</t>
+          <t>Grande camomille</t>
         </is>
       </c>
       <c r="C887" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>naturalisée</t>
         </is>
       </c>
       <c r="D887" s="2" t="inlineStr">
         <is>
-          <t>Landes, bruyères et fourrés méditerranéens</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E887" s="2" t="inlineStr">
         <is>
-          <t>Maquis et fourrés méditerranéens</t>
+          <t>Murs, friches et espaces très artificialisés</t>
         </is>
       </c>
       <c r="F887" s="2" t="inlineStr">
         <is>
-          <t>LAN-02</t>
+          <t>HAB-03</t>
         </is>
       </c>
       <c r="G887" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>spontané (milieu secondaire)</t>
         </is>
       </c>
       <c r="H887" s="2" t="inlineStr">
@@ -54374,50 +54390,54 @@
       </c>
       <c r="J887" s="3" t="inlineStr">
         <is>
-          <t>Sous-arbrisseau commun des garrigues ensoleillées et des steppes du sud de l'Europe.</t>
+          <t>La grande camomille croît dans toute la France, dans les lieux incultes, dans les rocailles, les bords de chemins.</t>
         </is>
       </c>
       <c r="K887" s="2" t="inlineStr">
         <is>
-          <t>https://fr.wikipedia.org/wiki/Farigoule</t>
-        </is>
-      </c>
-      <c r="L887" s="3" t="inlineStr"/>
+          <t>https://fr.wikipedia.org/wiki/Tanacetum_parthenium</t>
+        </is>
+      </c>
+      <c r="L887" s="3" t="inlineStr">
+        <is>
+          <t>indigène en Europe de l'Est et du Sud, naturalisée en Europe</t>
+        </is>
+      </c>
     </row>
     <row r="888">
       <c r="A888" s="2" t="inlineStr">
         <is>
-          <t>Thymus vulgaris</t>
+          <t>Tanacetum parthenium</t>
         </is>
       </c>
       <c r="B888" s="2" t="inlineStr">
         <is>
-          <t>Thym commun</t>
+          <t>Grande camomille</t>
         </is>
       </c>
       <c r="C888" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>naturalisée</t>
         </is>
       </c>
       <c r="D888" s="2" t="inlineStr">
         <is>
-          <t>Prairies et pelouses</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E888" s="2" t="inlineStr">
         <is>
-          <t>Pelouses et prairies sèches</t>
+          <t>Cultures et jardins productifs</t>
         </is>
       </c>
       <c r="F888" s="2" t="inlineStr">
         <is>
-          <t>PRA-01</t>
+          <t>HAB-02</t>
         </is>
       </c>
       <c r="G888" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>spontané (milieu secondaire)</t>
         </is>
       </c>
       <c r="H888" s="2" t="inlineStr">
@@ -54432,30 +54452,34 @@
       </c>
       <c r="J888" s="3" t="inlineStr">
         <is>
-          <t>Habitats EUNIS : garrigues basiphiles occidentales (S61) et pelouses rocheuses calcaires (R18).</t>
+          <t>La grande camomille croît dans toute la France, dans les lieux incultes, les bords de chemins ou les milieux cultivés.</t>
         </is>
       </c>
       <c r="K888" s="2" t="inlineStr">
         <is>
-          <t>https://floraveg.eu/taxon/overview/Thymus%20vulgaris</t>
-        </is>
-      </c>
-      <c r="L888" s="3" t="inlineStr"/>
+          <t>https://fr.wikipedia.org/wiki/Tanacetum_parthenium</t>
+        </is>
+      </c>
+      <c r="L888" s="3" t="inlineStr">
+        <is>
+          <t>indigène en Europe de l'Est et du Sud, naturalisée en Europe</t>
+        </is>
+      </c>
     </row>
     <row r="889">
       <c r="A889" s="2" t="inlineStr">
         <is>
-          <t>Tiarella cordifolia</t>
+          <t>Tanacetum parthenium</t>
         </is>
       </c>
       <c r="B889" s="2" t="inlineStr">
         <is>
-          <t>Tiarelle</t>
+          <t>Grande camomille</t>
         </is>
       </c>
       <c r="C889" s="2" t="inlineStr">
         <is>
-          <t>exotique (cultivée en France)</t>
+          <t>naturalisée</t>
         </is>
       </c>
       <c r="D889" s="2" t="inlineStr">
@@ -54490,59 +54514,59 @@
       </c>
       <c r="J889" s="3" t="inlineStr">
         <is>
-          <t>Espèce exotique (origine : Est de l'Amérique du Nord), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+          <t>Elle est aussi cultivée comme plante médicinale et comme plante ornementale.</t>
         </is>
       </c>
       <c r="K889" s="2" t="inlineStr">
         <is>
-          <t>https://www.perennials.com/plants/tiarella-cordifolia.html</t>
+          <t>https://fr.wikipedia.org/wiki/Tanacetum_parthenium</t>
         </is>
       </c>
       <c r="L889" s="3" t="inlineStr">
         <is>
-          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+          <t>indigène en Europe de l'Est et du Sud, naturalisée en Europe</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="A890" s="2" t="inlineStr">
         <is>
-          <t>Tilia cordata</t>
+          <t>Tanacetum vulgare</t>
         </is>
       </c>
       <c r="B890" s="2" t="inlineStr">
         <is>
-          <t>Tilleul à petites feuilles</t>
+          <t>Tanaisie commune</t>
         </is>
       </c>
       <c r="C890" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>à vérifier</t>
         </is>
       </c>
       <c r="D890" s="2" t="inlineStr">
         <is>
-          <t>Forêts et sous-bois</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E890" s="2" t="inlineStr">
         <is>
-          <t>Forêts de feuillus caducs</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F890" s="2" t="inlineStr">
         <is>
-          <t>FOR-01</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G890" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H890" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I890" s="2" t="inlineStr">
@@ -54552,30 +54576,34 @@
       </c>
       <c r="J890" s="3" t="inlineStr">
         <is>
-          <t>Bois, dans presque toute la France et en Corse.</t>
+          <t>C'est aussi une plante ornementale des jardins privés ou publics, notamment la variété crispum aux feuilles frisées.</t>
         </is>
       </c>
       <c r="K890" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-68299</t>
-        </is>
-      </c>
-      <c r="L890" s="3" t="inlineStr"/>
+          <t>https://fr.wikipedia.org/wiki/Tanaisie_commune</t>
+        </is>
+      </c>
+      <c r="L890" s="3" t="inlineStr">
+        <is>
+          <t>très commune en Europe à l'état sauvage selon le texte mais milieux naturels non décrits</t>
+        </is>
+      </c>
     </row>
     <row r="891">
       <c r="A891" s="2" t="inlineStr">
         <is>
-          <t>Tilia cordata</t>
+          <t>Taxodium distichum</t>
         </is>
       </c>
       <c r="B891" s="2" t="inlineStr">
         <is>
-          <t>Tilleul à petites feuilles</t>
+          <t>Cyprès chauve</t>
         </is>
       </c>
       <c r="C891" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>exotique (cultivée en France)</t>
         </is>
       </c>
       <c r="D891" s="2" t="inlineStr">
@@ -54610,25 +54638,29 @@
       </c>
       <c r="J891" s="3" t="inlineStr">
         <is>
-          <t>Souvent planté.</t>
+          <t>Espèce exotique (origine : Sud-Est des États-Unis), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
         </is>
       </c>
       <c r="K891" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-68299</t>
-        </is>
-      </c>
-      <c r="L891" s="3" t="inlineStr"/>
+          <t>https://www.rhs.org.uk/plants/17999/taxodium-distichum-swamp-cypress-bald-cypress/details</t>
+        </is>
+      </c>
+      <c r="L891" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+        </is>
+      </c>
     </row>
     <row r="892">
       <c r="A892" s="2" t="inlineStr">
         <is>
-          <t>Tilia platyphyllos</t>
+          <t>Taxus baccata</t>
         </is>
       </c>
       <c r="B892" s="2" t="inlineStr">
         <is>
-          <t>Tilleul à grandes feuilles</t>
+          <t>If commun</t>
         </is>
       </c>
       <c r="C892" s="2" t="inlineStr">
@@ -54658,7 +54690,7 @@
       </c>
       <c r="H892" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I892" s="2" t="inlineStr">
@@ -54668,29 +54700,25 @@
       </c>
       <c r="J892" s="3" t="inlineStr">
         <is>
-          <t>Bois, dans les régions de l'Est et du Midi.</t>
+          <t>Écologie : rochers et bois des montagnes (Vosges, Jura, Alpes, Cévennes, Pyrénées, Corse).</t>
         </is>
       </c>
       <c r="K892" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-68332</t>
-        </is>
-      </c>
-      <c r="L892" s="3" t="inlineStr">
-        <is>
-          <t>assez rare à l'état naturel, surtout dans l'Est et le Midi</t>
-        </is>
-      </c>
+          <t>https://www.tela-botanica.org/bdtfx-nn-67146</t>
+        </is>
+      </c>
+      <c r="L892" s="3" t="inlineStr"/>
     </row>
     <row r="893">
       <c r="A893" s="2" t="inlineStr">
         <is>
-          <t>Tilia platyphyllos</t>
+          <t>Taxus baccata</t>
         </is>
       </c>
       <c r="B893" s="2" t="inlineStr">
         <is>
-          <t>Tilleul à grandes feuilles</t>
+          <t>If commun</t>
         </is>
       </c>
       <c r="C893" s="2" t="inlineStr">
@@ -54700,27 +54728,27 @@
       </c>
       <c r="D893" s="2" t="inlineStr">
         <is>
-          <t>Jardins et paysages façonnés</t>
+          <t>Rochers, éboulis et sols superficiels</t>
         </is>
       </c>
       <c r="E893" s="2" t="inlineStr">
         <is>
-          <t>Jardins, parcs et plantes ornementales</t>
+          <t>Falaises intérieures et dalles rocheuses</t>
         </is>
       </c>
       <c r="F893" s="2" t="inlineStr">
         <is>
-          <t>HAB-01</t>
+          <t>ROC-02</t>
         </is>
       </c>
       <c r="G893" s="2" t="inlineStr">
         <is>
-          <t>cultivé ou planté</t>
+          <t>naturel</t>
         </is>
       </c>
       <c r="H893" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>possible</t>
         </is>
       </c>
       <c r="I893" s="2" t="inlineStr">
@@ -54730,59 +54758,55 @@
       </c>
       <c r="J893" s="3" t="inlineStr">
         <is>
-          <t>Assez rare à l'état naturel, on le trouve surtout planté en haie ou isolé dans les parcs et le long des avenues.</t>
+          <t>Écologie : rochers et bois des montagnes.</t>
         </is>
       </c>
       <c r="K893" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/eflore/consultation/index_mobile.php?module=mobile&amp;referentiel=bdtfx&amp;num_nom=68332</t>
-        </is>
-      </c>
-      <c r="L893" s="3" t="inlineStr">
-        <is>
-          <t>assez rare à l'état naturel, surtout dans l'Est et le Midi</t>
-        </is>
-      </c>
+          <t>https://www.tela-botanica.org/bdtfx-nn-67146</t>
+        </is>
+      </c>
+      <c r="L893" s="3" t="inlineStr"/>
     </row>
     <row r="894">
       <c r="A894" s="2" t="inlineStr">
         <is>
-          <t>Tilia × euchlora</t>
+          <t>Taxus baccata</t>
         </is>
       </c>
       <c r="B894" s="2" t="inlineStr">
         <is>
-          <t>Tilleul de Crimée</t>
+          <t>If commun</t>
         </is>
       </c>
       <c r="C894" s="2" t="inlineStr">
         <is>
-          <t>exotique (cultivée en France)</t>
+          <t>indigène</t>
         </is>
       </c>
       <c r="D894" s="2" t="inlineStr">
         <is>
-          <t>Jardins et paysages façonnés</t>
+          <t>Forêts et sous-bois</t>
         </is>
       </c>
       <c r="E894" s="2" t="inlineStr">
         <is>
-          <t>Jardins, parcs et plantes ornementales</t>
+          <t>Boisements de feuillus sempervirents</t>
         </is>
       </c>
       <c r="F894" s="2" t="inlineStr">
         <is>
-          <t>HAB-01</t>
+          <t>FOR-02</t>
         </is>
       </c>
       <c r="G894" s="2" t="inlineStr">
         <is>
-          <t>cultivé ou planté</t>
+          <t>naturel</t>
         </is>
       </c>
       <c r="H894" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>possible</t>
         </is>
       </c>
       <c r="I894" s="2" t="inlineStr">
@@ -54792,34 +54816,30 @@
       </c>
       <c r="J894" s="3" t="inlineStr">
         <is>
-          <t>Espèce exotique (origine : Crimée, Caucase), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+          <t>Habitat 9580 « Bois méditerranéens à Taxus baccata » (Cahiers d'habitats).</t>
         </is>
       </c>
       <c r="K894" s="2" t="inlineStr">
         <is>
-          <t>https://www.rhs.org.uk/plants/92313/tilia-x-euchlora/details</t>
-        </is>
-      </c>
-      <c r="L894" s="3" t="inlineStr">
-        <is>
-          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
-        </is>
-      </c>
+          <t>https://inpn.mnhn.fr/habitat/cd_hab/1163</t>
+        </is>
+      </c>
+      <c r="L894" s="3" t="inlineStr"/>
     </row>
     <row r="895">
       <c r="A895" s="2" t="inlineStr">
         <is>
-          <t>Trachelospermum jasminoides</t>
+          <t>Taxus baccata</t>
         </is>
       </c>
       <c r="B895" s="2" t="inlineStr">
         <is>
-          <t>Jasmin étoilé</t>
+          <t>If commun</t>
         </is>
       </c>
       <c r="C895" s="2" t="inlineStr">
         <is>
-          <t>exotique (cultivée en France)</t>
+          <t>indigène</t>
         </is>
       </c>
       <c r="D895" s="2" t="inlineStr">
@@ -54854,29 +54874,25 @@
       </c>
       <c r="J895" s="3" t="inlineStr">
         <is>
-          <t>Espèce exotique (origine : Chine, Japon, Corée, Vietnam), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+          <t>Hors de son aire spontanée, surtout planté dans les parcs et les cimetières.</t>
         </is>
       </c>
       <c r="K895" s="2" t="inlineStr">
         <is>
-          <t>https://www.rhs.org.uk/plants/18287/trachelospermum-jasminoides/details</t>
-        </is>
-      </c>
-      <c r="L895" s="3" t="inlineStr">
-        <is>
-          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
-        </is>
-      </c>
+          <t>https://www.tela-botanica.org/bdtfx-nn-67146</t>
+        </is>
+      </c>
+      <c r="L895" s="3" t="inlineStr"/>
     </row>
     <row r="896">
       <c r="A896" s="2" t="inlineStr">
         <is>
-          <t>Trachycarpus fortunei</t>
+          <t>Taxus × media</t>
         </is>
       </c>
       <c r="B896" s="2" t="inlineStr">
         <is>
-          <t>Palmier de Chine</t>
+          <t>If hybride</t>
         </is>
       </c>
       <c r="C896" s="2" t="inlineStr">
@@ -54916,12 +54932,12 @@
       </c>
       <c r="J896" s="3" t="inlineStr">
         <is>
-          <t>Espèce exotique (origine : Chine, Himalaya), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+          <t>Espèce exotique (origine : hybride horticole (T. baccata × T. cuspidata)), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
         </is>
       </c>
       <c r="K896" s="2" t="inlineStr">
         <is>
-          <t>https://www.rhs.org.uk/plants/18291/Trachycarpus-fortunei/Details</t>
+          <t>https://www.rhs.org.uk/plants/518671/taxus-x-media-groenland/details</t>
         </is>
       </c>
       <c r="L896" s="3" t="inlineStr">
@@ -54933,12 +54949,12 @@
     <row r="897">
       <c r="A897" s="2" t="inlineStr">
         <is>
-          <t>Tradescantia virginiana</t>
+          <t>Tetradium daniellii</t>
         </is>
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>Misère</t>
+          <t>Arbre à miel</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -54978,34 +54994,34 @@
       </c>
       <c r="J897" s="3" t="inlineStr">
         <is>
-          <t>Espèce exotique (origine : Est des États-Unis), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+          <t>L'arbre à miel est de plus en plus utilisé comme arbre d'alignement dans les villes, le long des rues ou des lignes de tramway (notamment à Montpellier).</t>
         </is>
       </c>
       <c r="K897" s="2" t="inlineStr">
         <is>
-          <t>https://www.rhs.org.uk/plants/18305/wd/details</t>
+          <t>https://fr.wikipedia.org/wiki/Tetradium_daniellii</t>
         </is>
       </c>
       <c r="L897" s="3" t="inlineStr">
         <is>
-          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+          <t>milieu d'origine hors de France non renseigné (règle R10) - encore assez rare en France</t>
         </is>
       </c>
     </row>
     <row r="898">
       <c r="A898" s="2" t="inlineStr">
         <is>
-          <t>Trifolium repens</t>
+          <t>Teucrium chamaedrys</t>
         </is>
       </c>
       <c r="B898" s="2" t="inlineStr">
         <is>
-          <t>Trèfle blanc</t>
+          <t>Germandrée petit-chêne</t>
         </is>
       </c>
       <c r="C898" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>à vérifier</t>
         </is>
       </c>
       <c r="D898" s="2" t="inlineStr">
@@ -55015,12 +55031,12 @@
       </c>
       <c r="E898" s="2" t="inlineStr">
         <is>
-          <t>Prairies mésophiles</t>
+          <t>Pelouses et prairies sèches</t>
         </is>
       </c>
       <c r="F898" s="2" t="inlineStr">
         <is>
-          <t>PRA-02</t>
+          <t>PRA-01</t>
         </is>
       </c>
       <c r="G898" s="2" t="inlineStr">
@@ -55040,50 +55056,54 @@
       </c>
       <c r="J898" s="3" t="inlineStr">
         <is>
-          <t>Prairies mésohydriques européennes, pâturées, planitiaires à montagnardes (Trifolio repentis - Cynosuretalia cristati).</t>
+          <t>On la trouve dans des pelouses calcaires sèches, des bois thermophiles ou des éboulis.</t>
         </is>
       </c>
       <c r="K898" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-69341</t>
-        </is>
-      </c>
-      <c r="L898" s="3" t="inlineStr"/>
+          <t>https://fr.wikipedia.org/wiki/Germandr%C3%A9e_petit-ch%C3%AAne</t>
+        </is>
+      </c>
+      <c r="L898" s="3" t="inlineStr">
+        <is>
+          <t>milieu décrit pour l'aire générale (presque toute l'Europe sauf le nord), France non citée</t>
+        </is>
+      </c>
     </row>
     <row r="899">
       <c r="A899" s="2" t="inlineStr">
         <is>
-          <t>Trifolium repens</t>
+          <t>Teucrium chamaedrys</t>
         </is>
       </c>
       <c r="B899" s="2" t="inlineStr">
         <is>
-          <t>Trèfle blanc</t>
+          <t>Germandrée petit-chêne</t>
         </is>
       </c>
       <c r="C899" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>à vérifier</t>
         </is>
       </c>
       <c r="D899" s="2" t="inlineStr">
         <is>
-          <t>Jardins et paysages façonnés</t>
+          <t>Forêts et sous-bois</t>
         </is>
       </c>
       <c r="E899" s="2" t="inlineStr">
         <is>
-          <t>Murs, friches et espaces très artificialisés</t>
+          <t>Forêts de feuillus caducs</t>
         </is>
       </c>
       <c r="F899" s="2" t="inlineStr">
         <is>
-          <t>HAB-03</t>
+          <t>FOR-01</t>
         </is>
       </c>
       <c r="G899" s="2" t="inlineStr">
         <is>
-          <t>spontané (milieu secondaire)</t>
+          <t>naturel</t>
         </is>
       </c>
       <c r="H899" s="2" t="inlineStr">
@@ -55098,50 +55118,54 @@
       </c>
       <c r="J899" s="3" t="inlineStr">
         <is>
-          <t>Colonise les prairies, pelouses fraîches, champs cultivés, pâturages, lieux piétinés, friches et talus, jusqu'à 2500 m.</t>
+          <t>On la trouve dans des pelouses calcaires sèches, des bois thermophiles ou des éboulis.</t>
         </is>
       </c>
       <c r="K899" s="2" t="inlineStr">
         <is>
-          <t>https://inpn.mnhn.fr/espece/cd_nom/127454</t>
-        </is>
-      </c>
-      <c r="L899" s="3" t="inlineStr"/>
+          <t>https://fr.wikipedia.org/wiki/Germandr%C3%A9e_petit-ch%C3%AAne</t>
+        </is>
+      </c>
+      <c r="L899" s="3" t="inlineStr">
+        <is>
+          <t>milieu décrit pour l'aire générale (presque toute l'Europe sauf le nord), France non citée</t>
+        </is>
+      </c>
     </row>
     <row r="900">
       <c r="A900" s="2" t="inlineStr">
         <is>
-          <t>Trifolium repens</t>
+          <t>Teucrium chamaedrys</t>
         </is>
       </c>
       <c r="B900" s="2" t="inlineStr">
         <is>
-          <t>Trèfle blanc</t>
+          <t>Germandrée petit-chêne</t>
         </is>
       </c>
       <c r="C900" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>à vérifier</t>
         </is>
       </c>
       <c r="D900" s="2" t="inlineStr">
         <is>
-          <t>Jardins et paysages façonnés</t>
+          <t>Rochers, éboulis et sols superficiels</t>
         </is>
       </c>
       <c r="E900" s="2" t="inlineStr">
         <is>
-          <t>Cultures et jardins productifs</t>
+          <t>Éboulis et pierriers</t>
         </is>
       </c>
       <c r="F900" s="2" t="inlineStr">
         <is>
-          <t>HAB-02</t>
+          <t>ROC-01</t>
         </is>
       </c>
       <c r="G900" s="2" t="inlineStr">
         <is>
-          <t>spontané (milieu secondaire)</t>
+          <t>naturel</t>
         </is>
       </c>
       <c r="H900" s="2" t="inlineStr">
@@ -55156,25 +55180,29 @@
       </c>
       <c r="J900" s="3" t="inlineStr">
         <is>
-          <t>Colonise aussi les champs cultivés.</t>
+          <t>On la trouve dans des pelouses calcaires sèches, des bois thermophiles ou des éboulis.</t>
         </is>
       </c>
       <c r="K900" s="2" t="inlineStr">
         <is>
-          <t>https://inpn.mnhn.fr/espece/cd_nom/127454</t>
-        </is>
-      </c>
-      <c r="L900" s="3" t="inlineStr"/>
+          <t>https://fr.wikipedia.org/wiki/Germandr%C3%A9e_petit-ch%C3%AAne</t>
+        </is>
+      </c>
+      <c r="L900" s="3" t="inlineStr">
+        <is>
+          <t>milieu décrit pour l'aire générale (presque toute l'Europe sauf le nord), France non citée</t>
+        </is>
+      </c>
     </row>
     <row r="901">
       <c r="A901" s="2" t="inlineStr">
         <is>
-          <t>Trollius europaeus</t>
+          <t>Teucrium fruticans</t>
         </is>
       </c>
       <c r="B901" s="2" t="inlineStr">
         <is>
-          <t>Trolle d'Europe</t>
+          <t>Germandrée arbustive</t>
         </is>
       </c>
       <c r="C901" s="2" t="inlineStr">
@@ -55184,17 +55212,17 @@
       </c>
       <c r="D901" s="2" t="inlineStr">
         <is>
-          <t>Prairies et pelouses</t>
+          <t>Landes, bruyères et fourrés méditerranéens</t>
         </is>
       </c>
       <c r="E901" s="2" t="inlineStr">
         <is>
-          <t>Prairies humides</t>
+          <t>Maquis et fourrés méditerranéens</t>
         </is>
       </c>
       <c r="F901" s="2" t="inlineStr">
         <is>
-          <t>PRA-03</t>
+          <t>LAN-02</t>
         </is>
       </c>
       <c r="G901" s="2" t="inlineStr">
@@ -55214,29 +55242,29 @@
       </c>
       <c r="J901" s="3" t="inlineStr">
         <is>
-          <t>Espèce caractéristique des prairies à Molinia caerulea et des prairies atlantiques humides.</t>
+          <t>Espèce des fourrés et fruticées thermoméditerranéens, plutôt sur substrat acide à l'état indigène.</t>
         </is>
       </c>
       <c r="K901" s="2" t="inlineStr">
         <is>
-          <t>https://inpn.mnhn.fr/espece/cd_nom/127872/tab/habitats</t>
+          <t>https://inpn.mnhn.fr/espece/cd_nom/125995</t>
         </is>
       </c>
       <c r="L901" s="3" t="inlineStr">
         <is>
-          <t>montagnard (Vosges, Jura, Alpes, Massif central, Pyrénées)</t>
+          <t>très rare et menacé à l'état indigène (sud de la Corse, Albères), peut-être naturalisé par endroits</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" s="2" t="inlineStr">
         <is>
-          <t>Trollius europaeus</t>
+          <t>Teucrium fruticans</t>
         </is>
       </c>
       <c r="B902" s="2" t="inlineStr">
         <is>
-          <t>Trolle d'Europe</t>
+          <t>Germandrée arbustive</t>
         </is>
       </c>
       <c r="C902" s="2" t="inlineStr">
@@ -55246,17 +55274,17 @@
       </c>
       <c r="D902" s="2" t="inlineStr">
         <is>
-          <t>Prairies et pelouses</t>
+          <t>Littoral, dunes et rivages salés</t>
         </is>
       </c>
       <c r="E902" s="2" t="inlineStr">
         <is>
-          <t>Pelouses alpines et subalpines</t>
+          <t>Falaises et rivages rocheux côtiers</t>
         </is>
       </c>
       <c r="F902" s="2" t="inlineStr">
         <is>
-          <t>PRA-04</t>
+          <t>LIT-03</t>
         </is>
       </c>
       <c r="G902" s="2" t="inlineStr">
@@ -55266,7 +55294,7 @@
       </c>
       <c r="H902" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>possible</t>
         </is>
       </c>
       <c r="I902" s="2" t="inlineStr">
@@ -55276,29 +55304,29 @@
       </c>
       <c r="J902" s="3" t="inlineStr">
         <is>
-          <t>Écologie : prairies et pâturages des montagnes (Vosges, Jura, Alpes, Auvergne, Pyrénées).</t>
+          <t>Écologie : coteaux du littoral de la Méditerranée (Pyrénées-Orientales, Var, Corse).</t>
         </is>
       </c>
       <c r="K902" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-75423-synthese?referentiel=bdtfx&amp;module=fiche&amp;action=fiche&amp;num_nom=75423&amp;niveau=3</t>
+          <t>https://www.tela-botanica.org/bdtfx-nn-75407</t>
         </is>
       </c>
       <c r="L902" s="3" t="inlineStr">
         <is>
-          <t>montagnard (Vosges, Jura, Alpes, Massif central, Pyrénées)</t>
+          <t>très rare et menacé à l'état indigène (sud de la Corse, Albères), peut-être naturalisé par endroits</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" s="2" t="inlineStr">
         <is>
-          <t>Trollius europaeus</t>
+          <t>Teucrium fruticans</t>
         </is>
       </c>
       <c r="B903" s="2" t="inlineStr">
         <is>
-          <t>Trolle d'Europe</t>
+          <t>Germandrée arbustive</t>
         </is>
       </c>
       <c r="C903" s="2" t="inlineStr">
@@ -55308,27 +55336,27 @@
       </c>
       <c r="D903" s="2" t="inlineStr">
         <is>
-          <t>Forêts et sous-bois</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E903" s="2" t="inlineStr">
         <is>
-          <t>Forêts de feuillus caducs</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F903" s="2" t="inlineStr">
         <is>
-          <t>FOR-01</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G903" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H903" s="2" t="inlineStr">
         <is>
-          <t>possible</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I903" s="2" t="inlineStr">
@@ -55338,29 +55366,29 @@
       </c>
       <c r="J903" s="3" t="inlineStr">
         <is>
-          <t>Plante des prairies humides et des bois clairs de montagne entre 500 et 2500 m.</t>
+          <t>Largement utilisée comme plante ornementale et plus ou moins naturalisée en climat thermoméditerranéen.</t>
         </is>
       </c>
       <c r="K903" s="2" t="inlineStr">
         <is>
-          <t>https://fr.wikipedia.org/wiki/Trolle_d'Europe</t>
+          <t>https://inpn.mnhn.fr/espece/cd_nom/125995</t>
         </is>
       </c>
       <c r="L903" s="3" t="inlineStr">
         <is>
-          <t>montagnard (Vosges, Jura, Alpes, Massif central, Pyrénées)</t>
+          <t>très rare et menacé à l'état indigène (sud de la Corse, Albères), peut-être naturalisé par endroits</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" s="2" t="inlineStr">
         <is>
-          <t>Tussilago farfara</t>
+          <t>Thalictrum aquilegiifolium</t>
         </is>
       </c>
       <c r="B904" s="2" t="inlineStr">
         <is>
-          <t>Tussilage</t>
+          <t>Pigamon à feuilles d'ancolie</t>
         </is>
       </c>
       <c r="C904" s="2" t="inlineStr">
@@ -55370,17 +55398,17 @@
       </c>
       <c r="D904" s="2" t="inlineStr">
         <is>
-          <t>Rochers, éboulis et sols superficiels</t>
+          <t>Marais, prairies humides et tourbières</t>
         </is>
       </c>
       <c r="E904" s="2" t="inlineStr">
         <is>
-          <t>Sols nus ou à végétation clairsemée</t>
+          <t>Prairies inondables ou longuement humides</t>
         </is>
       </c>
       <c r="F904" s="2" t="inlineStr">
         <is>
-          <t>ROC-03</t>
+          <t>HUM-03</t>
         </is>
       </c>
       <c r="G904" s="2" t="inlineStr">
@@ -55395,26 +55423,34 @@
       </c>
       <c r="I904" s="2" t="inlineStr">
         <is>
-          <t>à vérifier (non affichée)</t>
-        </is>
-      </c>
-      <c r="J904" s="3" t="inlineStr"/>
-      <c r="K904" s="2" t="inlineStr"/>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J904" s="3" t="inlineStr">
+        <is>
+          <t>Mégaphorbiaies hygrophiles subboréales à montagnardes, méso-eutrophiles à eutrophiles (Petasito hybridi - Chaerophylletalia hirsuti).</t>
+        </is>
+      </c>
+      <c r="K904" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tela-botanica.org/bdtfx-nn-67476-description</t>
+        </is>
+      </c>
       <c r="L904" s="3" t="inlineStr">
         <is>
-          <t>écologie source limitée à « lieux frais », milieu pionnier sur sol nu seulement d'après des commentaires de lecteurs, à vérifier</t>
+          <t>montagnes (Jura, Alpes, Massif central, Cévennes, Corbières, Pyrénées)</t>
         </is>
       </c>
     </row>
     <row r="905">
       <c r="A905" s="2" t="inlineStr">
         <is>
-          <t>Typha latifolia</t>
+          <t>Thalictrum aquilegiifolium</t>
         </is>
       </c>
       <c r="B905" s="2" t="inlineStr">
         <is>
-          <t>Massette à larges feuilles</t>
+          <t>Pigamon à feuilles d'ancolie</t>
         </is>
       </c>
       <c r="C905" s="2" t="inlineStr">
@@ -55424,17 +55460,17 @@
       </c>
       <c r="D905" s="2" t="inlineStr">
         <is>
-          <t>Marais, prairies humides et tourbières</t>
+          <t>Forêts et sous-bois</t>
         </is>
       </c>
       <c r="E905" s="2" t="inlineStr">
         <is>
-          <t>Roselières et végétations palustres</t>
+          <t>Forêts de feuillus caducs</t>
         </is>
       </c>
       <c r="F905" s="2" t="inlineStr">
         <is>
-          <t>HUM-04</t>
+          <t>FOR-01</t>
         </is>
       </c>
       <c r="G905" s="2" t="inlineStr">
@@ -55444,7 +55480,7 @@
       </c>
       <c r="H905" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I905" s="2" t="inlineStr">
@@ -55454,55 +55490,59 @@
       </c>
       <c r="J905" s="3" t="inlineStr">
         <is>
-          <t>Forme des colonies denses dans les roselières, sur sols très humides à marécageux près des eaux douces.</t>
+          <t>Écologie : bois et ravins des montagnes.</t>
         </is>
       </c>
       <c r="K905" s="2" t="inlineStr">
         <is>
-          <t>https://fr.wikipedia.org/wiki/Massette_%C3%A0_larges_feuilles</t>
-        </is>
-      </c>
-      <c r="L905" s="3" t="inlineStr"/>
+          <t>https://www.tela-botanica.org/bdtfx-nn-67476-description</t>
+        </is>
+      </c>
+      <c r="L905" s="3" t="inlineStr">
+        <is>
+          <t>montagnes (Jura, Alpes, Massif central, Cévennes, Corbières, Pyrénées)</t>
+        </is>
+      </c>
     </row>
     <row r="906">
       <c r="A906" s="2" t="inlineStr">
         <is>
-          <t>Typha latifolia</t>
+          <t>Thuja occidentalis</t>
         </is>
       </c>
       <c r="B906" s="2" t="inlineStr">
         <is>
-          <t>Massette à larges feuilles</t>
+          <t>Thuya du Canada</t>
         </is>
       </c>
       <c r="C906" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>exotique (cultivée en France)</t>
         </is>
       </c>
       <c r="D906" s="2" t="inlineStr">
         <is>
-          <t>Mares, rivières et berges</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E906" s="2" t="inlineStr">
         <is>
-          <t>Mares, étangs et plans d'eau</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F906" s="2" t="inlineStr">
         <is>
-          <t>EAU-01</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G906" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H906" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>typique</t>
         </is>
       </c>
       <c r="I906" s="2" t="inlineStr">
@@ -55512,50 +55552,54 @@
       </c>
       <c r="J906" s="3" t="inlineStr">
         <is>
-          <t>Écologie : mares, étangs et rivières, dans presque toute la France et en Corse.</t>
+          <t>Le thuya occidental est très largement utilisé comme arbre d'ornement, en particulier pour constituer des écrans et des haies dans les jardins.</t>
         </is>
       </c>
       <c r="K906" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/eflore/?action=pdf-export&amp;module=pdf-export&amp;niveau=2&amp;num_nom=70154&amp;referentiel=bdtfx</t>
-        </is>
-      </c>
-      <c r="L906" s="3" t="inlineStr"/>
+          <t>https://fr.wikipedia.org/wiki/Thuya_occidental</t>
+        </is>
+      </c>
+      <c r="L906" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+        </is>
+      </c>
     </row>
     <row r="907">
       <c r="A907" s="2" t="inlineStr">
         <is>
-          <t>Ulex europaeus</t>
+          <t>Thuja plicata</t>
         </is>
       </c>
       <c r="B907" s="2" t="inlineStr">
         <is>
-          <t>Ajonc d'Europe</t>
+          <t>Thuya géant</t>
         </is>
       </c>
       <c r="C907" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>exotique (cultivée en France)</t>
         </is>
       </c>
       <c r="D907" s="2" t="inlineStr">
         <is>
-          <t>Landes, bruyères et fourrés méditerranéens</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E907" s="2" t="inlineStr">
         <is>
-          <t>Landes tempérées à bruyères</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F907" s="2" t="inlineStr">
         <is>
-          <t>LAN-01</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G907" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H907" s="2" t="inlineStr">
@@ -55570,55 +55614,59 @@
       </c>
       <c r="J907" s="3" t="inlineStr">
         <is>
-          <t>Écologie : landes et lieux stériles siliceux, surtout dans l'Ouest et le Centre ; rare dans le Midi.</t>
+          <t>C'est un arbre d'ornement très cultivé dans les régions tempérées du monde, notamment en Europe dans les jardins sous forme de haies taillées ou non.</t>
         </is>
       </c>
       <c r="K907" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-70199-synthese</t>
-        </is>
-      </c>
-      <c r="L907" s="3" t="inlineStr"/>
+          <t>https://fr.wikipedia.org/wiki/Thuja_plicata</t>
+        </is>
+      </c>
+      <c r="L907" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+        </is>
+      </c>
     </row>
     <row r="908">
       <c r="A908" s="2" t="inlineStr">
         <is>
-          <t>Ulex minor</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="B908" s="2" t="inlineStr">
         <is>
-          <t>Ajonc nain</t>
+          <t>Serpolet</t>
         </is>
       </c>
       <c r="C908" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>à vérifier</t>
         </is>
       </c>
       <c r="D908" s="2" t="inlineStr">
         <is>
-          <t>Landes, bruyères et fourrés méditerranéens</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E908" s="2" t="inlineStr">
         <is>
-          <t>Landes tempérées à bruyères</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F908" s="2" t="inlineStr">
         <is>
-          <t>LAN-01</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G908" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H908" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I908" s="2" t="inlineStr">
@@ -55628,29 +55676,29 @@
       </c>
       <c r="J908" s="3" t="inlineStr">
         <is>
-          <t>Écologie : landes et lieux stériles siliceux, dans l'Ouest et le Centre, nul dans le Midi.</t>
+          <t>Plante couvre-sol, le serpolet ne doit pas être planté dans une terre trop riche car c'est dans les sols maigres et secs qu'il donne le meilleur de lui-même.</t>
         </is>
       </c>
       <c r="K908" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-70223</t>
+          <t>https://fr.wikipedia.org/wiki/Serpolet</t>
         </is>
       </c>
       <c r="L908" s="3" t="inlineStr">
         <is>
-          <t>surtout dans l'Ouest et le Centre, absent du Midi</t>
+          <t>statut en France non précisé (originaire d'Europe et d'Asie) - milieu naturel non décrit par le texte</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" s="2" t="inlineStr">
         <is>
-          <t>Ulex minor</t>
+          <t>Thymus vulgaris</t>
         </is>
       </c>
       <c r="B909" s="2" t="inlineStr">
         <is>
-          <t>Ajonc nain</t>
+          <t>Thym commun</t>
         </is>
       </c>
       <c r="C909" s="2" t="inlineStr">
@@ -55660,17 +55708,17 @@
       </c>
       <c r="D909" s="2" t="inlineStr">
         <is>
-          <t>Marais, prairies humides et tourbières</t>
+          <t>Landes, bruyères et fourrés méditerranéens</t>
         </is>
       </c>
       <c r="E909" s="2" t="inlineStr">
         <is>
-          <t>Bas-marais, tourbières de transition et marais tourbeux</t>
+          <t>Maquis et fourrés méditerranéens</t>
         </is>
       </c>
       <c r="F909" s="2" t="inlineStr">
         <is>
-          <t>HUM-02</t>
+          <t>LAN-02</t>
         </is>
       </c>
       <c r="G909" s="2" t="inlineStr">
@@ -55680,7 +55728,7 @@
       </c>
       <c r="H909" s="2" t="inlineStr">
         <is>
-          <t>possible</t>
+          <t>typique</t>
         </is>
       </c>
       <c r="I909" s="2" t="inlineStr">
@@ -55690,29 +55738,25 @@
       </c>
       <c r="J909" s="3" t="inlineStr">
         <is>
-          <t>Fréquent sur silice dans les landes humides et lieux incultes, surtout dans l'ouest et le centre de la France.</t>
+          <t>Sous-arbrisseau commun des garrigues ensoleillées et des steppes du sud de l'Europe.</t>
         </is>
       </c>
       <c r="K909" s="2" t="inlineStr">
         <is>
-          <t>https://fr.wikipedia.org/wiki/Ajonc_nain</t>
-        </is>
-      </c>
-      <c r="L909" s="3" t="inlineStr">
-        <is>
-          <t>surtout dans l'Ouest et le Centre, absent du Midi</t>
-        </is>
-      </c>
+          <t>https://fr.wikipedia.org/wiki/Farigoule</t>
+        </is>
+      </c>
+      <c r="L909" s="3" t="inlineStr"/>
     </row>
     <row r="910">
       <c r="A910" s="2" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Thymus vulgaris</t>
         </is>
       </c>
       <c r="B910" s="2" t="inlineStr">
         <is>
-          <t>Orme champêtre</t>
+          <t>Thym commun</t>
         </is>
       </c>
       <c r="C910" s="2" t="inlineStr">
@@ -55722,17 +55766,17 @@
       </c>
       <c r="D910" s="2" t="inlineStr">
         <is>
-          <t>Haies, lisières et fourrés</t>
+          <t>Prairies et pelouses</t>
         </is>
       </c>
       <c r="E910" s="2" t="inlineStr">
         <is>
-          <t>Haies et lignes d'arbres</t>
+          <t>Pelouses et prairies sèches</t>
         </is>
       </c>
       <c r="F910" s="2" t="inlineStr">
         <is>
-          <t>LIS-01</t>
+          <t>PRA-01</t>
         </is>
       </c>
       <c r="G910" s="2" t="inlineStr">
@@ -55742,7 +55786,7 @@
       </c>
       <c r="H910" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I910" s="2" t="inlineStr">
@@ -55752,54 +55796,50 @@
       </c>
       <c r="J910" s="3" t="inlineStr">
         <is>
-          <t>Il est présent dans les haies, les forêts alluviales, les friches, les talus, les décombres.</t>
+          <t>Habitats EUNIS : garrigues basiphiles occidentales (S61) et pelouses rocheuses calcaires (R18).</t>
         </is>
       </c>
       <c r="K910" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/eflore/consultation/index_mobile.php?module=mobile&amp;referentiel=bdtfx&amp;num_nom=70296</t>
-        </is>
-      </c>
-      <c r="L910" s="3" t="inlineStr">
-        <is>
-          <t>fortement décimé par la graphiose, souvent réduit à l'état d'arbuste</t>
-        </is>
-      </c>
+          <t>https://floraveg.eu/taxon/overview/Thymus%20vulgaris</t>
+        </is>
+      </c>
+      <c r="L910" s="3" t="inlineStr"/>
     </row>
     <row r="911">
       <c r="A911" s="2" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Tiarella cordifolia</t>
         </is>
       </c>
       <c r="B911" s="2" t="inlineStr">
         <is>
-          <t>Orme champêtre</t>
+          <t>Tiarelle</t>
         </is>
       </c>
       <c r="C911" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>exotique (cultivée en France)</t>
         </is>
       </c>
       <c r="D911" s="2" t="inlineStr">
         <is>
-          <t>Forêts et sous-bois</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E911" s="2" t="inlineStr">
         <is>
-          <t>Forêts de feuillus caducs</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F911" s="2" t="inlineStr">
         <is>
-          <t>FOR-01</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G911" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H911" s="2" t="inlineStr">
@@ -55814,29 +55854,29 @@
       </c>
       <c r="J911" s="3" t="inlineStr">
         <is>
-          <t>Présent dans les forêts alluviales, jusqu'à 1300 m d'altitude.</t>
+          <t>Espèce exotique (origine : Est de l'Amérique du Nord), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
         </is>
       </c>
       <c r="K911" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/eflore/consultation/index_mobile.php?module=mobile&amp;referentiel=bdtfx&amp;num_nom=70296</t>
+          <t>https://www.perennials.com/plants/tiarella-cordifolia.html</t>
         </is>
       </c>
       <c r="L911" s="3" t="inlineStr">
         <is>
-          <t>fortement décimé par la graphiose, souvent réduit à l'état d'arbuste</t>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" s="2" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Tilia cordata</t>
         </is>
       </c>
       <c r="B912" s="2" t="inlineStr">
         <is>
-          <t>Orme champêtre</t>
+          <t>Tilleul à petites feuilles</t>
         </is>
       </c>
       <c r="C912" s="2" t="inlineStr">
@@ -55846,27 +55886,27 @@
       </c>
       <c r="D912" s="2" t="inlineStr">
         <is>
-          <t>Jardins et paysages façonnés</t>
+          <t>Forêts et sous-bois</t>
         </is>
       </c>
       <c r="E912" s="2" t="inlineStr">
         <is>
-          <t>Murs, friches et espaces très artificialisés</t>
+          <t>Forêts de feuillus caducs</t>
         </is>
       </c>
       <c r="F912" s="2" t="inlineStr">
         <is>
-          <t>HAB-03</t>
+          <t>FOR-01</t>
         </is>
       </c>
       <c r="G912" s="2" t="inlineStr">
         <is>
-          <t>spontané (milieu secondaire)</t>
+          <t>naturel</t>
         </is>
       </c>
       <c r="H912" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>typique</t>
         </is>
       </c>
       <c r="I912" s="2" t="inlineStr">
@@ -55876,29 +55916,25 @@
       </c>
       <c r="J912" s="3" t="inlineStr">
         <is>
-          <t>Présent dans les friches, les talus, les décombres.</t>
+          <t>Bois, dans presque toute la France et en Corse.</t>
         </is>
       </c>
       <c r="K912" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/eflore/consultation/index_mobile.php?module=mobile&amp;referentiel=bdtfx&amp;num_nom=70296</t>
-        </is>
-      </c>
-      <c r="L912" s="3" t="inlineStr">
-        <is>
-          <t>fortement décimé par la graphiose, souvent réduit à l'état d'arbuste</t>
-        </is>
-      </c>
+          <t>https://www.tela-botanica.org/bdtfx-nn-68299</t>
+        </is>
+      </c>
+      <c r="L912" s="3" t="inlineStr"/>
     </row>
     <row r="913">
       <c r="A913" s="2" t="inlineStr">
         <is>
-          <t>Urtica dioica</t>
+          <t>Tilia cordata</t>
         </is>
       </c>
       <c r="B913" s="2" t="inlineStr">
         <is>
-          <t>Ortie dioïque</t>
+          <t>Tilleul à petites feuilles</t>
         </is>
       </c>
       <c r="C913" s="2" t="inlineStr">
@@ -55913,22 +55949,22 @@
       </c>
       <c r="E913" s="2" t="inlineStr">
         <is>
-          <t>Murs, friches et espaces très artificialisés</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F913" s="2" t="inlineStr">
         <is>
-          <t>HAB-03</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G913" s="2" t="inlineStr">
         <is>
-          <t>spontané (milieu secondaire)</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H913" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I913" s="2" t="inlineStr">
@@ -55938,12 +55974,12 @@
       </c>
       <c r="J913" s="3" t="inlineStr">
         <is>
-          <t>Lieux incultes, dans toute la France et la Corse.</t>
+          <t>Souvent planté.</t>
         </is>
       </c>
       <c r="K913" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-70396</t>
+          <t>https://www.tela-botanica.org/bdtfx-nn-68299</t>
         </is>
       </c>
       <c r="L913" s="3" t="inlineStr"/>
@@ -55951,12 +55987,12 @@
     <row r="914">
       <c r="A914" s="2" t="inlineStr">
         <is>
-          <t>Urtica dioica</t>
+          <t>Tilia platyphyllos</t>
         </is>
       </c>
       <c r="B914" s="2" t="inlineStr">
         <is>
-          <t>Ortie dioïque</t>
+          <t>Tilleul à grandes feuilles</t>
         </is>
       </c>
       <c r="C914" s="2" t="inlineStr">
@@ -55966,17 +56002,17 @@
       </c>
       <c r="D914" s="2" t="inlineStr">
         <is>
-          <t>Haies, lisières et fourrés</t>
+          <t>Forêts et sous-bois</t>
         </is>
       </c>
       <c r="E914" s="2" t="inlineStr">
         <is>
-          <t>Ourlets herbacés</t>
+          <t>Forêts de feuillus caducs</t>
         </is>
       </c>
       <c r="F914" s="2" t="inlineStr">
         <is>
-          <t>PRA-05</t>
+          <t>FOR-01</t>
         </is>
       </c>
       <c r="G914" s="2" t="inlineStr">
@@ -55986,7 +56022,7 @@
       </c>
       <c r="H914" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>typique</t>
         </is>
       </c>
       <c r="I914" s="2" t="inlineStr">
@@ -55996,25 +56032,29 @@
       </c>
       <c r="J914" s="3" t="inlineStr">
         <is>
-          <t>Friches et lisières vivaces médio-européennes, eutrophiles, mésohydriques à mésohygrophiles.</t>
+          <t>Bois, dans les régions de l'Est et du Midi.</t>
         </is>
       </c>
       <c r="K914" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-70396</t>
-        </is>
-      </c>
-      <c r="L914" s="3" t="inlineStr"/>
+          <t>https://www.tela-botanica.org/bdtfx-nn-68332</t>
+        </is>
+      </c>
+      <c r="L914" s="3" t="inlineStr">
+        <is>
+          <t>assez rare à l'état naturel, surtout dans l'Est et le Midi</t>
+        </is>
+      </c>
     </row>
     <row r="915">
       <c r="A915" s="2" t="inlineStr">
         <is>
-          <t>Valeriana officinalis</t>
+          <t>Tilia platyphyllos</t>
         </is>
       </c>
       <c r="B915" s="2" t="inlineStr">
         <is>
-          <t>Valériane officinale</t>
+          <t>Tilleul à grandes feuilles</t>
         </is>
       </c>
       <c r="C915" s="2" t="inlineStr">
@@ -56024,27 +56064,27 @@
       </c>
       <c r="D915" s="2" t="inlineStr">
         <is>
-          <t>Forêts et sous-bois</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E915" s="2" t="inlineStr">
         <is>
-          <t>Forêts de feuillus caducs</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F915" s="2" t="inlineStr">
         <is>
-          <t>FOR-01</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G915" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H915" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I915" s="2" t="inlineStr">
@@ -56054,54 +56094,54 @@
       </c>
       <c r="J915" s="3" t="inlineStr">
         <is>
-          <t>Bois humides, bords des ruisseaux, dans presque toute la France.</t>
+          <t>Assez rare à l'état naturel, on le trouve surtout planté en haie ou isolé dans les parcs et le long des avenues.</t>
         </is>
       </c>
       <c r="K915" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-70592-synthese</t>
+          <t>https://www.tela-botanica.org/eflore/consultation/index_mobile.php?module=mobile&amp;referentiel=bdtfx&amp;num_nom=68332</t>
         </is>
       </c>
       <c r="L915" s="3" t="inlineStr">
         <is>
-          <t>nulle dans la région méditerranéenne</t>
+          <t>assez rare à l'état naturel, surtout dans l'Est et le Midi</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" s="2" t="inlineStr">
         <is>
-          <t>Valeriana officinalis</t>
+          <t>Tilia tomentosa</t>
         </is>
       </c>
       <c r="B916" s="2" t="inlineStr">
         <is>
-          <t>Valériane officinale</t>
+          <t>Tilleul argenté</t>
         </is>
       </c>
       <c r="C916" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>exotique (cultivée en France)</t>
         </is>
       </c>
       <c r="D916" s="2" t="inlineStr">
         <is>
-          <t>Mares, rivières et berges</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E916" s="2" t="inlineStr">
         <is>
-          <t>Berges et zones littorales d'eau douce</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F916" s="2" t="inlineStr">
         <is>
-          <t>EAU-03</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G916" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H916" s="2" t="inlineStr">
@@ -56116,59 +56156,59 @@
       </c>
       <c r="J916" s="3" t="inlineStr">
         <is>
-          <t>Bois humides, bords des ruisseaux, dans presque toute la France.</t>
+          <t>Résistant bien à la pollution, il est souvent employé comme arbre d'alignement dans les villes.</t>
         </is>
       </c>
       <c r="K916" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-70592-synthese</t>
+          <t>https://fr.wikipedia.org/wiki/Tilleul_argent%C3%A9</t>
         </is>
       </c>
       <c r="L916" s="3" t="inlineStr">
         <is>
-          <t>nulle dans la région méditerranéenne</t>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" s="2" t="inlineStr">
         <is>
-          <t>Valeriana officinalis</t>
+          <t>Tilia × euchlora</t>
         </is>
       </c>
       <c r="B917" s="2" t="inlineStr">
         <is>
-          <t>Valériane officinale</t>
+          <t>Tilleul de Crimée</t>
         </is>
       </c>
       <c r="C917" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>exotique (cultivée en France)</t>
         </is>
       </c>
       <c r="D917" s="2" t="inlineStr">
         <is>
-          <t>Prairies et pelouses</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E917" s="2" t="inlineStr">
         <is>
-          <t>Prairies humides</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F917" s="2" t="inlineStr">
         <is>
-          <t>PRA-03</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G917" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H917" s="2" t="inlineStr">
         <is>
-          <t>possible</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I917" s="2" t="inlineStr">
@@ -56178,34 +56218,34 @@
       </c>
       <c r="J917" s="3" t="inlineStr">
         <is>
-          <t>Prairies humides et bords des eaux (pour la subsp. sambucifolia).</t>
+          <t>Espèce exotique (origine : Crimée, Caucase), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
         </is>
       </c>
       <c r="K917" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-70601</t>
+          <t>https://www.rhs.org.uk/plants/92313/tilia-x-euchlora/details</t>
         </is>
       </c>
       <c r="L917" s="3" t="inlineStr">
         <is>
-          <t>nulle dans la région méditerranéenne</t>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" s="2" t="inlineStr">
         <is>
-          <t>Verbascum thapsus</t>
+          <t>Trachelospermum jasminoides</t>
         </is>
       </c>
       <c r="B918" s="2" t="inlineStr">
         <is>
-          <t>Molène bouillon-blanc</t>
+          <t>Jasmin étoilé</t>
         </is>
       </c>
       <c r="C918" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>exotique (cultivée en France)</t>
         </is>
       </c>
       <c r="D918" s="2" t="inlineStr">
@@ -56215,22 +56255,22 @@
       </c>
       <c r="E918" s="2" t="inlineStr">
         <is>
-          <t>Murs, friches et espaces très artificialisés</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F918" s="2" t="inlineStr">
         <is>
-          <t>HAB-03</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G918" s="2" t="inlineStr">
         <is>
-          <t>spontané (milieu secondaire)</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H918" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I918" s="2" t="inlineStr">
@@ -56240,50 +56280,54 @@
       </c>
       <c r="J918" s="3" t="inlineStr">
         <is>
-          <t>Écologie : lieux incultes, dans toute la France et en Corse.</t>
+          <t>Espèce exotique (origine : Chine, Japon, Corée, Vietnam), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
         </is>
       </c>
       <c r="K918" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-70991</t>
-        </is>
-      </c>
-      <c r="L918" s="3" t="inlineStr"/>
+          <t>https://www.rhs.org.uk/plants/18287/trachelospermum-jasminoides/details</t>
+        </is>
+      </c>
+      <c r="L918" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+        </is>
+      </c>
     </row>
     <row r="919">
       <c r="A919" s="2" t="inlineStr">
         <is>
-          <t>Verbascum thapsus</t>
+          <t>Trachycarpus fortunei</t>
         </is>
       </c>
       <c r="B919" s="2" t="inlineStr">
         <is>
-          <t>Molène bouillon-blanc</t>
+          <t>Palmier de Chine</t>
         </is>
       </c>
       <c r="C919" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>exotique (cultivée en France)</t>
         </is>
       </c>
       <c r="D919" s="2" t="inlineStr">
         <is>
-          <t>Rochers, éboulis et sols superficiels</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E919" s="2" t="inlineStr">
         <is>
-          <t>Sols nus ou à végétation clairsemée</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F919" s="2" t="inlineStr">
         <is>
-          <t>ROC-03</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G919" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H919" s="2" t="inlineStr">
@@ -56298,55 +56342,59 @@
       </c>
       <c r="J919" s="3" t="inlineStr">
         <is>
-          <t>Les graines germent presque exclusivement sur sol nu, en pleine lumière.</t>
+          <t>Espèce exotique (origine : Chine, Himalaya), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
         </is>
       </c>
       <c r="K919" s="2" t="inlineStr">
         <is>
-          <t>https://fr.wikipedia.org/wiki/Bouillon-blanc</t>
-        </is>
-      </c>
-      <c r="L919" s="3" t="inlineStr"/>
+          <t>https://www.rhs.org.uk/plants/18291/Trachycarpus-fortunei/Details</t>
+        </is>
+      </c>
+      <c r="L919" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+        </is>
+      </c>
     </row>
     <row r="920">
       <c r="A920" s="2" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Tradescantia virginiana</t>
         </is>
       </c>
       <c r="B920" s="2" t="inlineStr">
         <is>
-          <t>Véronique en épi</t>
+          <t>Misère</t>
         </is>
       </c>
       <c r="C920" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>exotique (cultivée en France)</t>
         </is>
       </c>
       <c r="D920" s="2" t="inlineStr">
         <is>
-          <t>Prairies et pelouses</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E920" s="2" t="inlineStr">
         <is>
-          <t>Pelouses et prairies sèches</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F920" s="2" t="inlineStr">
         <is>
-          <t>PRA-01</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G920" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H920" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I920" s="2" t="inlineStr">
@@ -56356,25 +56404,29 @@
       </c>
       <c r="J920" s="3" t="inlineStr">
         <is>
-          <t>Écologie : pelouses sèches dans une grande partie de la France, manque dans l'Ouest et la région méditerranéenne.</t>
+          <t>Espèce exotique (origine : Est des États-Unis), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
         </is>
       </c>
       <c r="K920" s="2" t="inlineStr">
         <is>
-          <t>https://tela-botanica.org/eflore/?action=fiche&amp;module=fiche&amp;num_nom=75432&amp;onglet=synthese&amp;referentiel=bdtfx</t>
-        </is>
-      </c>
-      <c r="L920" s="3" t="inlineStr"/>
+          <t>https://www.rhs.org.uk/plants/18305/wd/details</t>
+        </is>
+      </c>
+      <c r="L920" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+        </is>
+      </c>
     </row>
     <row r="921">
       <c r="A921" s="2" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Trifolium repens</t>
         </is>
       </c>
       <c r="B921" s="2" t="inlineStr">
         <is>
-          <t>Véronique en épi</t>
+          <t>Trèfle blanc</t>
         </is>
       </c>
       <c r="C921" s="2" t="inlineStr">
@@ -56389,12 +56441,12 @@
       </c>
       <c r="E921" s="2" t="inlineStr">
         <is>
-          <t>Pelouses alpines et subalpines</t>
+          <t>Prairies mésophiles</t>
         </is>
       </c>
       <c r="F921" s="2" t="inlineStr">
         <is>
-          <t>PRA-04</t>
+          <t>PRA-02</t>
         </is>
       </c>
       <c r="G921" s="2" t="inlineStr">
@@ -56404,7 +56456,7 @@
       </c>
       <c r="H921" s="2" t="inlineStr">
         <is>
-          <t>possible</t>
+          <t>typique</t>
         </is>
       </c>
       <c r="I921" s="2" t="inlineStr">
@@ -56414,12 +56466,12 @@
       </c>
       <c r="J921" s="3" t="inlineStr">
         <is>
-          <t>Espèce caractéristique des pelouses sèches des Festuco-Brometea, surtout en montagne (100 à 2050 m).</t>
+          <t>Prairies mésohydriques européennes, pâturées, planitiaires à montagnardes (Trifolio repentis - Cynosuretalia cristati).</t>
         </is>
       </c>
       <c r="K921" s="2" t="inlineStr">
         <is>
-          <t>https://inpn.mnhn.fr/espece/cd_nom/129007/tab/habitats</t>
+          <t>https://www.tela-botanica.org/bdtfx-nn-69341</t>
         </is>
       </c>
       <c r="L921" s="3" t="inlineStr"/>
@@ -56427,12 +56479,12 @@
     <row r="922">
       <c r="A922" s="2" t="inlineStr">
         <is>
-          <t>Viburnum tinus</t>
+          <t>Trifolium repens</t>
         </is>
       </c>
       <c r="B922" s="2" t="inlineStr">
         <is>
-          <t>Laurier-tin</t>
+          <t>Trèfle blanc</t>
         </is>
       </c>
       <c r="C922" s="2" t="inlineStr">
@@ -56442,27 +56494,27 @@
       </c>
       <c r="D922" s="2" t="inlineStr">
         <is>
-          <t>Forêts et sous-bois</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E922" s="2" t="inlineStr">
         <is>
-          <t>Boisements de feuillus sempervirents</t>
+          <t>Murs, friches et espaces très artificialisés</t>
         </is>
       </c>
       <c r="F922" s="2" t="inlineStr">
         <is>
-          <t>FOR-02</t>
+          <t>HAB-03</t>
         </is>
       </c>
       <c r="G922" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>spontané (milieu secondaire)</t>
         </is>
       </c>
       <c r="H922" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I922" s="2" t="inlineStr">
@@ -56472,29 +56524,25 @@
       </c>
       <c r="J922" s="3" t="inlineStr">
         <is>
-          <t>Espèce type des chênaies vertes.</t>
+          <t>Colonise les prairies, pelouses fraîches, champs cultivés, pâturages, lieux piétinés, friches et talus, jusqu'à 2500 m.</t>
         </is>
       </c>
       <c r="K922" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/eflore/consultation/index_mobile.php?module=mobile&amp;referentiel=bdtfx&amp;num_nom=71463</t>
-        </is>
-      </c>
-      <c r="L922" s="3" t="inlineStr">
-        <is>
-          <t>limité au Midi méditerranéen et à la Corse, naturalisé dans le Sud-Ouest</t>
-        </is>
-      </c>
+          <t>https://inpn.mnhn.fr/espece/cd_nom/127454</t>
+        </is>
+      </c>
+      <c r="L922" s="3" t="inlineStr"/>
     </row>
     <row r="923">
       <c r="A923" s="2" t="inlineStr">
         <is>
-          <t>Viburnum tinus</t>
+          <t>Trifolium repens</t>
         </is>
       </c>
       <c r="B923" s="2" t="inlineStr">
         <is>
-          <t>Laurier-tin</t>
+          <t>Trèfle blanc</t>
         </is>
       </c>
       <c r="C923" s="2" t="inlineStr">
@@ -56504,27 +56552,27 @@
       </c>
       <c r="D923" s="2" t="inlineStr">
         <is>
-          <t>Landes, bruyères et fourrés méditerranéens</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E923" s="2" t="inlineStr">
         <is>
-          <t>Maquis et fourrés méditerranéens</t>
+          <t>Cultures et jardins productifs</t>
         </is>
       </c>
       <c r="F923" s="2" t="inlineStr">
         <is>
-          <t>LAN-02</t>
+          <t>HAB-02</t>
         </is>
       </c>
       <c r="G923" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>spontané (milieu secondaire)</t>
         </is>
       </c>
       <c r="H923" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>possible</t>
         </is>
       </c>
       <c r="I923" s="2" t="inlineStr">
@@ -56534,59 +56582,55 @@
       </c>
       <c r="J923" s="3" t="inlineStr">
         <is>
-          <t>Écologie : bois et garrigues du Midi, Provence, Languedoc, Roussillon, Corse.</t>
+          <t>Colonise aussi les champs cultivés.</t>
         </is>
       </c>
       <c r="K923" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-71463</t>
-        </is>
-      </c>
-      <c r="L923" s="3" t="inlineStr">
-        <is>
-          <t>limité au Midi méditerranéen et à la Corse, naturalisé dans le Sud-Ouest</t>
-        </is>
-      </c>
+          <t>https://inpn.mnhn.fr/espece/cd_nom/127454</t>
+        </is>
+      </c>
+      <c r="L923" s="3" t="inlineStr"/>
     </row>
     <row r="924">
       <c r="A924" s="2" t="inlineStr">
         <is>
-          <t>Viburnum × burkwoodii</t>
+          <t>Trollius europaeus</t>
         </is>
       </c>
       <c r="B924" s="2" t="inlineStr">
         <is>
-          <t>Viorne de Burkwood</t>
+          <t>Trolle d'Europe</t>
         </is>
       </c>
       <c r="C924" s="2" t="inlineStr">
         <is>
-          <t>exotique (cultivée en France)</t>
+          <t>indigène</t>
         </is>
       </c>
       <c r="D924" s="2" t="inlineStr">
         <is>
-          <t>Jardins et paysages façonnés</t>
+          <t>Prairies et pelouses</t>
         </is>
       </c>
       <c r="E924" s="2" t="inlineStr">
         <is>
-          <t>Jardins, parcs et plantes ornementales</t>
+          <t>Prairies humides</t>
         </is>
       </c>
       <c r="F924" s="2" t="inlineStr">
         <is>
-          <t>HAB-01</t>
+          <t>PRA-03</t>
         </is>
       </c>
       <c r="G924" s="2" t="inlineStr">
         <is>
-          <t>cultivé ou planté</t>
+          <t>naturel</t>
         </is>
       </c>
       <c r="H924" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>typique</t>
         </is>
       </c>
       <c r="I924" s="2" t="inlineStr">
@@ -56596,29 +56640,29 @@
       </c>
       <c r="J924" s="3" t="inlineStr">
         <is>
-          <t>Espèce exotique (origine : hybride horticole (V. carlesii × V. utile)), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+          <t>Espèce caractéristique des prairies à Molinia caerulea et des prairies atlantiques humides.</t>
         </is>
       </c>
       <c r="K924" s="2" t="inlineStr">
         <is>
-          <t>https://www.rhs.org.uk/plants/91671/viburnum-x-burkwoodii/details</t>
+          <t>https://inpn.mnhn.fr/espece/cd_nom/127872/tab/habitats</t>
         </is>
       </c>
       <c r="L924" s="3" t="inlineStr">
         <is>
-          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+          <t>montagnard (Vosges, Jura, Alpes, Massif central, Pyrénées)</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" s="2" t="inlineStr">
         <is>
-          <t>Vinca minor</t>
+          <t>Trollius europaeus</t>
         </is>
       </c>
       <c r="B925" s="2" t="inlineStr">
         <is>
-          <t>Petite pervenche</t>
+          <t>Trolle d'Europe</t>
         </is>
       </c>
       <c r="C925" s="2" t="inlineStr">
@@ -56628,17 +56672,17 @@
       </c>
       <c r="D925" s="2" t="inlineStr">
         <is>
-          <t>Forêts et sous-bois</t>
+          <t>Prairies et pelouses</t>
         </is>
       </c>
       <c r="E925" s="2" t="inlineStr">
         <is>
-          <t>Forêts de feuillus caducs</t>
+          <t>Pelouses alpines et subalpines</t>
         </is>
       </c>
       <c r="F925" s="2" t="inlineStr">
         <is>
-          <t>FOR-01</t>
+          <t>PRA-04</t>
         </is>
       </c>
       <c r="G925" s="2" t="inlineStr">
@@ -56648,7 +56692,7 @@
       </c>
       <c r="H925" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I925" s="2" t="inlineStr">
@@ -56658,25 +56702,29 @@
       </c>
       <c r="J925" s="3" t="inlineStr">
         <is>
-          <t>Écologie : bois, haies et rochers dans toute la France, sous-bois herbacés médio-européens planitiaires à montagnards.</t>
+          <t>Écologie : prairies et pâturages des montagnes (Vosges, Jura, Alpes, Auvergne, Pyrénées).</t>
         </is>
       </c>
       <c r="K925" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-71984</t>
-        </is>
-      </c>
-      <c r="L925" s="3" t="inlineStr"/>
+          <t>https://www.tela-botanica.org/bdtfx-nn-75423-synthese?referentiel=bdtfx&amp;module=fiche&amp;action=fiche&amp;num_nom=75423&amp;niveau=3</t>
+        </is>
+      </c>
+      <c r="L925" s="3" t="inlineStr">
+        <is>
+          <t>montagnard (Vosges, Jura, Alpes, Massif central, Pyrénées)</t>
+        </is>
+      </c>
     </row>
     <row r="926">
       <c r="A926" s="2" t="inlineStr">
         <is>
-          <t>Vinca minor</t>
+          <t>Trollius europaeus</t>
         </is>
       </c>
       <c r="B926" s="2" t="inlineStr">
         <is>
-          <t>Petite pervenche</t>
+          <t>Trolle d'Europe</t>
         </is>
       </c>
       <c r="C926" s="2" t="inlineStr">
@@ -56686,17 +56734,17 @@
       </c>
       <c r="D926" s="2" t="inlineStr">
         <is>
-          <t>Haies, lisières et fourrés</t>
+          <t>Forêts et sous-bois</t>
         </is>
       </c>
       <c r="E926" s="2" t="inlineStr">
         <is>
-          <t>Haies et lignes d'arbres</t>
+          <t>Forêts de feuillus caducs</t>
         </is>
       </c>
       <c r="F926" s="2" t="inlineStr">
         <is>
-          <t>LIS-01</t>
+          <t>FOR-01</t>
         </is>
       </c>
       <c r="G926" s="2" t="inlineStr">
@@ -56706,7 +56754,7 @@
       </c>
       <c r="H926" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>possible</t>
         </is>
       </c>
       <c r="I926" s="2" t="inlineStr">
@@ -56716,55 +56764,59 @@
       </c>
       <c r="J926" s="3" t="inlineStr">
         <is>
-          <t>Écologie : bois, haies et rochers dans toute la France.</t>
+          <t>Plante des prairies humides et des bois clairs de montagne entre 500 et 2500 m.</t>
         </is>
       </c>
       <c r="K926" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-71984</t>
-        </is>
-      </c>
-      <c r="L926" s="3" t="inlineStr"/>
+          <t>https://fr.wikipedia.org/wiki/Trolle_d'Europe</t>
+        </is>
+      </c>
+      <c r="L926" s="3" t="inlineStr">
+        <is>
+          <t>montagnard (Vosges, Jura, Alpes, Massif central, Pyrénées)</t>
+        </is>
+      </c>
     </row>
     <row r="927">
       <c r="A927" s="2" t="inlineStr">
         <is>
-          <t>Viola odorata</t>
+          <t>Tsuga canadensis</t>
         </is>
       </c>
       <c r="B927" s="2" t="inlineStr">
         <is>
-          <t>Violette odorante</t>
+          <t>Pruche du Canada</t>
         </is>
       </c>
       <c r="C927" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>exotique (cultivée en France)</t>
         </is>
       </c>
       <c r="D927" s="2" t="inlineStr">
         <is>
-          <t>Haies, lisières et fourrés</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E927" s="2" t="inlineStr">
         <is>
-          <t>Haies et lignes d'arbres</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F927" s="2" t="inlineStr">
         <is>
-          <t>LIS-01</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G927" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H927" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I927" s="2" t="inlineStr">
@@ -56774,50 +56826,54 @@
       </c>
       <c r="J927" s="3" t="inlineStr">
         <is>
-          <t>Haies, bois, prés, dans toute la France et en Corse.</t>
+          <t>En Europe occidentale et centrale, on la plante dans les parcs à titre ornemental.</t>
         </is>
       </c>
       <c r="K927" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-72558</t>
-        </is>
-      </c>
-      <c r="L927" s="3" t="inlineStr"/>
+          <t>https://fr.wikipedia.org/wiki/Pruche_du_Canada</t>
+        </is>
+      </c>
+      <c r="L927" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+        </is>
+      </c>
     </row>
     <row r="928">
       <c r="A928" s="2" t="inlineStr">
         <is>
-          <t>Viola odorata</t>
+          <t>Tsuga heterophylla</t>
         </is>
       </c>
       <c r="B928" s="2" t="inlineStr">
         <is>
-          <t>Violette odorante</t>
+          <t>Pruche de l'Ouest</t>
         </is>
       </c>
       <c r="C928" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>exotique (cultivée en France)</t>
         </is>
       </c>
       <c r="D928" s="2" t="inlineStr">
         <is>
-          <t>Forêts et sous-bois</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E928" s="2" t="inlineStr">
         <is>
-          <t>Forêts de feuillus caducs</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F928" s="2" t="inlineStr">
         <is>
-          <t>FOR-01</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G928" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H928" s="2" t="inlineStr">
@@ -56832,50 +56888,54 @@
       </c>
       <c r="J928" s="3" t="inlineStr">
         <is>
-          <t>Haies, bois, prés, dans toute la France et en Corse.</t>
+          <t>On le cultive dans la partie occidentale de l'Europe pour son bois, mais en Europe centrale on ne le plante qu'à titre ornemental dans des parcs.</t>
         </is>
       </c>
       <c r="K928" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-72558</t>
-        </is>
-      </c>
-      <c r="L928" s="3" t="inlineStr"/>
+          <t>https://fr.wikipedia.org/wiki/Pruche_de_l%27Ouest</t>
+        </is>
+      </c>
+      <c r="L928" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10) - aussi cultivé pour son bois en Europe occidentale</t>
+        </is>
+      </c>
     </row>
     <row r="929">
       <c r="A929" s="2" t="inlineStr">
         <is>
-          <t>Viola odorata</t>
+          <t>Tsuga heterophylla</t>
         </is>
       </c>
       <c r="B929" s="2" t="inlineStr">
         <is>
-          <t>Violette odorante</t>
+          <t>Pruche de l'Ouest</t>
         </is>
       </c>
       <c r="C929" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>exotique (cultivée en France)</t>
         </is>
       </c>
       <c r="D929" s="2" t="inlineStr">
         <is>
-          <t>Prairies et pelouses</t>
+          <t>Forêts et sous-bois</t>
         </is>
       </c>
       <c r="E929" s="2" t="inlineStr">
         <is>
-          <t>Prairies mésophiles</t>
+          <t>Forêts de conifères</t>
         </is>
       </c>
       <c r="F929" s="2" t="inlineStr">
         <is>
-          <t>PRA-02</t>
+          <t>FOR-03</t>
         </is>
       </c>
       <c r="G929" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H929" s="2" t="inlineStr">
@@ -56890,55 +56950,59 @@
       </c>
       <c r="J929" s="3" t="inlineStr">
         <is>
-          <t>Haies, bois, prés, dans toute la France et en Corse.</t>
+          <t>On le cultive dans la partie occidentale de l'Europe pour son bois.</t>
         </is>
       </c>
       <c r="K929" s="2" t="inlineStr">
         <is>
-          <t>https://www.tela-botanica.org/bdtfx-nn-72558</t>
-        </is>
-      </c>
-      <c r="L929" s="3" t="inlineStr"/>
+          <t>https://fr.wikipedia.org/wiki/Pruche_de_l%27Ouest</t>
+        </is>
+      </c>
+      <c r="L929" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10) - aussi cultivé pour son bois en Europe occidentale</t>
+        </is>
+      </c>
     </row>
     <row r="930">
       <c r="A930" s="2" t="inlineStr">
         <is>
-          <t>Vitex agnus-castus</t>
+          <t>Tulbaghia violacea</t>
         </is>
       </c>
       <c r="B930" s="2" t="inlineStr">
         <is>
-          <t>Gattilier</t>
+          <t>Ail du Cap</t>
         </is>
       </c>
       <c r="C930" s="2" t="inlineStr">
         <is>
-          <t>indigène</t>
+          <t>exotique (cultivée en France)</t>
         </is>
       </c>
       <c r="D930" s="2" t="inlineStr">
         <is>
-          <t>Mares, rivières et berges</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E930" s="2" t="inlineStr">
         <is>
-          <t>Berges et zones littorales d'eau douce</t>
+          <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
       <c r="F930" s="2" t="inlineStr">
         <is>
-          <t>EAU-03</t>
+          <t>HAB-01</t>
         </is>
       </c>
       <c r="G930" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>cultivé ou planté</t>
         </is>
       </c>
       <c r="H930" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I930" s="2" t="inlineStr">
@@ -56948,29 +57012,29 @@
       </c>
       <c r="J930" s="3" t="inlineStr">
         <is>
-          <t>Fourrés de gattiliers (CORINE 44.812) : cours d'eau temporaires et sites humides de l'étage thermoméditerranéen ; rares en Provence orientale et en Corse.</t>
+          <t>Tulbaghia violacea est une espèce de plantes à fleurs de la famille des Amaryllidaceae cultivée pour son intérêt ornemental.</t>
         </is>
       </c>
       <c r="K930" s="2" t="inlineStr">
         <is>
-          <t>https://inpn.mnhn.fr/habitat/cd_hab/10162/tab/description?lg=en</t>
+          <t>https://fr.wikipedia.org/wiki/Tulbaghia_violacea</t>
         </is>
       </c>
       <c r="L930" s="3" t="inlineStr">
         <is>
-          <t>rare en France</t>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
         </is>
       </c>
     </row>
     <row r="931">
       <c r="A931" s="2" t="inlineStr">
         <is>
-          <t>Vitex agnus-castus</t>
+          <t>Tussilago farfara</t>
         </is>
       </c>
       <c r="B931" s="2" t="inlineStr">
         <is>
-          <t>Gattilier</t>
+          <t>Tussilage</t>
         </is>
       </c>
       <c r="C931" s="2" t="inlineStr">
@@ -56980,27 +57044,27 @@
       </c>
       <c r="D931" s="2" t="inlineStr">
         <is>
-          <t>Landes, bruyères et fourrés méditerranéens</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E931" s="2" t="inlineStr">
         <is>
-          <t>Maquis et fourrés méditerranéens</t>
+          <t>Murs, friches et espaces très artificialisés</t>
         </is>
       </c>
       <c r="F931" s="2" t="inlineStr">
         <is>
-          <t>LAN-02</t>
+          <t>HAB-03</t>
         </is>
       </c>
       <c r="G931" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>spontané (milieu secondaire)</t>
         </is>
       </c>
       <c r="H931" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>typique</t>
         </is>
       </c>
       <c r="I931" s="2" t="inlineStr">
@@ -57010,29 +57074,25 @@
       </c>
       <c r="J931" s="3" t="inlineStr">
         <is>
-          <t>F9.31 « Galeries à Nerium oleander, Vitex agnus-castus et Tamarix » (EUNIS 2012).</t>
+          <t>Elle est typique des sols instables riches en bases : terrains vagues et remués, pionnière des chemins et des talus.</t>
         </is>
       </c>
       <c r="K931" s="2" t="inlineStr">
         <is>
-          <t>https://inpn.mnhn.fr/habitat/cd_hab/5366</t>
-        </is>
-      </c>
-      <c r="L931" s="3" t="inlineStr">
-        <is>
-          <t>rare en France</t>
-        </is>
-      </c>
+          <t>https://fr.wikipedia.org/wiki/Tussilage</t>
+        </is>
+      </c>
+      <c r="L931" s="3" t="inlineStr"/>
     </row>
     <row r="932">
       <c r="A932" s="2" t="inlineStr">
         <is>
-          <t>Vitis vinifera</t>
+          <t>Tussilago farfara</t>
         </is>
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>Vigne cultivée</t>
+          <t>Tussilage</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -57042,27 +57102,27 @@
       </c>
       <c r="D932" s="2" t="inlineStr">
         <is>
-          <t>Forêts et sous-bois</t>
+          <t>Jardins et paysages façonnés</t>
         </is>
       </c>
       <c r="E932" s="2" t="inlineStr">
         <is>
-          <t>Forêts de feuillus caducs</t>
+          <t>Cultures et jardins productifs</t>
         </is>
       </c>
       <c r="F932" s="2" t="inlineStr">
         <is>
-          <t>FOR-01</t>
+          <t>HAB-02</t>
         </is>
       </c>
       <c r="G932" s="2" t="inlineStr">
         <is>
-          <t>naturel</t>
+          <t>spontané (milieu secondaire)</t>
         </is>
       </c>
       <c r="H932" s="2" t="inlineStr">
         <is>
-          <t>typique</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="I932" s="2" t="inlineStr">
@@ -57072,59 +57132,55 @@
       </c>
       <c r="J932" s="3" t="inlineStr">
         <is>
-          <t>Forêts alluviales le long des cours d'eau, sur sols frais neutres à calcaires, jusqu'à 600 m environ.</t>
+          <t>Le Tussilage est une espèce pionnière des chemins, champs, rives et talus, jachères, toujours sur sols remués ou instables.</t>
         </is>
       </c>
       <c r="K932" s="2" t="inlineStr">
         <is>
-          <t>https://inpn.mnhn.fr/espece/cd_nom/142451</t>
-        </is>
-      </c>
-      <c r="L932" s="3" t="inlineStr">
-        <is>
-          <t>écologie donnée pour la subsp. sylvestris (vigne sauvage rare) - la culture de la vigne n'est pas sourcée ici</t>
-        </is>
-      </c>
+          <t>https://fr.wikipedia.org/wiki/Tussilage</t>
+        </is>
+      </c>
+      <c r="L932" s="3" t="inlineStr"/>
     </row>
     <row r="933">
       <c r="A933" s="2" t="inlineStr">
         <is>
-          <t>Washingtonia filifera</t>
+          <t>Tussilago farfara</t>
         </is>
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>Palmier de Californie</t>
+          <t>Tussilage</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
         <is>
-          <t>exotique (cultivée en France)</t>
+          <t>indigène</t>
         </is>
       </c>
       <c r="D933" s="2" t="inlineStr">
         <is>
-          <t>Jardins et paysages façonnés</t>
+          <t>Marais, prairies humides et tourbières</t>
         </is>
       </c>
       <c r="E933" s="2" t="inlineStr">
         <is>
-          <t>Jardins, parcs et plantes ornementales</t>
+          <t>Bas-marais, tourbières de transition et marais tourbeux</t>
         </is>
       </c>
       <c r="F933" s="2" t="inlineStr">
         <is>
-          <t>HAB-01</t>
+          <t>HUM-02</t>
         </is>
       </c>
       <c r="G933" s="2" t="inlineStr">
         <is>
-          <t>cultivé ou planté</t>
+          <t>naturel</t>
         </is>
       </c>
       <c r="H933" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>possible</t>
         </is>
       </c>
       <c r="I933" s="2" t="inlineStr">
@@ -57134,59 +57190,55 @@
       </c>
       <c r="J933" s="3" t="inlineStr">
         <is>
-          <t>Espèce exotique (origine : Sud-Ouest des États-Unis (Californie, Arizona), Basse-Californie), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+          <t>Il apprécie également les sols ruisselants marneux ou tourbeux à Scirpe pauciflore (Caricion davallianae) où il devient volontiers dominant.</t>
         </is>
       </c>
       <c r="K933" s="2" t="inlineStr">
         <is>
-          <t>https://gardenerspath.com/plants/landscape-trees/grow-california-fan-palm/</t>
-        </is>
-      </c>
-      <c r="L933" s="3" t="inlineStr">
-        <is>
-          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
-        </is>
-      </c>
+          <t>https://fr.wikipedia.org/wiki/Tussilage</t>
+        </is>
+      </c>
+      <c r="L933" s="3" t="inlineStr"/>
     </row>
     <row r="934">
       <c r="A934" s="2" t="inlineStr">
         <is>
-          <t>Weigela florida</t>
+          <t>Typha latifolia</t>
         </is>
       </c>
       <c r="B934" s="2" t="inlineStr">
         <is>
-          <t>Weigela</t>
+          <t>Massette à larges feuilles</t>
         </is>
       </c>
       <c r="C934" s="2" t="inlineStr">
         <is>
-          <t>exotique (cultivée en France)</t>
+          <t>indigène</t>
         </is>
       </c>
       <c r="D934" s="2" t="inlineStr">
         <is>
-          <t>Jardins et paysages façonnés</t>
+          <t>Marais, prairies humides et tourbières</t>
         </is>
       </c>
       <c r="E934" s="2" t="inlineStr">
         <is>
-          <t>Jardins, parcs et plantes ornementales</t>
+          <t>Roselières et végétations palustres</t>
         </is>
       </c>
       <c r="F934" s="2" t="inlineStr">
         <is>
-          <t>HAB-01</t>
+          <t>HUM-04</t>
         </is>
       </c>
       <c r="G934" s="2" t="inlineStr">
         <is>
-          <t>cultivé ou planté</t>
+          <t>naturel</t>
         </is>
       </c>
       <c r="H934" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>typique</t>
         </is>
       </c>
       <c r="I934" s="2" t="inlineStr">
@@ -57196,54 +57248,50 @@
       </c>
       <c r="J934" s="3" t="inlineStr">
         <is>
-          <t>Espèce exotique (origine : Chine du Nord, Corée, Japon), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+          <t>Forme des colonies denses dans les roselières, sur sols très humides à marécageux près des eaux douces.</t>
         </is>
       </c>
       <c r="K934" s="2" t="inlineStr">
         <is>
-          <t>https://www.rhs.org.uk/plants/101006/wd/details</t>
-        </is>
-      </c>
-      <c r="L934" s="3" t="inlineStr">
-        <is>
-          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
-        </is>
-      </c>
+          <t>https://fr.wikipedia.org/wiki/Massette_%C3%A0_larges_feuilles</t>
+        </is>
+      </c>
+      <c r="L934" s="3" t="inlineStr"/>
     </row>
     <row r="935">
       <c r="A935" s="2" t="inlineStr">
         <is>
-          <t>Wisteria sinensis</t>
+          <t>Typha latifolia</t>
         </is>
       </c>
       <c r="B935" s="2" t="inlineStr">
         <is>
-          <t>Glycine de Chine</t>
+          <t>Massette à larges feuilles</t>
         </is>
       </c>
       <c r="C935" s="2" t="inlineStr">
         <is>
-          <t>exotique (cultivée en France)</t>
+          <t>indigène</t>
         </is>
       </c>
       <c r="D935" s="2" t="inlineStr">
         <is>
-          <t>Jardins et paysages façonnés</t>
+          <t>Mares, rivières et berges</t>
         </is>
       </c>
       <c r="E935" s="2" t="inlineStr">
         <is>
-          <t>Jardins, parcs et plantes ornementales</t>
+          <t>Mares, étangs et plans d'eau</t>
         </is>
       </c>
       <c r="F935" s="2" t="inlineStr">
         <is>
-          <t>HAB-01</t>
+          <t>EAU-01</t>
         </is>
       </c>
       <c r="G935" s="2" t="inlineStr">
         <is>
-          <t>cultivé ou planté</t>
+          <t>naturel</t>
         </is>
       </c>
       <c r="H935" s="2" t="inlineStr">
@@ -57258,59 +57306,55 @@
       </c>
       <c r="J935" s="3" t="inlineStr">
         <is>
-          <t>Présente en France, cultivée en extérieur.</t>
+          <t>Écologie : mares, étangs et rivières, dans presque toute la France et en Corse.</t>
         </is>
       </c>
       <c r="K935" s="2" t="inlineStr">
         <is>
-          <t>https://tela-botanica.org/eflore/?action=fiche&amp;module=fiche&amp;num_nom=72992&amp;onglet=synthese&amp;referentiel=bdtfx</t>
-        </is>
-      </c>
-      <c r="L935" s="3" t="inlineStr">
-        <is>
-          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
-        </is>
-      </c>
+          <t>https://www.tela-botanica.org/eflore/?action=pdf-export&amp;module=pdf-export&amp;niveau=2&amp;num_nom=70154&amp;referentiel=bdtfx</t>
+        </is>
+      </c>
+      <c r="L935" s="3" t="inlineStr"/>
     </row>
     <row r="936">
       <c r="A936" s="2" t="inlineStr">
         <is>
-          <t>Yucca filamentosa</t>
+          <t>Ulex europaeus</t>
         </is>
       </c>
       <c r="B936" s="2" t="inlineStr">
         <is>
-          <t>Yucca filamenteux</t>
+          <t>Ajonc d'Europe</t>
         </is>
       </c>
       <c r="C936" s="2" t="inlineStr">
         <is>
-          <t>exotique (cultivée en France)</t>
+          <t>indigène</t>
         </is>
       </c>
       <c r="D936" s="2" t="inlineStr">
         <is>
-          <t>Jardins et paysages façonnés</t>
+          <t>Landes, bruyères et fourrés méditerranéens</t>
         </is>
       </c>
       <c r="E936" s="2" t="inlineStr">
         <is>
-          <t>Jardins, parcs et plantes ornementales</t>
+          <t>Landes tempérées à bruyères</t>
         </is>
       </c>
       <c r="F936" s="2" t="inlineStr">
         <is>
-          <t>HAB-01</t>
+          <t>LAN-01</t>
         </is>
       </c>
       <c r="G936" s="2" t="inlineStr">
         <is>
-          <t>cultivé ou planté</t>
+          <t>naturel</t>
         </is>
       </c>
       <c r="H936" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>typique</t>
         </is>
       </c>
       <c r="I936" s="2" t="inlineStr">
@@ -57320,59 +57364,55 @@
       </c>
       <c r="J936" s="3" t="inlineStr">
         <is>
-          <t>Espèce exotique (origine : Sud-Est des États-Unis), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+          <t>Écologie : landes et lieux stériles siliceux, surtout dans l'Ouest et le Centre ; rare dans le Midi.</t>
         </is>
       </c>
       <c r="K936" s="2" t="inlineStr">
         <is>
-          <t>https://plants.ces.ncsu.edu/plants/all/yucca-filamentosa/</t>
-        </is>
-      </c>
-      <c r="L936" s="3" t="inlineStr">
-        <is>
-          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
-        </is>
-      </c>
+          <t>https://www.tela-botanica.org/bdtfx-nn-70199-synthese</t>
+        </is>
+      </c>
+      <c r="L936" s="3" t="inlineStr"/>
     </row>
     <row r="937">
       <c r="A937" s="2" t="inlineStr">
         <is>
-          <t>Zantedeschia aethiopica</t>
+          <t>Ulex minor</t>
         </is>
       </c>
       <c r="B937" s="2" t="inlineStr">
         <is>
-          <t>Arum d'Éthiopie</t>
+          <t>Ajonc nain</t>
         </is>
       </c>
       <c r="C937" s="2" t="inlineStr">
         <is>
-          <t>exotique (cultivée en France)</t>
+          <t>indigène</t>
         </is>
       </c>
       <c r="D937" s="2" t="inlineStr">
         <is>
-          <t>Jardins et paysages façonnés</t>
+          <t>Landes, bruyères et fourrés méditerranéens</t>
         </is>
       </c>
       <c r="E937" s="2" t="inlineStr">
         <is>
-          <t>Jardins, parcs et plantes ornementales</t>
+          <t>Landes tempérées à bruyères</t>
         </is>
       </c>
       <c r="F937" s="2" t="inlineStr">
         <is>
-          <t>HAB-01</t>
+          <t>LAN-01</t>
         </is>
       </c>
       <c r="G937" s="2" t="inlineStr">
         <is>
-          <t>cultivé ou planté</t>
+          <t>naturel</t>
         </is>
       </c>
       <c r="H937" s="2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>typique</t>
         </is>
       </c>
       <c r="I937" s="2" t="inlineStr">
@@ -57382,84 +57422,3058 @@
       </c>
       <c r="J937" s="3" t="inlineStr">
         <is>
-          <t>Espèce exotique (origine : Afrique du Sud), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+          <t>Écologie : landes et lieux stériles siliceux, dans l'Ouest et le Centre, nul dans le Midi.</t>
         </is>
       </c>
       <c r="K937" s="2" t="inlineStr">
         <is>
-          <t>https://www.rhs.org.uk/plants/19190/zantedeschia-aethiopica/details</t>
+          <t>https://www.tela-botanica.org/bdtfx-nn-70223</t>
         </is>
       </c>
       <c r="L937" s="3" t="inlineStr">
         <is>
-          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+          <t>surtout dans l'Ouest et le Centre, absent du Midi</t>
         </is>
       </c>
     </row>
     <row r="938">
       <c r="A938" s="2" t="inlineStr">
         <is>
+          <t>Ulex minor</t>
+        </is>
+      </c>
+      <c r="B938" s="2" t="inlineStr">
+        <is>
+          <t>Ajonc nain</t>
+        </is>
+      </c>
+      <c r="C938" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D938" s="2" t="inlineStr">
+        <is>
+          <t>Marais, prairies humides et tourbières</t>
+        </is>
+      </c>
+      <c r="E938" s="2" t="inlineStr">
+        <is>
+          <t>Bas-marais, tourbières de transition et marais tourbeux</t>
+        </is>
+      </c>
+      <c r="F938" s="2" t="inlineStr">
+        <is>
+          <t>HUM-02</t>
+        </is>
+      </c>
+      <c r="G938" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H938" s="2" t="inlineStr">
+        <is>
+          <t>possible</t>
+        </is>
+      </c>
+      <c r="I938" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J938" s="3" t="inlineStr">
+        <is>
+          <t>Fréquent sur silice dans les landes humides et lieux incultes, surtout dans l'ouest et le centre de la France.</t>
+        </is>
+      </c>
+      <c r="K938" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/Ajonc_nain</t>
+        </is>
+      </c>
+      <c r="L938" s="3" t="inlineStr">
+        <is>
+          <t>surtout dans l'Ouest et le Centre, absent du Midi</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="2" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="B939" s="2" t="inlineStr">
+        <is>
+          <t>Orme de montagne</t>
+        </is>
+      </c>
+      <c r="C939" s="2" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="D939" s="2" t="inlineStr">
+        <is>
+          <t>Forêts et sous-bois</t>
+        </is>
+      </c>
+      <c r="E939" s="2" t="inlineStr">
+        <is>
+          <t>Forêts de feuillus caducs</t>
+        </is>
+      </c>
+      <c r="F939" s="2" t="inlineStr">
+        <is>
+          <t>FOR-01</t>
+        </is>
+      </c>
+      <c r="G939" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H939" s="2" t="inlineStr">
+        <is>
+          <t>typique</t>
+        </is>
+      </c>
+      <c r="I939" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J939" s="3" t="inlineStr">
+        <is>
+          <t>C'est un arbre forestier, spontané dans une grande partie de l'Europe, essentiellement à l'étage collinéen et en plaine dans la moitié nord et plutôt en montagne dans la moitié sud.</t>
+        </is>
+      </c>
+      <c r="K939" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/Orme_de_montagne</t>
+        </is>
+      </c>
+      <c r="L939" s="3" t="inlineStr">
+        <is>
+          <t>milieu décrit pour l'aire générale - plutôt en montagne dans la moitié sud de l'Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="2" t="inlineStr">
+        <is>
+          <t>Ulmus laevis</t>
+        </is>
+      </c>
+      <c r="B940" s="2" t="inlineStr">
+        <is>
+          <t>Orme lisse</t>
+        </is>
+      </c>
+      <c r="C940" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D940" s="2" t="inlineStr">
+        <is>
+          <t>Forêts et sous-bois</t>
+        </is>
+      </c>
+      <c r="E940" s="2" t="inlineStr">
+        <is>
+          <t>Forêts de feuillus caducs</t>
+        </is>
+      </c>
+      <c r="F940" s="2" t="inlineStr">
+        <is>
+          <t>FOR-01</t>
+        </is>
+      </c>
+      <c r="G940" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H940" s="2" t="inlineStr">
+        <is>
+          <t>typique</t>
+        </is>
+      </c>
+      <c r="I940" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J940" s="3" t="inlineStr">
+        <is>
+          <t>Forêts alluviales (Alnion glutinosae) et aulnaie-frênaie (Alno Padion), espèce de demi-ombre sur des matériaux alluviaux fins, limono-argileux et riches.</t>
+        </is>
+      </c>
+      <c r="K940" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/Ulmus_laevis</t>
+        </is>
+      </c>
+      <c r="L940" s="3" t="inlineStr">
+        <is>
+          <t>devenu rare à l'état naturel, absent notamment de la majeure partie du Midi méditerranéen et des Alpes</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="2" t="inlineStr">
+        <is>
+          <t>Ulmus minor</t>
+        </is>
+      </c>
+      <c r="B941" s="2" t="inlineStr">
+        <is>
+          <t>Orme champêtre</t>
+        </is>
+      </c>
+      <c r="C941" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D941" s="2" t="inlineStr">
+        <is>
+          <t>Haies, lisières et fourrés</t>
+        </is>
+      </c>
+      <c r="E941" s="2" t="inlineStr">
+        <is>
+          <t>Haies et lignes d'arbres</t>
+        </is>
+      </c>
+      <c r="F941" s="2" t="inlineStr">
+        <is>
+          <t>LIS-01</t>
+        </is>
+      </c>
+      <c r="G941" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H941" s="2" t="inlineStr">
+        <is>
+          <t>typique</t>
+        </is>
+      </c>
+      <c r="I941" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J941" s="3" t="inlineStr">
+        <is>
+          <t>Il est présent dans les haies, les forêts alluviales, les friches, les talus, les décombres.</t>
+        </is>
+      </c>
+      <c r="K941" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tela-botanica.org/eflore/consultation/index_mobile.php?module=mobile&amp;referentiel=bdtfx&amp;num_nom=70296</t>
+        </is>
+      </c>
+      <c r="L941" s="3" t="inlineStr">
+        <is>
+          <t>fortement décimé par la graphiose, souvent réduit à l'état d'arbuste</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="2" t="inlineStr">
+        <is>
+          <t>Ulmus minor</t>
+        </is>
+      </c>
+      <c r="B942" s="2" t="inlineStr">
+        <is>
+          <t>Orme champêtre</t>
+        </is>
+      </c>
+      <c r="C942" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D942" s="2" t="inlineStr">
+        <is>
+          <t>Forêts et sous-bois</t>
+        </is>
+      </c>
+      <c r="E942" s="2" t="inlineStr">
+        <is>
+          <t>Forêts de feuillus caducs</t>
+        </is>
+      </c>
+      <c r="F942" s="2" t="inlineStr">
+        <is>
+          <t>FOR-01</t>
+        </is>
+      </c>
+      <c r="G942" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H942" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I942" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J942" s="3" t="inlineStr">
+        <is>
+          <t>Présent dans les forêts alluviales, jusqu'à 1300 m d'altitude.</t>
+        </is>
+      </c>
+      <c r="K942" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tela-botanica.org/eflore/consultation/index_mobile.php?module=mobile&amp;referentiel=bdtfx&amp;num_nom=70296</t>
+        </is>
+      </c>
+      <c r="L942" s="3" t="inlineStr">
+        <is>
+          <t>fortement décimé par la graphiose, souvent réduit à l'état d'arbuste</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="2" t="inlineStr">
+        <is>
+          <t>Ulmus minor</t>
+        </is>
+      </c>
+      <c r="B943" s="2" t="inlineStr">
+        <is>
+          <t>Orme champêtre</t>
+        </is>
+      </c>
+      <c r="C943" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D943" s="2" t="inlineStr">
+        <is>
+          <t>Jardins et paysages façonnés</t>
+        </is>
+      </c>
+      <c r="E943" s="2" t="inlineStr">
+        <is>
+          <t>Murs, friches et espaces très artificialisés</t>
+        </is>
+      </c>
+      <c r="F943" s="2" t="inlineStr">
+        <is>
+          <t>HAB-03</t>
+        </is>
+      </c>
+      <c r="G943" s="2" t="inlineStr">
+        <is>
+          <t>spontané (milieu secondaire)</t>
+        </is>
+      </c>
+      <c r="H943" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I943" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J943" s="3" t="inlineStr">
+        <is>
+          <t>Présent dans les friches, les talus, les décombres.</t>
+        </is>
+      </c>
+      <c r="K943" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tela-botanica.org/eflore/consultation/index_mobile.php?module=mobile&amp;referentiel=bdtfx&amp;num_nom=70296</t>
+        </is>
+      </c>
+      <c r="L943" s="3" t="inlineStr">
+        <is>
+          <t>fortement décimé par la graphiose, souvent réduit à l'état d'arbuste</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="2" t="inlineStr">
+        <is>
+          <t>Ulmus parvifolia</t>
+        </is>
+      </c>
+      <c r="B944" s="2" t="inlineStr">
+        <is>
+          <t>Orme de Chine</t>
+        </is>
+      </c>
+      <c r="C944" s="2" t="inlineStr">
+        <is>
+          <t>exotique (cultivée en France)</t>
+        </is>
+      </c>
+      <c r="D944" s="2" t="inlineStr">
+        <is>
+          <t>Jardins et paysages façonnés</t>
+        </is>
+      </c>
+      <c r="E944" s="2" t="inlineStr">
+        <is>
+          <t>Jardins, parcs et plantes ornementales</t>
+        </is>
+      </c>
+      <c r="F944" s="2" t="inlineStr">
+        <is>
+          <t>HAB-01</t>
+        </is>
+      </c>
+      <c r="G944" s="2" t="inlineStr">
+        <is>
+          <t>cultivé ou planté</t>
+        </is>
+      </c>
+      <c r="H944" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I944" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J944" s="3" t="inlineStr">
+        <is>
+          <t>C'est une espèce horticole couramment utilisée dans la pratique du bonsaï.</t>
+        </is>
+      </c>
+      <c r="K944" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/Orme_de_Chine</t>
+        </is>
+      </c>
+      <c r="L944" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="2" t="inlineStr">
+        <is>
+          <t>Ulmus pumila</t>
+        </is>
+      </c>
+      <c r="B945" s="2" t="inlineStr">
+        <is>
+          <t>Orme de Sibérie</t>
+        </is>
+      </c>
+      <c r="C945" s="2" t="inlineStr">
+        <is>
+          <t>exotique (cultivée en France)</t>
+        </is>
+      </c>
+      <c r="D945" s="2" t="inlineStr">
+        <is>
+          <t>Jardins et paysages façonnés</t>
+        </is>
+      </c>
+      <c r="E945" s="2" t="inlineStr">
+        <is>
+          <t>Jardins, parcs et plantes ornementales</t>
+        </is>
+      </c>
+      <c r="F945" s="2" t="inlineStr">
+        <is>
+          <t>HAB-01</t>
+        </is>
+      </c>
+      <c r="G945" s="2" t="inlineStr">
+        <is>
+          <t>cultivé ou planté</t>
+        </is>
+      </c>
+      <c r="H945" s="2" t="inlineStr">
+        <is>
+          <t>possible</t>
+        </is>
+      </c>
+      <c r="I945" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J945" s="3" t="inlineStr">
+        <is>
+          <t>U. pumila a été introduit en Espagne comme plante ornementale, puis à partir des années 1930 en Italie.</t>
+        </is>
+      </c>
+      <c r="K945" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/Ulmus_pumila</t>
+        </is>
+      </c>
+      <c r="L945" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10) - culture citée pour l'Europe du Sud, France non citée</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="2" t="inlineStr">
+        <is>
+          <t>Urtica dioica</t>
+        </is>
+      </c>
+      <c r="B946" s="2" t="inlineStr">
+        <is>
+          <t>Ortie dioïque</t>
+        </is>
+      </c>
+      <c r="C946" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D946" s="2" t="inlineStr">
+        <is>
+          <t>Jardins et paysages façonnés</t>
+        </is>
+      </c>
+      <c r="E946" s="2" t="inlineStr">
+        <is>
+          <t>Murs, friches et espaces très artificialisés</t>
+        </is>
+      </c>
+      <c r="F946" s="2" t="inlineStr">
+        <is>
+          <t>HAB-03</t>
+        </is>
+      </c>
+      <c r="G946" s="2" t="inlineStr">
+        <is>
+          <t>spontané (milieu secondaire)</t>
+        </is>
+      </c>
+      <c r="H946" s="2" t="inlineStr">
+        <is>
+          <t>typique</t>
+        </is>
+      </c>
+      <c r="I946" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J946" s="3" t="inlineStr">
+        <is>
+          <t>Lieux incultes, dans toute la France et la Corse.</t>
+        </is>
+      </c>
+      <c r="K946" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tela-botanica.org/bdtfx-nn-70396</t>
+        </is>
+      </c>
+      <c r="L946" s="3" t="inlineStr"/>
+    </row>
+    <row r="947">
+      <c r="A947" s="2" t="inlineStr">
+        <is>
+          <t>Urtica dioica</t>
+        </is>
+      </c>
+      <c r="B947" s="2" t="inlineStr">
+        <is>
+          <t>Ortie dioïque</t>
+        </is>
+      </c>
+      <c r="C947" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D947" s="2" t="inlineStr">
+        <is>
+          <t>Haies, lisières et fourrés</t>
+        </is>
+      </c>
+      <c r="E947" s="2" t="inlineStr">
+        <is>
+          <t>Ourlets herbacés</t>
+        </is>
+      </c>
+      <c r="F947" s="2" t="inlineStr">
+        <is>
+          <t>PRA-05</t>
+        </is>
+      </c>
+      <c r="G947" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H947" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I947" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J947" s="3" t="inlineStr">
+        <is>
+          <t>Friches et lisières vivaces médio-européennes, eutrophiles, mésohydriques à mésohygrophiles.</t>
+        </is>
+      </c>
+      <c r="K947" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tela-botanica.org/bdtfx-nn-70396</t>
+        </is>
+      </c>
+      <c r="L947" s="3" t="inlineStr"/>
+    </row>
+    <row r="948">
+      <c r="A948" s="2" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="B948" s="2" t="inlineStr">
+        <is>
+          <t>Myrtille</t>
+        </is>
+      </c>
+      <c r="C948" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D948" s="2" t="inlineStr">
+        <is>
+          <t>Forêts et sous-bois</t>
+        </is>
+      </c>
+      <c r="E948" s="2" t="inlineStr">
+        <is>
+          <t>Forêts de conifères</t>
+        </is>
+      </c>
+      <c r="F948" s="2" t="inlineStr">
+        <is>
+          <t>FOR-03</t>
+        </is>
+      </c>
+      <c r="G948" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H948" s="2" t="inlineStr">
+        <is>
+          <t>typique</t>
+        </is>
+      </c>
+      <c r="I948" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J948" s="3" t="inlineStr">
+        <is>
+          <t>Elle croît dans les forêts de conifères, les bois clairs, les landes et les tourbières, associée aux plantes acidophiles.</t>
+        </is>
+      </c>
+      <c r="K948" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/Vaccinium_myrtillus</t>
+        </is>
+      </c>
+      <c r="L948" s="3" t="inlineStr"/>
+    </row>
+    <row r="949">
+      <c r="A949" s="2" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="B949" s="2" t="inlineStr">
+        <is>
+          <t>Myrtille</t>
+        </is>
+      </c>
+      <c r="C949" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D949" s="2" t="inlineStr">
+        <is>
+          <t>Landes, bruyères et fourrés méditerranéens</t>
+        </is>
+      </c>
+      <c r="E949" s="2" t="inlineStr">
+        <is>
+          <t>Landes tempérées à bruyères</t>
+        </is>
+      </c>
+      <c r="F949" s="2" t="inlineStr">
+        <is>
+          <t>LAN-01</t>
+        </is>
+      </c>
+      <c r="G949" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H949" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I949" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J949" s="3" t="inlineStr">
+        <is>
+          <t>Elle croît dans les forêts de conifères, les bois clairs, les landes et les tourbières, associée aux plantes acidophiles.</t>
+        </is>
+      </c>
+      <c r="K949" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/Vaccinium_myrtillus</t>
+        </is>
+      </c>
+      <c r="L949" s="3" t="inlineStr"/>
+    </row>
+    <row r="950">
+      <c r="A950" s="2" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="B950" s="2" t="inlineStr">
+        <is>
+          <t>Myrtille</t>
+        </is>
+      </c>
+      <c r="C950" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D950" s="2" t="inlineStr">
+        <is>
+          <t>Marais, prairies humides et tourbières</t>
+        </is>
+      </c>
+      <c r="E950" s="2" t="inlineStr">
+        <is>
+          <t>Tourbières hautes et bombées</t>
+        </is>
+      </c>
+      <c r="F950" s="2" t="inlineStr">
+        <is>
+          <t>HUM-01</t>
+        </is>
+      </c>
+      <c r="G950" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H950" s="2" t="inlineStr">
+        <is>
+          <t>possible</t>
+        </is>
+      </c>
+      <c r="I950" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J950" s="3" t="inlineStr">
+        <is>
+          <t>Elle croît dans les forêts de conifères, les bois clairs, les landes et les tourbières, associée aux plantes acidophiles.</t>
+        </is>
+      </c>
+      <c r="K950" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/Vaccinium_myrtillus</t>
+        </is>
+      </c>
+      <c r="L950" s="3" t="inlineStr"/>
+    </row>
+    <row r="951">
+      <c r="A951" s="2" t="inlineStr">
+        <is>
+          <t>Valeriana officinalis</t>
+        </is>
+      </c>
+      <c r="B951" s="2" t="inlineStr">
+        <is>
+          <t>Valériane officinale</t>
+        </is>
+      </c>
+      <c r="C951" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D951" s="2" t="inlineStr">
+        <is>
+          <t>Forêts et sous-bois</t>
+        </is>
+      </c>
+      <c r="E951" s="2" t="inlineStr">
+        <is>
+          <t>Forêts de feuillus caducs</t>
+        </is>
+      </c>
+      <c r="F951" s="2" t="inlineStr">
+        <is>
+          <t>FOR-01</t>
+        </is>
+      </c>
+      <c r="G951" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H951" s="2" t="inlineStr">
+        <is>
+          <t>typique</t>
+        </is>
+      </c>
+      <c r="I951" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J951" s="3" t="inlineStr">
+        <is>
+          <t>Bois humides, bords des ruisseaux, dans presque toute la France.</t>
+        </is>
+      </c>
+      <c r="K951" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tela-botanica.org/bdtfx-nn-70592-synthese</t>
+        </is>
+      </c>
+      <c r="L951" s="3" t="inlineStr">
+        <is>
+          <t>nulle dans la région méditerranéenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="2" t="inlineStr">
+        <is>
+          <t>Valeriana officinalis</t>
+        </is>
+      </c>
+      <c r="B952" s="2" t="inlineStr">
+        <is>
+          <t>Valériane officinale</t>
+        </is>
+      </c>
+      <c r="C952" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D952" s="2" t="inlineStr">
+        <is>
+          <t>Mares, rivières et berges</t>
+        </is>
+      </c>
+      <c r="E952" s="2" t="inlineStr">
+        <is>
+          <t>Berges et zones littorales d'eau douce</t>
+        </is>
+      </c>
+      <c r="F952" s="2" t="inlineStr">
+        <is>
+          <t>EAU-03</t>
+        </is>
+      </c>
+      <c r="G952" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H952" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I952" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J952" s="3" t="inlineStr">
+        <is>
+          <t>Bois humides, bords des ruisseaux, dans presque toute la France.</t>
+        </is>
+      </c>
+      <c r="K952" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tela-botanica.org/bdtfx-nn-70592-synthese</t>
+        </is>
+      </c>
+      <c r="L952" s="3" t="inlineStr">
+        <is>
+          <t>nulle dans la région méditerranéenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="2" t="inlineStr">
+        <is>
+          <t>Valeriana officinalis</t>
+        </is>
+      </c>
+      <c r="B953" s="2" t="inlineStr">
+        <is>
+          <t>Valériane officinale</t>
+        </is>
+      </c>
+      <c r="C953" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D953" s="2" t="inlineStr">
+        <is>
+          <t>Prairies et pelouses</t>
+        </is>
+      </c>
+      <c r="E953" s="2" t="inlineStr">
+        <is>
+          <t>Prairies humides</t>
+        </is>
+      </c>
+      <c r="F953" s="2" t="inlineStr">
+        <is>
+          <t>PRA-03</t>
+        </is>
+      </c>
+      <c r="G953" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H953" s="2" t="inlineStr">
+        <is>
+          <t>possible</t>
+        </is>
+      </c>
+      <c r="I953" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J953" s="3" t="inlineStr">
+        <is>
+          <t>Prairies humides et bords des eaux (pour la subsp. sambucifolia).</t>
+        </is>
+      </c>
+      <c r="K953" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tela-botanica.org/bdtfx-nn-70601</t>
+        </is>
+      </c>
+      <c r="L953" s="3" t="inlineStr">
+        <is>
+          <t>nulle dans la région méditerranéenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="2" t="inlineStr">
+        <is>
+          <t>Verbascum thapsus</t>
+        </is>
+      </c>
+      <c r="B954" s="2" t="inlineStr">
+        <is>
+          <t>Molène bouillon-blanc</t>
+        </is>
+      </c>
+      <c r="C954" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D954" s="2" t="inlineStr">
+        <is>
+          <t>Jardins et paysages façonnés</t>
+        </is>
+      </c>
+      <c r="E954" s="2" t="inlineStr">
+        <is>
+          <t>Murs, friches et espaces très artificialisés</t>
+        </is>
+      </c>
+      <c r="F954" s="2" t="inlineStr">
+        <is>
+          <t>HAB-03</t>
+        </is>
+      </c>
+      <c r="G954" s="2" t="inlineStr">
+        <is>
+          <t>spontané (milieu secondaire)</t>
+        </is>
+      </c>
+      <c r="H954" s="2" t="inlineStr">
+        <is>
+          <t>typique</t>
+        </is>
+      </c>
+      <c r="I954" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J954" s="3" t="inlineStr">
+        <is>
+          <t>Écologie : lieux incultes, dans toute la France et en Corse.</t>
+        </is>
+      </c>
+      <c r="K954" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tela-botanica.org/bdtfx-nn-70991</t>
+        </is>
+      </c>
+      <c r="L954" s="3" t="inlineStr"/>
+    </row>
+    <row r="955">
+      <c r="A955" s="2" t="inlineStr">
+        <is>
+          <t>Verbascum thapsus</t>
+        </is>
+      </c>
+      <c r="B955" s="2" t="inlineStr">
+        <is>
+          <t>Molène bouillon-blanc</t>
+        </is>
+      </c>
+      <c r="C955" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D955" s="2" t="inlineStr">
+        <is>
+          <t>Rochers, éboulis et sols superficiels</t>
+        </is>
+      </c>
+      <c r="E955" s="2" t="inlineStr">
+        <is>
+          <t>Sols nus ou à végétation clairsemée</t>
+        </is>
+      </c>
+      <c r="F955" s="2" t="inlineStr">
+        <is>
+          <t>ROC-03</t>
+        </is>
+      </c>
+      <c r="G955" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H955" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I955" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J955" s="3" t="inlineStr">
+        <is>
+          <t>Les graines germent presque exclusivement sur sol nu, en pleine lumière.</t>
+        </is>
+      </c>
+      <c r="K955" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/Bouillon-blanc</t>
+        </is>
+      </c>
+      <c r="L955" s="3" t="inlineStr"/>
+    </row>
+    <row r="956">
+      <c r="A956" s="2" t="inlineStr">
+        <is>
+          <t>Verbena bonariensis</t>
+        </is>
+      </c>
+      <c r="B956" s="2" t="inlineStr">
+        <is>
+          <t>Verveine de Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C956" s="2" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="D956" s="2" t="inlineStr">
+        <is>
+          <t>Jardins et paysages façonnés</t>
+        </is>
+      </c>
+      <c r="E956" s="2" t="inlineStr">
+        <is>
+          <t>Jardins, parcs et plantes ornementales</t>
+        </is>
+      </c>
+      <c r="F956" s="2" t="inlineStr">
+        <is>
+          <t>HAB-01</t>
+        </is>
+      </c>
+      <c r="G956" s="2" t="inlineStr">
+        <is>
+          <t>cultivé ou planté</t>
+        </is>
+      </c>
+      <c r="H956" s="2" t="inlineStr">
+        <is>
+          <t>typique</t>
+        </is>
+      </c>
+      <c r="I956" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J956" s="3" t="inlineStr">
+        <is>
+          <t>Elle est principalement utilisée dans les massifs et plates-bandes, où ses longues tiges élancées et ses inflorescences violettes apportent de la légèreté aux jardins.</t>
+        </is>
+      </c>
+      <c r="K956" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/Verveine_de_Buenos_Aires</t>
+        </is>
+      </c>
+      <c r="L956" s="3" t="inlineStr">
+        <is>
+          <t>naturalisée dans plusieurs pays d'Europe (Espagne, Italie, Allemagne, Royaume-Uni), France non citée - milieu d'origine non renseigné (règle R10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="2" t="inlineStr">
+        <is>
+          <t>Verbena officinalis</t>
+        </is>
+      </c>
+      <c r="B957" s="2" t="inlineStr">
+        <is>
+          <t>Verveine officinale</t>
+        </is>
+      </c>
+      <c r="C957" s="2" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="D957" s="2" t="inlineStr">
+        <is>
+          <t>Prairies et pelouses</t>
+        </is>
+      </c>
+      <c r="E957" s="2" t="inlineStr">
+        <is>
+          <t>Prairies mésophiles</t>
+        </is>
+      </c>
+      <c r="F957" s="2" t="inlineStr">
+        <is>
+          <t>PRA-02</t>
+        </is>
+      </c>
+      <c r="G957" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H957" s="2" t="inlineStr">
+        <is>
+          <t>typique</t>
+        </is>
+      </c>
+      <c r="I957" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J957" s="3" t="inlineStr">
+        <is>
+          <t>La verveine officinale indigène se trouve dans les prairies et au bord des chemins.</t>
+        </is>
+      </c>
+      <c r="K957" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/Verveine_officinale</t>
+        </is>
+      </c>
+      <c r="L957" s="3" t="inlineStr">
+        <is>
+          <t>le texte la dit indigène sans préciser la France</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="2" t="inlineStr">
+        <is>
+          <t>Verbena officinalis</t>
+        </is>
+      </c>
+      <c r="B958" s="2" t="inlineStr">
+        <is>
+          <t>Verveine officinale</t>
+        </is>
+      </c>
+      <c r="C958" s="2" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="D958" s="2" t="inlineStr">
+        <is>
+          <t>Jardins et paysages façonnés</t>
+        </is>
+      </c>
+      <c r="E958" s="2" t="inlineStr">
+        <is>
+          <t>Murs, friches et espaces très artificialisés</t>
+        </is>
+      </c>
+      <c r="F958" s="2" t="inlineStr">
+        <is>
+          <t>HAB-03</t>
+        </is>
+      </c>
+      <c r="G958" s="2" t="inlineStr">
+        <is>
+          <t>spontané (milieu secondaire)</t>
+        </is>
+      </c>
+      <c r="H958" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I958" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J958" s="3" t="inlineStr">
+        <is>
+          <t>La verveine officinale indigène se trouve dans les prairies et au bord des chemins.</t>
+        </is>
+      </c>
+      <c r="K958" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/Verveine_officinale</t>
+        </is>
+      </c>
+      <c r="L958" s="3" t="inlineStr">
+        <is>
+          <t>le texte la dit indigène sans préciser la France</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="2" t="inlineStr">
+        <is>
+          <t>Veronica chamaedrys</t>
+        </is>
+      </c>
+      <c r="B959" s="2" t="inlineStr">
+        <is>
+          <t>Véronique petit-chêne</t>
+        </is>
+      </c>
+      <c r="C959" s="2" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="D959" s="2" t="inlineStr">
+        <is>
+          <t>Prairies et pelouses</t>
+        </is>
+      </c>
+      <c r="E959" s="2" t="inlineStr">
+        <is>
+          <t>Prairies mésophiles</t>
+        </is>
+      </c>
+      <c r="F959" s="2" t="inlineStr">
+        <is>
+          <t>PRA-02</t>
+        </is>
+      </c>
+      <c r="G959" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H959" s="2" t="inlineStr">
+        <is>
+          <t>typique</t>
+        </is>
+      </c>
+      <c r="I959" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J959" s="3" t="inlineStr">
+        <is>
+          <t>Elle apprécie notamment les prés et les lieux boisés, où elle peut former d'importants tapis.</t>
+        </is>
+      </c>
+      <c r="K959" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/V%C3%A9ronique_petit-ch%C3%AAne</t>
+        </is>
+      </c>
+      <c r="L959" s="3" t="inlineStr">
+        <is>
+          <t>milieu décrit pour l'aire générale - souvent en montagne</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="2" t="inlineStr">
+        <is>
+          <t>Veronica chamaedrys</t>
+        </is>
+      </c>
+      <c r="B960" s="2" t="inlineStr">
+        <is>
+          <t>Véronique petit-chêne</t>
+        </is>
+      </c>
+      <c r="C960" s="2" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="D960" s="2" t="inlineStr">
+        <is>
+          <t>Forêts et sous-bois</t>
+        </is>
+      </c>
+      <c r="E960" s="2" t="inlineStr">
+        <is>
+          <t>Forêts de feuillus caducs</t>
+        </is>
+      </c>
+      <c r="F960" s="2" t="inlineStr">
+        <is>
+          <t>FOR-01</t>
+        </is>
+      </c>
+      <c r="G960" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H960" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I960" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J960" s="3" t="inlineStr">
+        <is>
+          <t>Fréquente dans les prés et les bois clairs, souvent en zones montagneuses.</t>
+        </is>
+      </c>
+      <c r="K960" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/V%C3%A9ronique_petit-ch%C3%AAne</t>
+        </is>
+      </c>
+      <c r="L960" s="3" t="inlineStr">
+        <is>
+          <t>milieu décrit pour l'aire générale - souvent en montagne</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="2" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="B961" s="2" t="inlineStr">
+        <is>
+          <t>Véronique en épi</t>
+        </is>
+      </c>
+      <c r="C961" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D961" s="2" t="inlineStr">
+        <is>
+          <t>Prairies et pelouses</t>
+        </is>
+      </c>
+      <c r="E961" s="2" t="inlineStr">
+        <is>
+          <t>Pelouses et prairies sèches</t>
+        </is>
+      </c>
+      <c r="F961" s="2" t="inlineStr">
+        <is>
+          <t>PRA-01</t>
+        </is>
+      </c>
+      <c r="G961" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H961" s="2" t="inlineStr">
+        <is>
+          <t>typique</t>
+        </is>
+      </c>
+      <c r="I961" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J961" s="3" t="inlineStr">
+        <is>
+          <t>Écologie : pelouses sèches dans une grande partie de la France, manque dans l'Ouest et la région méditerranéenne.</t>
+        </is>
+      </c>
+      <c r="K961" s="2" t="inlineStr">
+        <is>
+          <t>https://tela-botanica.org/eflore/?action=fiche&amp;module=fiche&amp;num_nom=75432&amp;onglet=synthese&amp;referentiel=bdtfx</t>
+        </is>
+      </c>
+      <c r="L961" s="3" t="inlineStr"/>
+    </row>
+    <row r="962">
+      <c r="A962" s="2" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="B962" s="2" t="inlineStr">
+        <is>
+          <t>Véronique en épi</t>
+        </is>
+      </c>
+      <c r="C962" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D962" s="2" t="inlineStr">
+        <is>
+          <t>Prairies et pelouses</t>
+        </is>
+      </c>
+      <c r="E962" s="2" t="inlineStr">
+        <is>
+          <t>Pelouses alpines et subalpines</t>
+        </is>
+      </c>
+      <c r="F962" s="2" t="inlineStr">
+        <is>
+          <t>PRA-04</t>
+        </is>
+      </c>
+      <c r="G962" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H962" s="2" t="inlineStr">
+        <is>
+          <t>possible</t>
+        </is>
+      </c>
+      <c r="I962" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J962" s="3" t="inlineStr">
+        <is>
+          <t>Espèce caractéristique des pelouses sèches des Festuco-Brometea, surtout en montagne (100 à 2050 m).</t>
+        </is>
+      </c>
+      <c r="K962" s="2" t="inlineStr">
+        <is>
+          <t>https://inpn.mnhn.fr/espece/cd_nom/129007/tab/habitats</t>
+        </is>
+      </c>
+      <c r="L962" s="3" t="inlineStr"/>
+    </row>
+    <row r="963">
+      <c r="A963" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum davidii</t>
+        </is>
+      </c>
+      <c r="B963" s="2" t="inlineStr">
+        <is>
+          <t>Viorne de David</t>
+        </is>
+      </c>
+      <c r="C963" s="2" t="inlineStr">
+        <is>
+          <t>exotique (cultivée en France)</t>
+        </is>
+      </c>
+      <c r="D963" s="2" t="inlineStr">
+        <is>
+          <t>Jardins et paysages façonnés</t>
+        </is>
+      </c>
+      <c r="E963" s="2" t="inlineStr">
+        <is>
+          <t>Jardins, parcs et plantes ornementales</t>
+        </is>
+      </c>
+      <c r="F963" s="2" t="inlineStr">
+        <is>
+          <t>HAB-01</t>
+        </is>
+      </c>
+      <c r="G963" s="2" t="inlineStr">
+        <is>
+          <t>cultivé ou planté</t>
+        </is>
+      </c>
+      <c r="H963" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I963" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J963" s="3" t="inlineStr">
+        <is>
+          <t>Il est utilisé en horticulture en raison de son beau feuillage persistant vert foncé, lustré.</t>
+        </is>
+      </c>
+      <c r="K963" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/Viburnum_davidii</t>
+        </is>
+      </c>
+      <c r="L963" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum lantana</t>
+        </is>
+      </c>
+      <c r="B964" s="2" t="inlineStr">
+        <is>
+          <t>Viorne mancienne</t>
+        </is>
+      </c>
+      <c r="C964" s="2" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="D964" s="2" t="inlineStr">
+        <is>
+          <t>Jardins et paysages façonnés</t>
+        </is>
+      </c>
+      <c r="E964" s="2" t="inlineStr">
+        <is>
+          <t>Jardins, parcs et plantes ornementales</t>
+        </is>
+      </c>
+      <c r="F964" s="2" t="inlineStr">
+        <is>
+          <t>HAB-01</t>
+        </is>
+      </c>
+      <c r="G964" s="2" t="inlineStr">
+        <is>
+          <t>cultivé ou planté</t>
+        </is>
+      </c>
+      <c r="H964" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I964" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J964" s="3" t="inlineStr">
+        <is>
+          <t>On l'utilise souvent comme plante ornementale pour ses fleurs et ses baies.</t>
+        </is>
+      </c>
+      <c r="K964" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/Viorne_lantane</t>
+        </is>
+      </c>
+      <c r="L964" s="3" t="inlineStr">
+        <is>
+          <t>statut en France non précisé par le texte - milieu naturel non décrit</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum opulus</t>
+        </is>
+      </c>
+      <c r="B965" s="2" t="inlineStr">
+        <is>
+          <t>Viorne obier</t>
+        </is>
+      </c>
+      <c r="C965" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D965" s="2" t="inlineStr">
+        <is>
+          <t>Forêts et sous-bois</t>
+        </is>
+      </c>
+      <c r="E965" s="2" t="inlineStr">
+        <is>
+          <t>Forêts de feuillus caducs</t>
+        </is>
+      </c>
+      <c r="F965" s="2" t="inlineStr">
+        <is>
+          <t>FOR-01</t>
+        </is>
+      </c>
+      <c r="G965" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H965" s="2" t="inlineStr">
+        <is>
+          <t>typique</t>
+        </is>
+      </c>
+      <c r="I965" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J965" s="3" t="inlineStr">
+        <is>
+          <t>C'est un arbuste des bois sur sol humide et des marais.</t>
+        </is>
+      </c>
+      <c r="K965" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/Viorne_obier</t>
+        </is>
+      </c>
+      <c r="L965" s="3" t="inlineStr"/>
+    </row>
+    <row r="966">
+      <c r="A966" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum opulus</t>
+        </is>
+      </c>
+      <c r="B966" s="2" t="inlineStr">
+        <is>
+          <t>Viorne obier</t>
+        </is>
+      </c>
+      <c r="C966" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D966" s="2" t="inlineStr">
+        <is>
+          <t>Marais, prairies humides et tourbières</t>
+        </is>
+      </c>
+      <c r="E966" s="2" t="inlineStr">
+        <is>
+          <t>Roselières et végétations palustres</t>
+        </is>
+      </c>
+      <c r="F966" s="2" t="inlineStr">
+        <is>
+          <t>HUM-04</t>
+        </is>
+      </c>
+      <c r="G966" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H966" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I966" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J966" s="3" t="inlineStr">
+        <is>
+          <t>C'est un arbuste des bois sur sol humide et des marais.</t>
+        </is>
+      </c>
+      <c r="K966" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/Viorne_obier</t>
+        </is>
+      </c>
+      <c r="L966" s="3" t="inlineStr"/>
+    </row>
+    <row r="967">
+      <c r="A967" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum plicatum</t>
+        </is>
+      </c>
+      <c r="B967" s="2" t="inlineStr">
+        <is>
+          <t>Viorne du Japon</t>
+        </is>
+      </c>
+      <c r="C967" s="2" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="D967" s="2" t="inlineStr">
+        <is>
+          <t>Jardins et paysages façonnés</t>
+        </is>
+      </c>
+      <c r="E967" s="2" t="inlineStr">
+        <is>
+          <t>Jardins, parcs et plantes ornementales</t>
+        </is>
+      </c>
+      <c r="F967" s="2" t="inlineStr">
+        <is>
+          <t>HAB-01</t>
+        </is>
+      </c>
+      <c r="G967" s="2" t="inlineStr">
+        <is>
+          <t>cultivé ou planté</t>
+        </is>
+      </c>
+      <c r="H967" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I967" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J967" s="3" t="inlineStr">
+        <is>
+          <t>Viburnum plicatum, la Viorne de Chine, est une plante ornementale de la famille des Adoxacées.</t>
+        </is>
+      </c>
+      <c r="K967" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/Viburnum_plicatum</t>
+        </is>
+      </c>
+      <c r="L967" s="3" t="inlineStr">
+        <is>
+          <t>origine non précisée par le texte - milieu d'origine non renseigné (règle R10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum rhytidophyllum</t>
+        </is>
+      </c>
+      <c r="B968" s="2" t="inlineStr">
+        <is>
+          <t>Viorne à feuilles ridées</t>
+        </is>
+      </c>
+      <c r="C968" s="2" t="inlineStr">
+        <is>
+          <t>exotique (cultivée en France)</t>
+        </is>
+      </c>
+      <c r="D968" s="2" t="inlineStr">
+        <is>
+          <t>Jardins et paysages façonnés</t>
+        </is>
+      </c>
+      <c r="E968" s="2" t="inlineStr">
+        <is>
+          <t>Jardins, parcs et plantes ornementales</t>
+        </is>
+      </c>
+      <c r="F968" s="2" t="inlineStr">
+        <is>
+          <t>HAB-01</t>
+        </is>
+      </c>
+      <c r="G968" s="2" t="inlineStr">
+        <is>
+          <t>cultivé ou planté</t>
+        </is>
+      </c>
+      <c r="H968" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I968" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J968" s="3" t="inlineStr">
+        <is>
+          <t>La viorne à feuilles ridées est utilisée en horticulture pour son feuillage persistant et sa grande rusticité.</t>
+        </is>
+      </c>
+      <c r="K968" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/Viburnum_rhytidophyllum</t>
+        </is>
+      </c>
+      <c r="L968" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10) - potentiellement envahissante en Suisse</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum tinus</t>
+        </is>
+      </c>
+      <c r="B969" s="2" t="inlineStr">
+        <is>
+          <t>Laurier-tin</t>
+        </is>
+      </c>
+      <c r="C969" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D969" s="2" t="inlineStr">
+        <is>
+          <t>Forêts et sous-bois</t>
+        </is>
+      </c>
+      <c r="E969" s="2" t="inlineStr">
+        <is>
+          <t>Boisements de feuillus sempervirents</t>
+        </is>
+      </c>
+      <c r="F969" s="2" t="inlineStr">
+        <is>
+          <t>FOR-02</t>
+        </is>
+      </c>
+      <c r="G969" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H969" s="2" t="inlineStr">
+        <is>
+          <t>typique</t>
+        </is>
+      </c>
+      <c r="I969" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J969" s="3" t="inlineStr">
+        <is>
+          <t>Espèce type des chênaies vertes.</t>
+        </is>
+      </c>
+      <c r="K969" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tela-botanica.org/eflore/consultation/index_mobile.php?module=mobile&amp;referentiel=bdtfx&amp;num_nom=71463</t>
+        </is>
+      </c>
+      <c r="L969" s="3" t="inlineStr">
+        <is>
+          <t>limité au Midi méditerranéen et à la Corse, naturalisé dans le Sud-Ouest</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum tinus</t>
+        </is>
+      </c>
+      <c r="B970" s="2" t="inlineStr">
+        <is>
+          <t>Laurier-tin</t>
+        </is>
+      </c>
+      <c r="C970" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D970" s="2" t="inlineStr">
+        <is>
+          <t>Landes, bruyères et fourrés méditerranéens</t>
+        </is>
+      </c>
+      <c r="E970" s="2" t="inlineStr">
+        <is>
+          <t>Maquis et fourrés méditerranéens</t>
+        </is>
+      </c>
+      <c r="F970" s="2" t="inlineStr">
+        <is>
+          <t>LAN-02</t>
+        </is>
+      </c>
+      <c r="G970" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H970" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I970" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J970" s="3" t="inlineStr">
+        <is>
+          <t>Écologie : bois et garrigues du Midi, Provence, Languedoc, Roussillon, Corse.</t>
+        </is>
+      </c>
+      <c r="K970" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tela-botanica.org/bdtfx-nn-71463</t>
+        </is>
+      </c>
+      <c r="L970" s="3" t="inlineStr">
+        <is>
+          <t>limité au Midi méditerranéen et à la Corse, naturalisé dans le Sud-Ouest</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum × burkwoodii</t>
+        </is>
+      </c>
+      <c r="B971" s="2" t="inlineStr">
+        <is>
+          <t>Viorne de Burkwood</t>
+        </is>
+      </c>
+      <c r="C971" s="2" t="inlineStr">
+        <is>
+          <t>exotique (cultivée en France)</t>
+        </is>
+      </c>
+      <c r="D971" s="2" t="inlineStr">
+        <is>
+          <t>Jardins et paysages façonnés</t>
+        </is>
+      </c>
+      <c r="E971" s="2" t="inlineStr">
+        <is>
+          <t>Jardins, parcs et plantes ornementales</t>
+        </is>
+      </c>
+      <c r="F971" s="2" t="inlineStr">
+        <is>
+          <t>HAB-01</t>
+        </is>
+      </c>
+      <c r="G971" s="2" t="inlineStr">
+        <is>
+          <t>cultivé ou planté</t>
+        </is>
+      </c>
+      <c r="H971" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I971" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J971" s="3" t="inlineStr">
+        <is>
+          <t>Espèce exotique (origine : hybride horticole (V. carlesii × V. utile)), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+        </is>
+      </c>
+      <c r="K971" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rhs.org.uk/plants/91671/viburnum-x-burkwoodii/details</t>
+        </is>
+      </c>
+      <c r="L971" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="2" t="inlineStr">
+        <is>
+          <t>Vinca minor</t>
+        </is>
+      </c>
+      <c r="B972" s="2" t="inlineStr">
+        <is>
+          <t>Petite pervenche</t>
+        </is>
+      </c>
+      <c r="C972" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D972" s="2" t="inlineStr">
+        <is>
+          <t>Forêts et sous-bois</t>
+        </is>
+      </c>
+      <c r="E972" s="2" t="inlineStr">
+        <is>
+          <t>Forêts de feuillus caducs</t>
+        </is>
+      </c>
+      <c r="F972" s="2" t="inlineStr">
+        <is>
+          <t>FOR-01</t>
+        </is>
+      </c>
+      <c r="G972" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H972" s="2" t="inlineStr">
+        <is>
+          <t>typique</t>
+        </is>
+      </c>
+      <c r="I972" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J972" s="3" t="inlineStr">
+        <is>
+          <t>Écologie : bois, haies et rochers dans toute la France, sous-bois herbacés médio-européens planitiaires à montagnards.</t>
+        </is>
+      </c>
+      <c r="K972" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tela-botanica.org/bdtfx-nn-71984</t>
+        </is>
+      </c>
+      <c r="L972" s="3" t="inlineStr"/>
+    </row>
+    <row r="973">
+      <c r="A973" s="2" t="inlineStr">
+        <is>
+          <t>Vinca minor</t>
+        </is>
+      </c>
+      <c r="B973" s="2" t="inlineStr">
+        <is>
+          <t>Petite pervenche</t>
+        </is>
+      </c>
+      <c r="C973" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D973" s="2" t="inlineStr">
+        <is>
+          <t>Haies, lisières et fourrés</t>
+        </is>
+      </c>
+      <c r="E973" s="2" t="inlineStr">
+        <is>
+          <t>Haies et lignes d'arbres</t>
+        </is>
+      </c>
+      <c r="F973" s="2" t="inlineStr">
+        <is>
+          <t>LIS-01</t>
+        </is>
+      </c>
+      <c r="G973" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H973" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I973" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J973" s="3" t="inlineStr">
+        <is>
+          <t>Écologie : bois, haies et rochers dans toute la France.</t>
+        </is>
+      </c>
+      <c r="K973" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tela-botanica.org/bdtfx-nn-71984</t>
+        </is>
+      </c>
+      <c r="L973" s="3" t="inlineStr"/>
+    </row>
+    <row r="974">
+      <c r="A974" s="2" t="inlineStr">
+        <is>
+          <t>Viola odorata</t>
+        </is>
+      </c>
+      <c r="B974" s="2" t="inlineStr">
+        <is>
+          <t>Violette odorante</t>
+        </is>
+      </c>
+      <c r="C974" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D974" s="2" t="inlineStr">
+        <is>
+          <t>Haies, lisières et fourrés</t>
+        </is>
+      </c>
+      <c r="E974" s="2" t="inlineStr">
+        <is>
+          <t>Haies et lignes d'arbres</t>
+        </is>
+      </c>
+      <c r="F974" s="2" t="inlineStr">
+        <is>
+          <t>LIS-01</t>
+        </is>
+      </c>
+      <c r="G974" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H974" s="2" t="inlineStr">
+        <is>
+          <t>typique</t>
+        </is>
+      </c>
+      <c r="I974" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J974" s="3" t="inlineStr">
+        <is>
+          <t>Haies, bois, prés, dans toute la France et en Corse.</t>
+        </is>
+      </c>
+      <c r="K974" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tela-botanica.org/bdtfx-nn-72558</t>
+        </is>
+      </c>
+      <c r="L974" s="3" t="inlineStr"/>
+    </row>
+    <row r="975">
+      <c r="A975" s="2" t="inlineStr">
+        <is>
+          <t>Viola odorata</t>
+        </is>
+      </c>
+      <c r="B975" s="2" t="inlineStr">
+        <is>
+          <t>Violette odorante</t>
+        </is>
+      </c>
+      <c r="C975" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D975" s="2" t="inlineStr">
+        <is>
+          <t>Forêts et sous-bois</t>
+        </is>
+      </c>
+      <c r="E975" s="2" t="inlineStr">
+        <is>
+          <t>Forêts de feuillus caducs</t>
+        </is>
+      </c>
+      <c r="F975" s="2" t="inlineStr">
+        <is>
+          <t>FOR-01</t>
+        </is>
+      </c>
+      <c r="G975" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H975" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I975" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J975" s="3" t="inlineStr">
+        <is>
+          <t>Haies, bois, prés, dans toute la France et en Corse.</t>
+        </is>
+      </c>
+      <c r="K975" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tela-botanica.org/bdtfx-nn-72558</t>
+        </is>
+      </c>
+      <c r="L975" s="3" t="inlineStr"/>
+    </row>
+    <row r="976">
+      <c r="A976" s="2" t="inlineStr">
+        <is>
+          <t>Viola odorata</t>
+        </is>
+      </c>
+      <c r="B976" s="2" t="inlineStr">
+        <is>
+          <t>Violette odorante</t>
+        </is>
+      </c>
+      <c r="C976" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D976" s="2" t="inlineStr">
+        <is>
+          <t>Prairies et pelouses</t>
+        </is>
+      </c>
+      <c r="E976" s="2" t="inlineStr">
+        <is>
+          <t>Prairies mésophiles</t>
+        </is>
+      </c>
+      <c r="F976" s="2" t="inlineStr">
+        <is>
+          <t>PRA-02</t>
+        </is>
+      </c>
+      <c r="G976" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H976" s="2" t="inlineStr">
+        <is>
+          <t>possible</t>
+        </is>
+      </c>
+      <c r="I976" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J976" s="3" t="inlineStr">
+        <is>
+          <t>Haies, bois, prés, dans toute la France et en Corse.</t>
+        </is>
+      </c>
+      <c r="K976" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tela-botanica.org/bdtfx-nn-72558</t>
+        </is>
+      </c>
+      <c r="L976" s="3" t="inlineStr"/>
+    </row>
+    <row r="977">
+      <c r="A977" s="2" t="inlineStr">
+        <is>
+          <t>Vitex agnus-castus</t>
+        </is>
+      </c>
+      <c r="B977" s="2" t="inlineStr">
+        <is>
+          <t>Gattilier</t>
+        </is>
+      </c>
+      <c r="C977" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D977" s="2" t="inlineStr">
+        <is>
+          <t>Mares, rivières et berges</t>
+        </is>
+      </c>
+      <c r="E977" s="2" t="inlineStr">
+        <is>
+          <t>Berges et zones littorales d'eau douce</t>
+        </is>
+      </c>
+      <c r="F977" s="2" t="inlineStr">
+        <is>
+          <t>EAU-03</t>
+        </is>
+      </c>
+      <c r="G977" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H977" s="2" t="inlineStr">
+        <is>
+          <t>typique</t>
+        </is>
+      </c>
+      <c r="I977" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J977" s="3" t="inlineStr">
+        <is>
+          <t>Fourrés de gattiliers (CORINE 44.812) : cours d'eau temporaires et sites humides de l'étage thermoméditerranéen ; rares en Provence orientale et en Corse.</t>
+        </is>
+      </c>
+      <c r="K977" s="2" t="inlineStr">
+        <is>
+          <t>https://inpn.mnhn.fr/habitat/cd_hab/10162/tab/description?lg=en</t>
+        </is>
+      </c>
+      <c r="L977" s="3" t="inlineStr">
+        <is>
+          <t>rare en France</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="2" t="inlineStr">
+        <is>
+          <t>Vitex agnus-castus</t>
+        </is>
+      </c>
+      <c r="B978" s="2" t="inlineStr">
+        <is>
+          <t>Gattilier</t>
+        </is>
+      </c>
+      <c r="C978" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D978" s="2" t="inlineStr">
+        <is>
+          <t>Landes, bruyères et fourrés méditerranéens</t>
+        </is>
+      </c>
+      <c r="E978" s="2" t="inlineStr">
+        <is>
+          <t>Maquis et fourrés méditerranéens</t>
+        </is>
+      </c>
+      <c r="F978" s="2" t="inlineStr">
+        <is>
+          <t>LAN-02</t>
+        </is>
+      </c>
+      <c r="G978" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H978" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I978" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J978" s="3" t="inlineStr">
+        <is>
+          <t>F9.31 « Galeries à Nerium oleander, Vitex agnus-castus et Tamarix » (EUNIS 2012).</t>
+        </is>
+      </c>
+      <c r="K978" s="2" t="inlineStr">
+        <is>
+          <t>https://inpn.mnhn.fr/habitat/cd_hab/5366</t>
+        </is>
+      </c>
+      <c r="L978" s="3" t="inlineStr">
+        <is>
+          <t>rare en France</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="2" t="inlineStr">
+        <is>
+          <t>Vitis coignetiae</t>
+        </is>
+      </c>
+      <c r="B979" s="2" t="inlineStr">
+        <is>
+          <t>Vigne de Coignet</t>
+        </is>
+      </c>
+      <c r="C979" s="2" t="inlineStr">
+        <is>
+          <t>exotique (cultivée en France)</t>
+        </is>
+      </c>
+      <c r="D979" s="2" t="inlineStr">
+        <is>
+          <t>Jardins et paysages façonnés</t>
+        </is>
+      </c>
+      <c r="E979" s="2" t="inlineStr">
+        <is>
+          <t>Jardins, parcs et plantes ornementales</t>
+        </is>
+      </c>
+      <c r="F979" s="2" t="inlineStr">
+        <is>
+          <t>HAB-01</t>
+        </is>
+      </c>
+      <c r="G979" s="2" t="inlineStr">
+        <is>
+          <t>cultivé ou planté</t>
+        </is>
+      </c>
+      <c r="H979" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I979" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J979" s="3" t="inlineStr">
+        <is>
+          <t>La vigne de Coignet est utilisée comme plante ornementale pour son feuillage d'automne qui vire au rouge lie-de-vin puis à l'écarlate.</t>
+        </is>
+      </c>
+      <c r="K979" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/Vitis_coignetiae</t>
+        </is>
+      </c>
+      <c r="L979" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="2" t="inlineStr">
+        <is>
+          <t>Vitis vinifera</t>
+        </is>
+      </c>
+      <c r="B980" s="2" t="inlineStr">
+        <is>
+          <t>Vigne cultivée</t>
+        </is>
+      </c>
+      <c r="C980" s="2" t="inlineStr">
+        <is>
+          <t>indigène</t>
+        </is>
+      </c>
+      <c r="D980" s="2" t="inlineStr">
+        <is>
+          <t>Forêts et sous-bois</t>
+        </is>
+      </c>
+      <c r="E980" s="2" t="inlineStr">
+        <is>
+          <t>Forêts de feuillus caducs</t>
+        </is>
+      </c>
+      <c r="F980" s="2" t="inlineStr">
+        <is>
+          <t>FOR-01</t>
+        </is>
+      </c>
+      <c r="G980" s="2" t="inlineStr">
+        <is>
+          <t>naturel</t>
+        </is>
+      </c>
+      <c r="H980" s="2" t="inlineStr">
+        <is>
+          <t>typique</t>
+        </is>
+      </c>
+      <c r="I980" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J980" s="3" t="inlineStr">
+        <is>
+          <t>Forêts alluviales le long des cours d'eau, sur sols frais neutres à calcaires, jusqu'à 600 m environ.</t>
+        </is>
+      </c>
+      <c r="K980" s="2" t="inlineStr">
+        <is>
+          <t>https://inpn.mnhn.fr/espece/cd_nom/142451</t>
+        </is>
+      </c>
+      <c r="L980" s="3" t="inlineStr">
+        <is>
+          <t>écologie donnée pour la subsp. sylvestris (vigne sauvage rare) - la culture de la vigne n'est pas sourcée ici</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="2" t="inlineStr">
+        <is>
+          <t>Washingtonia filifera</t>
+        </is>
+      </c>
+      <c r="B981" s="2" t="inlineStr">
+        <is>
+          <t>Palmier de Californie</t>
+        </is>
+      </c>
+      <c r="C981" s="2" t="inlineStr">
+        <is>
+          <t>exotique (cultivée en France)</t>
+        </is>
+      </c>
+      <c r="D981" s="2" t="inlineStr">
+        <is>
+          <t>Jardins et paysages façonnés</t>
+        </is>
+      </c>
+      <c r="E981" s="2" t="inlineStr">
+        <is>
+          <t>Jardins, parcs et plantes ornementales</t>
+        </is>
+      </c>
+      <c r="F981" s="2" t="inlineStr">
+        <is>
+          <t>HAB-01</t>
+        </is>
+      </c>
+      <c r="G981" s="2" t="inlineStr">
+        <is>
+          <t>cultivé ou planté</t>
+        </is>
+      </c>
+      <c r="H981" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I981" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J981" s="3" t="inlineStr">
+        <is>
+          <t>Espèce exotique (origine : Sud-Ouest des États-Unis (Californie, Arizona), Basse-Californie), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+        </is>
+      </c>
+      <c r="K981" s="2" t="inlineStr">
+        <is>
+          <t>https://gardenerspath.com/plants/landscape-trees/grow-california-fan-palm/</t>
+        </is>
+      </c>
+      <c r="L981" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="2" t="inlineStr">
+        <is>
+          <t>Weigela florida</t>
+        </is>
+      </c>
+      <c r="B982" s="2" t="inlineStr">
+        <is>
+          <t>Weigela</t>
+        </is>
+      </c>
+      <c r="C982" s="2" t="inlineStr">
+        <is>
+          <t>exotique (cultivée en France)</t>
+        </is>
+      </c>
+      <c r="D982" s="2" t="inlineStr">
+        <is>
+          <t>Jardins et paysages façonnés</t>
+        </is>
+      </c>
+      <c r="E982" s="2" t="inlineStr">
+        <is>
+          <t>Jardins, parcs et plantes ornementales</t>
+        </is>
+      </c>
+      <c r="F982" s="2" t="inlineStr">
+        <is>
+          <t>HAB-01</t>
+        </is>
+      </c>
+      <c r="G982" s="2" t="inlineStr">
+        <is>
+          <t>cultivé ou planté</t>
+        </is>
+      </c>
+      <c r="H982" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I982" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J982" s="3" t="inlineStr">
+        <is>
+          <t>Espèce exotique (origine : Chine du Nord, Corée, Japon), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+        </is>
+      </c>
+      <c r="K982" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rhs.org.uk/plants/101006/wd/details</t>
+        </is>
+      </c>
+      <c r="L982" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="2" t="inlineStr">
+        <is>
+          <t>Wisteria floribunda</t>
+        </is>
+      </c>
+      <c r="B983" s="2" t="inlineStr">
+        <is>
+          <t>Glycine du Japon</t>
+        </is>
+      </c>
+      <c r="C983" s="2" t="inlineStr">
+        <is>
+          <t>exotique (cultivée en France)</t>
+        </is>
+      </c>
+      <c r="D983" s="2" t="inlineStr">
+        <is>
+          <t>Jardins et paysages façonnés</t>
+        </is>
+      </c>
+      <c r="E983" s="2" t="inlineStr">
+        <is>
+          <t>Jardins, parcs et plantes ornementales</t>
+        </is>
+      </c>
+      <c r="F983" s="2" t="inlineStr">
+        <is>
+          <t>HAB-01</t>
+        </is>
+      </c>
+      <c r="G983" s="2" t="inlineStr">
+        <is>
+          <t>cultivé ou planté</t>
+        </is>
+      </c>
+      <c r="H983" s="2" t="inlineStr">
+        <is>
+          <t>typique</t>
+        </is>
+      </c>
+      <c r="I983" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J983" s="3" t="inlineStr">
+        <is>
+          <t>C'est une plante grimpante ligneuse originaire du Japon, couramment cultivée comme plante ornementale pour ses longues grappes de fleurs pendantes.</t>
+        </is>
+      </c>
+      <c r="K983" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/Wisteria_floribunda</t>
+        </is>
+      </c>
+      <c r="L983" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="2" t="inlineStr">
+        <is>
+          <t>Wisteria sinensis</t>
+        </is>
+      </c>
+      <c r="B984" s="2" t="inlineStr">
+        <is>
+          <t>Glycine de Chine</t>
+        </is>
+      </c>
+      <c r="C984" s="2" t="inlineStr">
+        <is>
+          <t>exotique (cultivée en France)</t>
+        </is>
+      </c>
+      <c r="D984" s="2" t="inlineStr">
+        <is>
+          <t>Jardins et paysages façonnés</t>
+        </is>
+      </c>
+      <c r="E984" s="2" t="inlineStr">
+        <is>
+          <t>Jardins, parcs et plantes ornementales</t>
+        </is>
+      </c>
+      <c r="F984" s="2" t="inlineStr">
+        <is>
+          <t>HAB-01</t>
+        </is>
+      </c>
+      <c r="G984" s="2" t="inlineStr">
+        <is>
+          <t>cultivé ou planté</t>
+        </is>
+      </c>
+      <c r="H984" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I984" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J984" s="3" t="inlineStr">
+        <is>
+          <t>Présente en France, cultivée en extérieur.</t>
+        </is>
+      </c>
+      <c r="K984" s="2" t="inlineStr">
+        <is>
+          <t>https://tela-botanica.org/eflore/?action=fiche&amp;module=fiche&amp;num_nom=72992&amp;onglet=synthese&amp;referentiel=bdtfx</t>
+        </is>
+      </c>
+      <c r="L984" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="2" t="inlineStr">
+        <is>
+          <t>Yucca filamentosa</t>
+        </is>
+      </c>
+      <c r="B985" s="2" t="inlineStr">
+        <is>
+          <t>Yucca filamenteux</t>
+        </is>
+      </c>
+      <c r="C985" s="2" t="inlineStr">
+        <is>
+          <t>exotique (cultivée en France)</t>
+        </is>
+      </c>
+      <c r="D985" s="2" t="inlineStr">
+        <is>
+          <t>Jardins et paysages façonnés</t>
+        </is>
+      </c>
+      <c r="E985" s="2" t="inlineStr">
+        <is>
+          <t>Jardins, parcs et plantes ornementales</t>
+        </is>
+      </c>
+      <c r="F985" s="2" t="inlineStr">
+        <is>
+          <t>HAB-01</t>
+        </is>
+      </c>
+      <c r="G985" s="2" t="inlineStr">
+        <is>
+          <t>cultivé ou planté</t>
+        </is>
+      </c>
+      <c r="H985" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I985" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J985" s="3" t="inlineStr">
+        <is>
+          <t>Espèce exotique (origine : Sud-Est des États-Unis), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+        </is>
+      </c>
+      <c r="K985" s="2" t="inlineStr">
+        <is>
+          <t>https://plants.ces.ncsu.edu/plants/all/yucca-filamentosa/</t>
+        </is>
+      </c>
+      <c r="L985" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="2" t="inlineStr">
+        <is>
+          <t>Zantedeschia aethiopica</t>
+        </is>
+      </c>
+      <c r="B986" s="2" t="inlineStr">
+        <is>
+          <t>Arum d'Éthiopie</t>
+        </is>
+      </c>
+      <c r="C986" s="2" t="inlineStr">
+        <is>
+          <t>exotique (cultivée en France)</t>
+        </is>
+      </c>
+      <c r="D986" s="2" t="inlineStr">
+        <is>
+          <t>Jardins et paysages façonnés</t>
+        </is>
+      </c>
+      <c r="E986" s="2" t="inlineStr">
+        <is>
+          <t>Jardins, parcs et plantes ornementales</t>
+        </is>
+      </c>
+      <c r="F986" s="2" t="inlineStr">
+        <is>
+          <t>HAB-01</t>
+        </is>
+      </c>
+      <c r="G986" s="2" t="inlineStr">
+        <is>
+          <t>cultivé ou planté</t>
+        </is>
+      </c>
+      <c r="H986" s="2" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="I986" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J986" s="3" t="inlineStr">
+        <is>
+          <t>Espèce exotique (origine : Afrique du Sud), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
+        </is>
+      </c>
+      <c r="K986" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rhs.org.uk/plants/19190/zantedeschia-aethiopica/details</t>
+        </is>
+      </c>
+      <c r="L986" s="3" t="inlineStr">
+        <is>
+          <t>milieu d'origine hors de France non renseigné (règle R10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="2" t="inlineStr">
+        <is>
           <t>Zelkova serrata</t>
         </is>
       </c>
-      <c r="B938" s="2" t="inlineStr">
+      <c r="B987" s="2" t="inlineStr">
         <is>
           <t>Zelkova du Japon</t>
         </is>
       </c>
-      <c r="C938" s="2" t="inlineStr">
+      <c r="C987" s="2" t="inlineStr">
         <is>
           <t>exotique (cultivée en France)</t>
         </is>
       </c>
-      <c r="D938" s="2" t="inlineStr">
+      <c r="D987" s="2" t="inlineStr">
         <is>
           <t>Jardins et paysages façonnés</t>
         </is>
       </c>
-      <c r="E938" s="2" t="inlineStr">
+      <c r="E987" s="2" t="inlineStr">
         <is>
           <t>Jardins, parcs et plantes ornementales</t>
         </is>
       </c>
-      <c r="F938" s="2" t="inlineStr">
+      <c r="F987" s="2" t="inlineStr">
         <is>
           <t>HAB-01</t>
         </is>
       </c>
-      <c r="G938" s="2" t="inlineStr">
+      <c r="G987" s="2" t="inlineStr">
         <is>
           <t>cultivé ou planté</t>
         </is>
       </c>
-      <c r="H938" s="2" t="inlineStr">
+      <c r="H987" s="2" t="inlineStr">
         <is>
           <t>frequent</t>
         </is>
       </c>
-      <c r="I938" s="2" t="inlineStr">
-        <is>
-          <t>vérifiée</t>
-        </is>
-      </c>
-      <c r="J938" s="3" t="inlineStr">
+      <c r="I987" s="2" t="inlineStr">
+        <is>
+          <t>vérifiée</t>
+        </is>
+      </c>
+      <c r="J987" s="3" t="inlineStr">
         <is>
           <t>Espèce exotique (origine : Japon, Corée, Chine), cultivée en France comme plante d'ornement ; statut relevé dans donnees/milieux-especes.json (certitude source).</t>
         </is>
       </c>
-      <c r="K938" s="2" t="inlineStr">
+      <c r="K987" s="2" t="inlineStr">
         <is>
           <t>https://www.rhs.org.uk/plants/19206/wd/details</t>
         </is>
       </c>
-      <c r="L938" s="3" t="inlineStr">
+      <c r="L987" s="3" t="inlineStr">
         <is>
           <t>milieu d'origine hors de France non renseigné (règle R10)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L938"/>
+  <autoFilter ref="A1:L987"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -58362,40 +61376,90 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K901" r:id="rId899"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K902" r:id="rId900"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K903" r:id="rId901"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K905" r:id="rId902"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K906" r:id="rId903"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K907" r:id="rId904"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K908" r:id="rId905"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K909" r:id="rId906"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K910" r:id="rId907"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K911" r:id="rId908"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K912" r:id="rId909"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K913" r:id="rId910"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K914" r:id="rId911"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K915" r:id="rId912"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K916" r:id="rId913"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K917" r:id="rId914"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K918" r:id="rId915"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K919" r:id="rId916"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K920" r:id="rId917"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K921" r:id="rId918"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K922" r:id="rId919"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K923" r:id="rId920"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K924" r:id="rId921"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K925" r:id="rId922"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K926" r:id="rId923"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K927" r:id="rId924"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K928" r:id="rId925"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K929" r:id="rId926"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K930" r:id="rId927"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K931" r:id="rId928"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K932" r:id="rId929"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K933" r:id="rId930"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K934" r:id="rId931"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K935" r:id="rId932"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K936" r:id="rId933"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K937" r:id="rId934"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K938" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K904" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K905" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K906" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K907" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K908" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K909" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K910" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K911" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K912" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K913" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K914" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K915" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K916" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K917" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K918" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K919" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K920" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K921" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K922" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K923" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K924" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K925" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K926" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K927" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K928" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K929" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K930" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K931" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K932" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K933" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K934" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K935" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K936" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K937" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K938" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K939" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K940" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K941" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K942" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K943" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K944" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K945" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K946" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K947" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K948" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K949" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K950" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K951" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K952" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K953" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K954" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K955" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K956" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K957" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K958" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K959" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K960" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K961" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K962" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K963" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K964" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K965" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K966" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K967" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K968" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K969" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K970" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K971" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K972" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K973" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K974" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K975" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K976" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K977" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K978" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K979" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K980" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K981" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K982" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K983" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K984" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K985" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K986" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K987" r:id="rId985"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58495,7 +61559,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
@@ -58515,7 +61579,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6">
@@ -58555,7 +61619,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -58595,7 +61659,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>327</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -58615,7 +61679,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -58635,7 +61699,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -58655,7 +61719,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -58675,7 +61739,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -58715,7 +61779,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -58735,7 +61799,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -58935,7 +61999,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27">
@@ -58955,7 +62019,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28">
@@ -59015,7 +62079,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -59089,7 +62153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C179"/>
+  <dimension ref="A1:C145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -61259,12 +64323,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Solidago canadensis</t>
+          <t>Sorbus × thuringiaca</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Verge d'or</t>
+          <t>Alisier de Thuringe</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -61276,12 +64340,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sorbus intermedia</t>
+          <t>Spiraea thunbergii</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Alisier de Suède</t>
+          <t>Spirée de Thunberg</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -61293,12 +64357,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sorbus × thuringiaca</t>
+          <t>Spiraea × vanhouttei</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Alisier de Thuringe</t>
+          <t>Spirée de Van Houtte</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -61310,12 +64374,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Spiraea japonica</t>
+          <t>Stachys officinalis</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Spirée du Japon</t>
+          <t>Bétoine officinale</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -61327,12 +64391,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Spiraea thunbergii</t>
+          <t>Stipa calamagrostis</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Spirée de Thunberg</t>
+          <t>Calamagrostide argentée</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -61344,12 +64408,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Spiraea × vanhouttei</t>
+          <t>Stipa tenuissima</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Spirée de Van Houtte</t>
+          <t>Stipe très fine</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -61361,12 +64425,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Stachys officinalis</t>
+          <t>Syringa reticulata</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Bétoine officinale</t>
+          <t>Lilas du Japon</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -61378,12 +64442,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Stipa calamagrostis</t>
+          <t>Tilia americana</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Calamagrostide argentée</t>
+          <t>Tilleul d'Amérique</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -61395,12 +64459,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Stipa gigantea</t>
+          <t>Tilia × europaea</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Stipe géante</t>
+          <t>Tilleul commun</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -61412,12 +64476,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Stipa tenuissima</t>
+          <t>Ulmus × hollandica</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Stipe très fine</t>
+          <t>Orme de Hollande</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -61429,12 +64493,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Strelitzia reginae</t>
+          <t>Vaccinium corymbosum</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Oiseau de paradis</t>
+          <t>Myrtillier</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -61446,12 +64510,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Symphoricarpos albus</t>
+          <t>Vaccinium vitis-idaea</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Symphorine</t>
+          <t>Airelle rouge</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -61463,12 +64527,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Syringa reticulata</t>
+          <t>Veronicastrum virginicum</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Lilas du Japon</t>
+          <t>Véronique de Virginie</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -61480,12 +64544,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Syringa vulgaris</t>
+          <t>Viburnum carlesii</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Lilas commun</t>
+          <t>Viorne de Carles</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -61497,12 +64561,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Tanacetum parthenium</t>
+          <t>Viburnum odoratissimum</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Grande camomille</t>
+          <t>Viorne odorante</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -61514,12 +64578,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Tanacetum vulgare</t>
+          <t>Viburnum × bodnantense</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Tanaisie commune</t>
+          <t>Viorne de Bodnant</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -61531,12 +64595,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Tetradium daniellii</t>
+          <t>Vinca major</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Arbre à miel</t>
+          <t>Grande pervenche</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -61548,593 +64612,15 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Teucrium chamaedrys</t>
+          <t>Westringia fruticosa</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Germandrée petit-chêne</t>
+          <t>Romarin d'Australie</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Thuja occidentalis</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Thuya du Canada</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Thuja plicata</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Thuya géant</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Thymus serpyllum</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Serpolet</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Tilia americana</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Tilleul d'Amérique</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Tilia tomentosa</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Tilleul argenté</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Tilia × europaea</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Tilleul commun</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Tsuga canadensis</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Pruche du Canada</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Tsuga heterophylla</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Pruche de l'Ouest</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Tulbaghia violacea</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Ail du Cap</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Tussilago farfara</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Tussilage</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>à vérifier seulement</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Orme de montagne</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Ulmus laevis</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Orme lisse</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Ulmus parvifolia</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Orme de Chine</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Ulmus pumila</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Orme de Sibérie</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Ulmus × hollandica</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Orme de Hollande</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Vaccinium corymbosum</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Myrtillier</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Vaccinium myrtillus</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Myrtille</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Vaccinium vitis-idaea</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Airelle rouge</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Verbena bonariensis</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Verveine de Buenos Aires</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Verbena officinalis</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Verveine officinale</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Veronica chamaedrys</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Véronique petit-chêne</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Veronicastrum virginicum</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Véronique de Virginie</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Viburnum carlesii</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Viorne de Carles</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Viburnum davidii</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Viorne de David</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Viburnum lantana</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Viorne mancienne</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Viburnum odoratissimum</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Viorne odorante</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Viburnum opulus</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Viorne obier</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Viburnum plicatum</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Viorne du Japon</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Viburnum rhytidophyllum</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Viorne à feuilles ridées</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Viburnum × bodnantense</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Viorne de Bodnant</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Vinca major</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Grande pervenche</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Vitis coignetiae</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Vigne de Coignet</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Westringia fruticosa</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Romarin d'Australie</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>aucune source trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Wisteria floribunda</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Glycine du Japon</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
         <is>
           <t>aucune source trouvée</t>
         </is>
